--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 08:56:24</t>
+          <t>2026-07-28 00:59:01</t>
         </is>
       </c>
     </row>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 00:59:01</t>
+          <t>2026-07-28 01:00:14</t>
         </is>
       </c>
     </row>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -26,12 +26,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新時間</t>
+          <t>資料基準</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 01:00:14</t>
+          <t>大樂透 2026-07-24 第 115000073 期；威力彩 2026-07-27 第 115000060 期</t>
         </is>
       </c>
     </row>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-07-24 第 115000073 期；威力彩 2026-07-27 第 115000060 期</t>
+          <t>大樂透 2026-07-28 第 115000074 期；威力彩 2026-07-27 第 115000060 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12, 15, 16, 18, 29, 34</t>
+          <t>15, 16, 18, 19, 29, 34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -251,7 +251,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>隨機基準</t>
         </is>
       </c>
       <c r="B4">
@@ -261,29 +261,29 @@
         <v>0.69</v>
       </c>
       <c r="D4">
-        <v>19.0</v>
+        <v>9.5</v>
       </c>
       <c r="E4">
-        <v>2.4</v>
+        <v>0.0</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.69</v>
+        <v>0.667</v>
       </c>
       <c r="D5">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -295,23 +295,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>隨機基準</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.69</v>
+        <v>0.667</v>
       </c>
       <c r="D6">
-        <v>9.5</v>
+        <v>16.7</v>
       </c>
       <c r="E6">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -324,7 +324,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="D7">
         <v>11.9</v>
@@ -398,7 +398,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>77.38</v>
+        <v>77.77</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>12.5</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>71.44</v>
+        <v>71.67</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="H3">
         <v>80.0</v>
       </c>
       <c r="I3">
-        <v>6.25</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>71.28</v>
+        <v>69.95</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>12.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>68.85</v>
+        <v>69.3</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -494,7 +494,7 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>70.0</v>
@@ -503,7 +503,7 @@
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>67.76</v>
+        <v>68.15</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="H6">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I6">
-        <v>18.75</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>67.7</v>
+        <v>68.13</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7">
+        <v>90.0</v>
+      </c>
+      <c r="H7">
         <v>60.0</v>
       </c>
-      <c r="H7">
-        <v>80.0</v>
-      </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>67.21</v>
+        <v>67.58</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -581,7 +581,7 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>80.0</v>
@@ -590,7 +590,7 @@
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>18.75</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>66.82</v>
+        <v>67.22</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -610,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>90.0</v>
@@ -619,7 +619,7 @@
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>12.5</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C10">
-        <v>66.74</v>
+        <v>67.03</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>15.62</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>66.66</v>
+        <v>66.86</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>70.0</v>
+        <v>100.0</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>18.75</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="12">
@@ -685,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12">
-        <v>66.36</v>
+        <v>64.95</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>90.0</v>
@@ -706,7 +706,7 @@
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>9.38</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -717,7 +717,7 @@
         <v>36</v>
       </c>
       <c r="C13">
-        <v>64.11</v>
+        <v>64.52</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -726,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13">
         <v>60.0</v>
@@ -735,7 +735,7 @@
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>9.38</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="14">
@@ -746,7 +746,7 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>63.64</v>
+        <v>64.06</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>60.0</v>
@@ -764,7 +764,7 @@
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>6.25</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         <v>28</v>
       </c>
       <c r="C15">
-        <v>63.54</v>
+        <v>63.85</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -784,7 +784,7 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>70.0</v>
@@ -793,7 +793,7 @@
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>31.25</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="16">
@@ -804,7 +804,7 @@
         <v>35</v>
       </c>
       <c r="C16">
-        <v>62.7</v>
+        <v>63.15</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -813,7 +813,7 @@
         <v>3</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>60.0</v>
@@ -822,7 +822,7 @@
         <v>60.0</v>
       </c>
       <c r="I16">
-        <v>0.0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>62.21</v>
+        <v>62.7</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="H17">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I17">
-        <v>18.75</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>60.81</v>
+        <v>62.03</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>9.38</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>60.81</v>
+        <v>61.77</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>9.38</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="20">
@@ -917,13 +917,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C20">
-        <v>60.72</v>
+        <v>61.22</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -932,13 +932,13 @@
         <v>4</v>
       </c>
       <c r="G20">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>12.5</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C21">
-        <v>60.34</v>
+        <v>61.12</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>6.25</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>59.94</v>
+        <v>60.67</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G22">
         <v>70.0</v>
       </c>
       <c r="H22">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>40.62</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>59.87</v>
+        <v>60.21</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H23">
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>3.12</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C24">
-        <v>59.79</v>
+        <v>60.21</v>
       </c>
       <c r="D24">
         <v>7</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>70.0</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>6.25</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="25">
@@ -1065,25 +1065,25 @@
         <v>48</v>
       </c>
       <c r="C25">
-        <v>59.64</v>
+        <v>59.4</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25">
-        <v>90.0</v>
+        <v>80.0</v>
       </c>
       <c r="H25">
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>31.25</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="26">
@@ -1094,25 +1094,25 @@
         <v>47</v>
       </c>
       <c r="C26">
-        <v>58.31</v>
+        <v>58.13</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>100.0</v>
+        <v>90.0</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>18.75</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="27">
@@ -1123,7 +1123,7 @@
         <v>22</v>
       </c>
       <c r="C27">
-        <v>57.76</v>
+        <v>57.94</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27">
         <v>70.0</v>
@@ -1141,7 +1141,7 @@
         <v>0.0</v>
       </c>
       <c r="I27">
-        <v>59.38</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="28">
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G28">
         <v>50.0</v>
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C29">
-        <v>57.08</v>
+        <v>56.12</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G29">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="H29">
         <v>0.0</v>
       </c>
       <c r="I29">
-        <v>62.5</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C30">
-        <v>55.88</v>
+        <v>55.21</v>
       </c>
       <c r="D30">
         <v>7</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <v>70.0</v>
       </c>
       <c r="H30">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I30">
-        <v>46.88</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="31">
@@ -1239,7 +1239,7 @@
         <v>13</v>
       </c>
       <c r="C31">
-        <v>54.59</v>
+        <v>54.98</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -1248,7 +1248,7 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31">
         <v>50.0</v>
@@ -1257,7 +1257,7 @@
         <v>40.0</v>
       </c>
       <c r="I31">
-        <v>15.62</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="32">
@@ -1265,7 +1265,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>53.85</v>
@@ -1297,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>53.5</v>
+        <v>53.61</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <v>50.0</v>
@@ -1315,7 +1315,7 @@
         <v>0.0</v>
       </c>
       <c r="I33">
-        <v>75.0</v>
+        <v>75.76</v>
       </c>
     </row>
     <row r="34">
@@ -1326,7 +1326,7 @@
         <v>20</v>
       </c>
       <c r="C34">
-        <v>52.88</v>
+        <v>53.16</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G34">
         <v>50.0</v>
@@ -1344,7 +1344,7 @@
         <v>20.0</v>
       </c>
       <c r="I34">
-        <v>37.5</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C35">
-        <v>52.72</v>
+        <v>53.15</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="H35">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I35">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="36">
@@ -1384,7 +1384,7 @@
         <v>46</v>
       </c>
       <c r="C36">
-        <v>52.27</v>
+        <v>52.71</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -1393,7 +1393,7 @@
         <v>3</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>40.0</v>
@@ -1402,7 +1402,7 @@
         <v>60.0</v>
       </c>
       <c r="I36">
-        <v>3.12</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="37">
@@ -1413,7 +1413,7 @@
         <v>33</v>
       </c>
       <c r="C37">
-        <v>51.47</v>
+        <v>51.8</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>50.0</v>
@@ -1431,7 +1431,7 @@
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>28.12</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="38">
@@ -1442,7 +1442,7 @@
         <v>17</v>
       </c>
       <c r="C38">
-        <v>48.19</v>
+        <v>48.61</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>50.0</v>
@@ -1460,7 +1460,7 @@
         <v>20.0</v>
       </c>
       <c r="I38">
-        <v>6.25</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="39">
@@ -1471,7 +1471,7 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>47.27</v>
+        <v>47.71</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -1480,7 +1480,7 @@
         <v>2</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>40.0</v>
@@ -1489,7 +1489,7 @@
         <v>40.0</v>
       </c>
       <c r="I39">
-        <v>3.12</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="40">
@@ -1497,7 +1497,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C40">
         <v>46.8</v>
@@ -1529,7 +1529,7 @@
         <v>38</v>
       </c>
       <c r="C41">
-        <v>45.71</v>
+        <v>45.89</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41">
         <v>40.0</v>
@@ -1547,7 +1547,7 @@
         <v>0.0</v>
       </c>
       <c r="I41">
-        <v>59.38</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C42">
-        <v>42.91</v>
+        <v>42.25</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H42">
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>43.75</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>42.91</v>
+        <v>41.8</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
         <v>1</v>
-      </c>
-      <c r="F43">
-        <v>14</v>
       </c>
       <c r="G43">
         <v>30.0</v>
       </c>
       <c r="H43">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I43">
-        <v>43.75</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="C44">
-        <v>41.51</v>
+        <v>41.8</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44">
         <v>30.0</v>
@@ -1634,7 +1634,7 @@
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>34.38</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="45">
@@ -1642,25 +1642,25 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C45">
-        <v>41.35</v>
+        <v>41.8</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H45">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I45">
         <v>0.0</v>
@@ -1671,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C46">
-        <v>40.1</v>
+        <v>40.44</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G46">
         <v>30.0</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>25.0</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C47">
-        <v>40.1</v>
+        <v>39.99</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G47">
         <v>30.0</v>
       </c>
       <c r="H47">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I47">
-        <v>25.0</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C48">
-        <v>39.79</v>
+        <v>39.08</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G48">
         <v>30.0</v>
       </c>
       <c r="H48">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I48">
-        <v>56.25</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C49">
-        <v>38.69</v>
+        <v>38.17</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G49">
         <v>30.0</v>
       </c>
       <c r="H49">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I49">
-        <v>15.62</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>33.4</v>
+        <v>33.63</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50">
         <v>20.0</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>50.0</v>
+        <v>51.52</v>
       </c>
     </row>
   </sheetData>
@@ -1867,173 +1867,173 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G3">
         <v>35</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I4">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H6">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -2042,345 +2042,345 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I7">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
         <v>19</v>
       </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
       <c r="H8">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H10">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>24</v>
+      </c>
+      <c r="G11">
         <v>29</v>
       </c>
-      <c r="F11">
-        <v>33</v>
-      </c>
-      <c r="G11">
-        <v>34</v>
-      </c>
       <c r="H11">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I11">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G12">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H12">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I12">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G13">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I13">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H14">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G15">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I15">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>25</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G16">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H16">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I16">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G17">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C18">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18">
+        <v>16</v>
+      </c>
+      <c r="F18">
         <v>20</v>
-      </c>
-      <c r="D18">
-        <v>26</v>
-      </c>
-      <c r="E18">
-        <v>29</v>
-      </c>
-      <c r="F18">
-        <v>31</v>
       </c>
       <c r="G18">
         <v>37</v>
@@ -2389,810 +2389,810 @@
         <v>49</v>
       </c>
       <c r="I18">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19">
         <v>29</v>
       </c>
       <c r="F19">
+        <v>31</v>
+      </c>
+      <c r="G19">
         <v>37</v>
       </c>
-      <c r="G19">
-        <v>47</v>
-      </c>
       <c r="H19">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G20">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H20">
         <v>48</v>
       </c>
       <c r="I20">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E21">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G21">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H21">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I21">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H22">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G23">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H23">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I23">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D24">
+        <v>12</v>
+      </c>
+      <c r="E24">
         <v>18</v>
       </c>
-      <c r="E24">
-        <v>25</v>
-      </c>
       <c r="F24">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G24">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H24">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I24">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F25">
         <v>28</v>
       </c>
       <c r="G25">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H25">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I25">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G26">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H26">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I26">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G27">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H27">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C28">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>14</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>26</v>
+      </c>
+      <c r="H28">
+        <v>32</v>
+      </c>
+      <c r="I28">
         <v>7</v>
-      </c>
-      <c r="D28">
-        <v>14</v>
-      </c>
-      <c r="E28">
-        <v>16</v>
-      </c>
-      <c r="F28">
-        <v>37</v>
-      </c>
-      <c r="G28">
-        <v>39</v>
-      </c>
-      <c r="H28">
-        <v>47</v>
-      </c>
-      <c r="I28">
-        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G29">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H29">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I29">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F30">
+        <v>19</v>
+      </c>
+      <c r="G30">
+        <v>20</v>
+      </c>
+      <c r="H30">
+        <v>40</v>
+      </c>
+      <c r="I30">
         <v>22</v>
-      </c>
-      <c r="G30">
-        <v>40</v>
-      </c>
-      <c r="H30">
-        <v>45</v>
-      </c>
-      <c r="I30">
-        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G31">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H31">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I31">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C32">
         <v>4</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G32">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H32">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I32">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H33">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I33">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F34">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G34">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H34">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I34">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C35">
         <v>5</v>
       </c>
       <c r="D35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E35">
+        <v>13</v>
+      </c>
+      <c r="F35">
         <v>25</v>
       </c>
-      <c r="F35">
-        <v>40</v>
-      </c>
       <c r="G35">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H35">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I35">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G36">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H36">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I36">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C37">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F37">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G37">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H37">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I37">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E38">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G38">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H38">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I38">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F39">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G39">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H39">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I39">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G40">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H40">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G41">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H41">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I41">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>11</v>
       </c>
       <c r="E42">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F42">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G42">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H42">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I42">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D43">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E43">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F43">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G43">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H43">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I43">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C44">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E44">
         <v>27</v>
       </c>
       <c r="F44">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G44">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H44">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I44">
         <v>37</v>
@@ -3200,30 +3200,30 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E45">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F45">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G45">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H45">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I45">
         <v>37</v>
@@ -3231,188 +3231,188 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C46">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E46">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F46">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G46">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H46">
         <v>49</v>
       </c>
       <c r="I46">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D47">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E47">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F47">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G47">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H47">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I47">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D48">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E48">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F48">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G48">
+        <v>45</v>
+      </c>
+      <c r="H48">
         <v>47</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>48</v>
-      </c>
-      <c r="I48">
-        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49">
         <v>22</v>
       </c>
       <c r="F49">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G49">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H49">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I49">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E50">
         <v>22</v>
       </c>
       <c r="F50">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G50">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H50">
+        <v>49</v>
+      </c>
+      <c r="I50">
         <v>31</v>
-      </c>
-      <c r="I50">
-        <v>45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E51">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F51">
         <v>27</v>
       </c>
       <c r="G51">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I51">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-07-28 第 115000074 期；威力彩 2026-07-27 第 115000060 期</t>
+          <t>大樂透 2026-07-28 第 115000074 期；威力彩 2026-07-30 第 115000061 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 13, 29, 34, 35, 38</t>
+          <t>9, 13, 14, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.571 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.547 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,10 +3464,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.238</v>
+        <v>1.19</v>
       </c>
       <c r="D2">
-        <v>38.1</v>
+        <v>35.7</v>
       </c>
       <c r="E2">
         <v>7.1</v>
@@ -3486,10 +3486,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.238</v>
+        <v>1.19</v>
       </c>
       <c r="D3">
-        <v>38.1</v>
+        <v>35.7</v>
       </c>
       <c r="E3">
         <v>7.1</v>
@@ -3552,7 +3552,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.81</v>
+        <v>0.833</v>
       </c>
       <c r="D6">
         <v>21.4</v>
@@ -3574,7 +3574,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D7">
         <v>11.9</v>
@@ -3648,7 +3648,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>71.9</v>
+        <v>72.45</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -3657,7 +3657,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>86.67</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>4.0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>69.33</v>
+        <v>69.82</v>
       </c>
       <c r="D3">
         <v>11</v>
@@ -3686,7 +3686,7 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>73.33</v>
@@ -3695,7 +3695,7 @@
         <v>83.33</v>
       </c>
       <c r="I3">
-        <v>16.0</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>64.37</v>
+        <v>66.73</v>
       </c>
       <c r="D4">
         <v>9</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>60.0</v>
       </c>
       <c r="H4">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="I4">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -3732,13 +3732,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>63.67</v>
+        <v>64.02</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3747,13 +3747,13 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>53.33</v>
+        <v>80.0</v>
       </c>
       <c r="H5">
         <v>66.67</v>
       </c>
       <c r="I5">
-        <v>8.0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="6">
@@ -3761,13 +3761,13 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>63.55</v>
+      </c>
+      <c r="D6">
         <v>13</v>
-      </c>
-      <c r="C6">
-        <v>63.47</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -3776,13 +3776,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>80.0</v>
+        <v>86.67</v>
       </c>
       <c r="H6">
         <v>66.67</v>
       </c>
       <c r="I6">
-        <v>4.0</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>62.97</v>
+        <v>63.34</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>86.67</v>
+        <v>73.33</v>
       </c>
       <c r="H7">
         <v>66.67</v>
       </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="8">
@@ -3822,25 +3822,25 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>62.77</v>
+        <v>63.25</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H8">
         <v>66.67</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="9">
@@ -3848,13 +3848,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>62.77</v>
+        <v>62.67</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
         <v>66.67</v>
@@ -3877,13 +3877,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C10">
-        <v>62.67</v>
+        <v>62.47</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>66.67</v>
+        <v>53.33</v>
       </c>
       <c r="H10">
         <v>66.67</v>
@@ -3909,7 +3909,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>62.0</v>
+        <v>62.44</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -3918,7 +3918,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>60.0</v>
@@ -3927,7 +3927,7 @@
         <v>50.0</v>
       </c>
       <c r="I11">
-        <v>24.0</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>60.8</v>
+        <v>61.18</v>
       </c>
       <c r="D12">
         <v>8</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>53.33</v>
       </c>
       <c r="H12">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="I12">
-        <v>100.0</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C13">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="D13">
         <v>8</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G13">
         <v>53.33</v>
       </c>
       <c r="H13">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I13">
-        <v>16.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C14">
-        <v>59.7</v>
+        <v>60.71</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>66.67</v>
+        <v>60.0</v>
       </c>
       <c r="H14">
         <v>50.0</v>
       </c>
       <c r="I14">
-        <v>8.0</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>59.33</v>
+        <v>60.23</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="H15">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I15">
-        <v>32.0</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>58.67</v>
+        <v>59.73</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G16">
-        <v>73.33</v>
+        <v>80.0</v>
       </c>
       <c r="H16">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I16">
-        <v>56.0</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C17">
-        <v>58.43</v>
+        <v>58.98</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>46.67</v>
+        <v>60.0</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I17">
-        <v>52.0</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="18">
@@ -4109,10 +4109,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C18">
-        <v>58.4</v>
+        <v>58.98</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -4121,7 +4121,7 @@
         <v>3</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>60.0</v>
@@ -4130,7 +4130,7 @@
         <v>50.0</v>
       </c>
       <c r="I18">
-        <v>0.0</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="19">
@@ -4138,13 +4138,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H19">
         <v>50.0</v>
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>57.23</v>
+        <v>55.95</v>
       </c>
       <c r="D20">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="F20">
-        <v>4</v>
-      </c>
       <c r="G20">
-        <v>100.0</v>
+        <v>46.67</v>
       </c>
       <c r="H20">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I20">
-        <v>16.0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="21">
@@ -4196,10 +4196,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21">
-        <v>55.4</v>
+        <v>54.8</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>46.67</v>
@@ -4217,7 +4217,7 @@
         <v>50.0</v>
       </c>
       <c r="I21">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>55.4</v>
+        <v>54.67</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G22">
         <v>46.67</v>
       </c>
       <c r="H22">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I22">
-        <v>4.0</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C23">
-        <v>54.23</v>
+        <v>53.55</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>46.67</v>
+        <v>100.0</v>
       </c>
       <c r="H23">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I23">
-        <v>24.0</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="24">
@@ -4286,7 +4286,7 @@
         <v>32</v>
       </c>
       <c r="C24">
-        <v>53.03</v>
+        <v>53.52</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -4295,7 +4295,7 @@
         <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>46.67</v>
@@ -4304,7 +4304,7 @@
         <v>33.33</v>
       </c>
       <c r="I24">
-        <v>16.0</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C25">
-        <v>52.43</v>
+        <v>52.57</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25">
-        <v>46.67</v>
+        <v>73.33</v>
       </c>
       <c r="H25">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I25">
-        <v>12.0</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>52.17</v>
+        <v>51.35</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>80.0</v>
+        <v>40.0</v>
       </c>
       <c r="H26">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I26">
-        <v>12.0</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>50.93</v>
+        <v>50.65</v>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>40.0</v>
       </c>
       <c r="H27">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I27">
-        <v>28.0</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C28">
-        <v>47.33</v>
+        <v>50.37</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>40.0</v>
+        <v>80.0</v>
       </c>
       <c r="H28">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I28">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>18</v>
       </c>
       <c r="C29">
-        <v>44.93</v>
+        <v>45.28</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -4440,7 +4440,7 @@
         <v>2</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <v>26.67</v>
@@ -4449,7 +4449,7 @@
         <v>33.33</v>
       </c>
       <c r="I29">
-        <v>40.0</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="30">
@@ -4460,7 +4460,7 @@
         <v>3</v>
       </c>
       <c r="C30">
-        <v>44.1</v>
+        <v>44.31</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4469,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30">
         <v>33.33</v>
@@ -4478,7 +4478,7 @@
         <v>0.0</v>
       </c>
       <c r="I30">
-        <v>64.0</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <v>43.86</v>
+      </c>
+      <c r="D31">
         <v>5</v>
       </c>
-      <c r="C31">
-        <v>43.73</v>
-      </c>
-      <c r="D31">
-        <v>4</v>
-      </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31">
-        <v>26.67</v>
+        <v>33.33</v>
       </c>
       <c r="H31">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I31">
-        <v>32.0</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>43.47</v>
+        <v>40.99</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G32">
-        <v>33.33</v>
+        <v>26.67</v>
       </c>
       <c r="H32">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I32">
-        <v>32.0</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>41.67</v>
+        <v>40.66</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33">
+        <v>26.67</v>
+      </c>
+      <c r="H33">
         <v>33.33</v>
       </c>
-      <c r="H33">
-        <v>16.67</v>
-      </c>
       <c r="I33">
-        <v>20.0</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C34">
-        <v>40.8</v>
+        <v>39.96</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G34">
         <v>26.67</v>
       </c>
       <c r="H34">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I34">
-        <v>68.0</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C35">
-        <v>40.47</v>
+        <v>38.95</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G35">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="H35">
         <v>16.67</v>
       </c>
       <c r="I35">
-        <v>12.0</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C36">
-        <v>40.13</v>
+        <v>38.81</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G36">
         <v>26.67</v>
       </c>
       <c r="H36">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I36">
-        <v>8.0</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C37">
-        <v>38.67</v>
+        <v>38.23</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G37">
-        <v>20.0</v>
+        <v>26.67</v>
       </c>
       <c r="H37">
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>52.0</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="38">
@@ -4689,10 +4689,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C38">
-        <v>38.37</v>
+        <v>37.08</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -4701,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <v>26.67</v>
@@ -4710,7 +4710,7 @@
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>24.0</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>32.37</v>
+        <v>32.74</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>13.33</v>
@@ -4739,7 +4739,7 @@
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>36.0</v>
+        <v>38.46</v>
       </c>
     </row>
   </sheetData>
@@ -4798,30 +4798,30 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>17</v>
+      </c>
+      <c r="F2">
         <v>19</v>
       </c>
-      <c r="D2">
-        <v>22</v>
-      </c>
-      <c r="E2">
-        <v>28</v>
-      </c>
-      <c r="F2">
-        <v>31</v>
-      </c>
       <c r="G2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -4829,30 +4829,30 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -4860,24 +4860,24 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>13</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4">
         <v>29</v>
@@ -4886,97 +4886,97 @@
         <v>31</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
         <v>23</v>
       </c>
-      <c r="E5">
-        <v>25</v>
-      </c>
-      <c r="F5">
+      <c r="G5">
         <v>29</v>
       </c>
-      <c r="G5">
-        <v>34</v>
-      </c>
       <c r="H5">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
         <v>29</v>
       </c>
-      <c r="F6">
-        <v>32</v>
-      </c>
       <c r="G6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>35</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -4984,402 +4984,402 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H10">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
         <v>6</v>
       </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
       <c r="E11">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G12">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H12">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>9</v>
+      </c>
+      <c r="F14">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>18</v>
+      </c>
+      <c r="H14">
+        <v>23</v>
+      </c>
+      <c r="I14">
         <v>4</v>
-      </c>
-      <c r="D14">
-        <v>17</v>
-      </c>
-      <c r="E14">
-        <v>19</v>
-      </c>
-      <c r="F14">
-        <v>25</v>
-      </c>
-      <c r="G14">
-        <v>28</v>
-      </c>
-      <c r="H14">
-        <v>29</v>
-      </c>
-      <c r="I14">
-        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H16">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G17">
         <v>28</v>
       </c>
       <c r="H17">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G18">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H18">
         <v>35</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E19">
+        <v>9</v>
+      </c>
+      <c r="F19">
+        <v>15</v>
+      </c>
+      <c r="G19">
         <v>24</v>
       </c>
-      <c r="F19">
-        <v>31</v>
-      </c>
-      <c r="G19">
-        <v>34</v>
-      </c>
       <c r="H19">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G20">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H20">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I20">
         <v>3</v>
@@ -5387,554 +5387,554 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H21">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G22">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H22">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G23">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H23">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G24">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H24">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E25">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F25">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G25">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H25">
         <v>38</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E26">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H26">
         <v>38</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G27">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H27">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>13</v>
+      </c>
+      <c r="F28">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>27</v>
+      </c>
+      <c r="H28">
+        <v>30</v>
+      </c>
+      <c r="I28">
         <v>8</v>
-      </c>
-      <c r="E28">
-        <v>27</v>
-      </c>
-      <c r="F28">
-        <v>33</v>
-      </c>
-      <c r="G28">
-        <v>35</v>
-      </c>
-      <c r="H28">
-        <v>38</v>
-      </c>
-      <c r="I28">
-        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D29">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F29">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G29">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H29">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F30">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G30">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H30">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G31">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H31">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G32">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H32">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F33">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G33">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H33">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F34">
         <v>27</v>
       </c>
       <c r="G34">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H34">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C35">
         <v>5</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F35">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G35">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E36">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F36">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G36">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H36">
         <v>34</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
         <v>13</v>
       </c>
-      <c r="D37">
-        <v>14</v>
-      </c>
       <c r="E37">
+        <v>21</v>
+      </c>
+      <c r="F37">
         <v>22</v>
       </c>
-      <c r="F37">
-        <v>28</v>
-      </c>
       <c r="G37">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H37">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F38">
         <v>28</v>
       </c>
       <c r="G38">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H38">
         <v>38</v>
@@ -5945,58 +5945,58 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
         <v>9</v>
       </c>
-      <c r="D39">
-        <v>13</v>
-      </c>
       <c r="E39">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F39">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G39">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H39">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C40">
+        <v>9</v>
+      </c>
+      <c r="D40">
+        <v>13</v>
+      </c>
+      <c r="E40">
         <v>14</v>
       </c>
-      <c r="D40">
-        <v>26</v>
-      </c>
-      <c r="E40">
-        <v>28</v>
-      </c>
       <c r="F40">
+        <v>18</v>
+      </c>
+      <c r="G40">
         <v>31</v>
-      </c>
-      <c r="G40">
-        <v>32</v>
       </c>
       <c r="H40">
         <v>34</v>
@@ -6007,61 +6007,61 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G41">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H41">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F42">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G42">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H42">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I42">
         <v>8</v>
@@ -6069,15 +6069,15 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>11</v>
@@ -6086,106 +6086,106 @@
         <v>14</v>
       </c>
       <c r="F43">
+        <v>17</v>
+      </c>
+      <c r="G43">
+        <v>29</v>
+      </c>
+      <c r="H43">
         <v>32</v>
       </c>
-      <c r="G43">
-        <v>36</v>
-      </c>
-      <c r="H43">
-        <v>38</v>
-      </c>
       <c r="I43">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C44">
         <v>7</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F44">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G44">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H44">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000017</v>
+        <v>115000018</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E45">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F45">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G45">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H45">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I45">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000016</v>
+        <v>115000017</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F46">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G46">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H46">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I46">
         <v>2</v>
@@ -6193,92 +6193,92 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000015</v>
+        <v>115000016</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C47">
+        <v>4</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47">
+        <v>13</v>
+      </c>
+      <c r="F47">
+        <v>24</v>
+      </c>
+      <c r="G47">
+        <v>31</v>
+      </c>
+      <c r="H47">
+        <v>35</v>
+      </c>
+      <c r="I47">
         <v>2</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47">
-        <v>6</v>
-      </c>
-      <c r="F47">
-        <v>12</v>
-      </c>
-      <c r="G47">
-        <v>23</v>
-      </c>
-      <c r="H47">
-        <v>27</v>
-      </c>
-      <c r="I47">
-        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000014</v>
+        <v>115000015</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
         <v>6</v>
       </c>
-      <c r="E48">
-        <v>19</v>
-      </c>
       <c r="F48">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G48">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H48">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000013</v>
+        <v>115000014</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
         <v>6</v>
       </c>
-      <c r="D49">
-        <v>10</v>
-      </c>
       <c r="E49">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F49">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G49">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H49">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I49">
         <v>3</v>
@@ -6286,64 +6286,64 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000012</v>
+        <v>115000013</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E50">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F50">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G50">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H50">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000011</v>
+        <v>115000012</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D51">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F51">
+        <v>33</v>
+      </c>
+      <c r="G51">
         <v>34</v>
-      </c>
-      <c r="G51">
-        <v>36</v>
       </c>
       <c r="H51">
         <v>37</v>
       </c>
       <c r="I51">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-07-28 第 115000074 期；威力彩 2026-07-30 第 115000061 期</t>
+          <t>大樂透 2026-07-31 第 115000075 期；威力彩 2026-07-30 第 115000061 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15, 16, 18, 19, 29, 34</t>
+          <t>11, 15, 16, 19, 29, 34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.072 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.048 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,7 +214,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.762</v>
+        <v>0.738</v>
       </c>
       <c r="D2">
         <v>16.7</v>
@@ -236,7 +236,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.738</v>
+        <v>0.714</v>
       </c>
       <c r="D3">
         <v>14.3</v>
@@ -398,7 +398,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>77.77</v>
+        <v>78.15</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>15.15</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>71.67</v>
+        <v>73.85</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>15.15</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>69.95</v>
@@ -482,13 +482,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>69.3</v>
+        <v>69.84</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -497,13 +497,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>68.15</v>
+        <v>69.73</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>3.03</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>68.13</v>
+        <v>68.48</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -552,7 +552,7 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>90.0</v>
@@ -561,7 +561,7 @@
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>67.58</v>
+        <v>67.6</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>21.21</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>67.22</v>
+        <v>67.05</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>90.0</v>
+        <v>80.0</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>15.15</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>67.03</v>
+        <v>66.71</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>21.21</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C11">
-        <v>66.86</v>
+        <v>65.39</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>100.0</v>
+        <v>90.0</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>9.09</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C12">
-        <v>64.95</v>
+        <v>64.91</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="13">
@@ -714,10 +714,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>64.52</v>
+        <v>64.46</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C14">
-        <v>64.06</v>
+        <v>64.4</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="H14">
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>9.09</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C15">
-        <v>63.85</v>
+        <v>63.58</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="F15">
-        <v>11</v>
-      </c>
       <c r="G15">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="H15">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I15">
-        <v>33.33</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="16">
@@ -801,10 +801,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>63.15</v>
+        <v>63.14</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -822,7 +822,7 @@
         <v>60.0</v>
       </c>
       <c r="I16">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C17">
-        <v>62.7</v>
+        <v>62.99</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>60.0</v>
       </c>
       <c r="H17">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I17">
-        <v>0.0</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="18">
@@ -859,10 +859,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C18">
-        <v>62.03</v>
+        <v>62.38</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>70.0</v>
@@ -880,7 +880,7 @@
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C19">
-        <v>61.77</v>
+        <v>61.61</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>90.0</v>
+        <v>80.0</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>12.12</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C20">
-        <v>61.22</v>
+        <v>61.5</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>12.12</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="21">
@@ -946,10 +946,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>61.12</v>
+        <v>61.06</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -967,7 +967,7 @@
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>15.15</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="22">
@@ -975,10 +975,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>60.67</v>
+        <v>60.61</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -996,7 +996,7 @@
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C23">
-        <v>60.21</v>
+        <v>59.69</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G23">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I23">
-        <v>9.09</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C24">
-        <v>60.21</v>
+        <v>58.48</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="H24">
         <v>20.0</v>
       </c>
       <c r="I24">
-        <v>42.42</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C25">
-        <v>59.4</v>
+        <v>57.7</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I25">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C26">
-        <v>58.13</v>
+        <v>57.7</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I26">
-        <v>21.21</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>57.94</v>
+        <v>57.25</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G27">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
         <v>0.0</v>
       </c>
       <c r="I27">
-        <v>60.61</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>57.16</v>
+      </c>
+      <c r="D28">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
         <v>5</v>
       </c>
-      <c r="C28">
-        <v>57.25</v>
-      </c>
-      <c r="D28">
-        <v>5</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>33</v>
-      </c>
       <c r="G28">
-        <v>50.0</v>
+        <v>90.0</v>
       </c>
       <c r="H28">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I28">
-        <v>100.0</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C29">
-        <v>56.12</v>
+        <v>56.96</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G29">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="H29">
         <v>0.0</v>
       </c>
       <c r="I29">
-        <v>48.48</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>55.21</v>
+        <v>56.35</v>
       </c>
       <c r="D30">
         <v>7</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G30">
         <v>70.0</v>
       </c>
       <c r="H30">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30">
-        <v>9.09</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>54.98</v>
+        <v>55.61</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="H31">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I31">
-        <v>18.18</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C32">
-        <v>53.85</v>
+        <v>55.47</v>
       </c>
       <c r="D32">
         <v>7</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G32">
         <v>70.0</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
+        <v>43</v>
+      </c>
+      <c r="C33">
+        <v>54.29</v>
+      </c>
+      <c r="D33">
         <v>7</v>
       </c>
-      <c r="C33">
-        <v>53.61</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="H33">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I33">
-        <v>75.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>53.16</v>
+        <v>53.72</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G34">
         <v>50.0</v>
       </c>
       <c r="H34">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34">
-        <v>39.39</v>
+        <v>76.47</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C35">
-        <v>53.15</v>
+        <v>52.25</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="H35">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I35">
-        <v>3.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>52.71</v>
+        <v>50.34</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="H36">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I36">
-        <v>6.06</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="37">
@@ -1410,10 +1410,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>51.8</v>
+        <v>49.01</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>50.0</v>
@@ -1431,7 +1431,7 @@
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>30.3</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="38">
@@ -1439,10 +1439,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C38">
-        <v>48.61</v>
+        <v>48.13</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38">
         <v>50.0</v>
@@ -1460,7 +1460,7 @@
         <v>20.0</v>
       </c>
       <c r="I38">
-        <v>9.09</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="39">
@@ -1471,7 +1471,7 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>47.71</v>
+        <v>48.12</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -1480,7 +1480,7 @@
         <v>2</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39">
         <v>40.0</v>
@@ -1489,7 +1489,7 @@
         <v>40.0</v>
       </c>
       <c r="I39">
-        <v>6.06</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="40">
@@ -1497,10 +1497,10 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C40">
-        <v>46.8</v>
+        <v>48.12</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1509,7 +1509,7 @@
         <v>2</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G40">
         <v>40.0</v>
@@ -1518,7 +1518,7 @@
         <v>40.0</v>
       </c>
       <c r="I40">
-        <v>0.0</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C41">
-        <v>45.89</v>
+        <v>47.24</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <v>40.0</v>
       </c>
       <c r="H41">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I41">
-        <v>60.61</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C42">
-        <v>42.25</v>
+        <v>46.06</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G42">
         <v>40.0</v>
       </c>
       <c r="H42">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I42">
-        <v>3.03</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C43">
-        <v>41.8</v>
+        <v>42.24</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H43">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I43">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="44">
@@ -1613,28 +1613,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>41.8</v>
+        <v>42.23</v>
       </c>
       <c r="D44">
         <v>3</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G44">
         <v>30.0</v>
       </c>
       <c r="H44">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I44">
-        <v>36.36</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C45">
-        <v>41.8</v>
+        <v>42.09</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G45">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H45">
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>0.0</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>41</v>
       </c>
       <c r="C46">
-        <v>40.44</v>
+        <v>40.76</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <v>30.0</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>27.27</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>21</v>
       </c>
       <c r="C47">
-        <v>39.99</v>
+        <v>40.17</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47">
         <v>30.0</v>
@@ -1721,7 +1721,7 @@
         <v>0.0</v>
       </c>
       <c r="I47">
-        <v>57.58</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="C48">
-        <v>39.08</v>
+        <v>39.44</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G48">
         <v>30.0</v>
@@ -1750,7 +1750,7 @@
         <v>20.0</v>
       </c>
       <c r="I48">
-        <v>18.18</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>30</v>
       </c>
       <c r="C49">
-        <v>38.17</v>
+        <v>38.41</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49">
         <v>30.0</v>
@@ -1779,7 +1779,7 @@
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>45.45</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="50">
@@ -1790,25 +1790,25 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>33.63</v>
+        <v>28.39</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G50">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H50">
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>51.52</v>
+        <v>52.94</v>
       </c>
     </row>
   </sheetData>
@@ -1867,204 +1867,204 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I2">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I3">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G4">
         <v>35</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H7">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -2073,345 +2073,345 @@
         <v>18</v>
       </c>
       <c r="G8">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>18</v>
+      </c>
+      <c r="G9">
         <v>19</v>
       </c>
-      <c r="F9">
-        <v>23</v>
-      </c>
-      <c r="G9">
-        <v>39</v>
-      </c>
       <c r="H9">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G10">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H10">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I10">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H11">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12">
+        <v>23</v>
+      </c>
+      <c r="F12">
+        <v>24</v>
+      </c>
+      <c r="G12">
         <v>29</v>
       </c>
-      <c r="F12">
-        <v>33</v>
-      </c>
-      <c r="G12">
-        <v>34</v>
-      </c>
       <c r="H12">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I12">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G13">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I13">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I14">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H15">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G16">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H16">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I16">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>25</v>
       </c>
       <c r="F17">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G17">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I17">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H18">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>9</v>
+      </c>
+      <c r="E19">
+        <v>16</v>
+      </c>
+      <c r="F19">
         <v>20</v>
-      </c>
-      <c r="D19">
-        <v>26</v>
-      </c>
-      <c r="E19">
-        <v>29</v>
-      </c>
-      <c r="F19">
-        <v>31</v>
       </c>
       <c r="G19">
         <v>37</v>
@@ -2420,810 +2420,810 @@
         <v>49</v>
       </c>
       <c r="I19">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D20">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20">
         <v>29</v>
       </c>
       <c r="F20">
+        <v>31</v>
+      </c>
+      <c r="G20">
         <v>37</v>
       </c>
-      <c r="G20">
-        <v>47</v>
-      </c>
       <c r="H20">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I20">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E21">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G21">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H21">
         <v>48</v>
       </c>
       <c r="I21">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D22">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G22">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H22">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I22">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G23">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H23">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F24">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G24">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H24">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I24">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D25">
+        <v>12</v>
+      </c>
+      <c r="E25">
         <v>18</v>
       </c>
-      <c r="E25">
-        <v>25</v>
-      </c>
       <c r="F25">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G25">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H25">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I25">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F26">
         <v>28</v>
       </c>
       <c r="G26">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H26">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I26">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E27">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G27">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H27">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I27">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G28">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H28">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29">
+        <v>14</v>
+      </c>
+      <c r="F29">
+        <v>25</v>
+      </c>
+      <c r="G29">
+        <v>26</v>
+      </c>
+      <c r="H29">
+        <v>32</v>
+      </c>
+      <c r="I29">
         <v>7</v>
-      </c>
-      <c r="D29">
-        <v>14</v>
-      </c>
-      <c r="E29">
-        <v>16</v>
-      </c>
-      <c r="F29">
-        <v>37</v>
-      </c>
-      <c r="G29">
-        <v>39</v>
-      </c>
-      <c r="H29">
-        <v>47</v>
-      </c>
-      <c r="I29">
-        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G30">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H30">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I30">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F31">
+        <v>19</v>
+      </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+      <c r="H31">
+        <v>40</v>
+      </c>
+      <c r="I31">
         <v>22</v>
-      </c>
-      <c r="G31">
-        <v>40</v>
-      </c>
-      <c r="H31">
-        <v>45</v>
-      </c>
-      <c r="I31">
-        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G32">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H32">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I32">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C33">
         <v>4</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F33">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G33">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H33">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I33">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G34">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H34">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I34">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G35">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H35">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I35">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C36">
         <v>5</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E36">
+        <v>13</v>
+      </c>
+      <c r="F36">
         <v>25</v>
       </c>
-      <c r="F36">
-        <v>40</v>
-      </c>
       <c r="G36">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H36">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I36">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F37">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G37">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H37">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I37">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C38">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F38">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G38">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H38">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I38">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C39">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D39">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E39">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F39">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G39">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H39">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I39">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E40">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F40">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G40">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H40">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I40">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F41">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G41">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H41">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C42">
         <v>5</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E42">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F42">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G42">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H42">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>11</v>
       </c>
       <c r="E43">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F43">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G43">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H43">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I43">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D44">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E44">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F44">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G44">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H44">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I44">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C45">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E45">
         <v>27</v>
       </c>
       <c r="F45">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G45">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H45">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I45">
         <v>37</v>
@@ -3231,30 +3231,30 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D46">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E46">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F46">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G46">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H46">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I46">
         <v>37</v>
@@ -3262,157 +3262,157 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C47">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E47">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F47">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G47">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H47">
         <v>49</v>
       </c>
       <c r="I47">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C48">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D48">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E48">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F48">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G48">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H48">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I48">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E49">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F49">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G49">
+        <v>45</v>
+      </c>
+      <c r="H49">
         <v>47</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>48</v>
-      </c>
-      <c r="I49">
-        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E50">
         <v>22</v>
       </c>
       <c r="F50">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G50">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I50">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E51">
         <v>22</v>
       </c>
       <c r="F51">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G51">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H51">
+        <v>49</v>
+      </c>
+      <c r="I51">
         <v>31</v>
-      </c>
-      <c r="I51">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-07-31 第 115000075 期；威力彩 2026-07-30 第 115000061 期</t>
+          <t>大樂透 2026-07-31 第 115000075 期；威力彩 2026-08-03 第 115000062 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -152,7 +152,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.547 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.476 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,13 +3464,13 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.19</v>
+        <v>1.119</v>
       </c>
       <c r="D2">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="E2">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -3486,13 +3486,13 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.19</v>
+        <v>1.119</v>
       </c>
       <c r="D3">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="E3">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3552,7 +3552,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="D6">
         <v>21.4</v>
@@ -3648,7 +3648,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>72.45</v>
+        <v>72.97</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -3657,7 +3657,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>86.67</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>7.69</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="3">
@@ -3677,25 +3677,25 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>69.82</v>
+        <v>66.1</v>
       </c>
       <c r="D3">
         <v>11</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>73.33</v>
       </c>
       <c r="H3">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="I3">
-        <v>19.23</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>66.73</v>
+        <v>64.43</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>60.0</v>
+        <v>73.33</v>
       </c>
       <c r="H4">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="5">
@@ -3732,13 +3732,13 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>64.08</v>
+      </c>
+      <c r="D5">
         <v>13</v>
-      </c>
-      <c r="C5">
-        <v>64.02</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3747,13 +3747,13 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>80.0</v>
+        <v>86.67</v>
       </c>
       <c r="H5">
         <v>66.67</v>
       </c>
       <c r="I5">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C6">
-        <v>63.55</v>
+        <v>63.88</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>86.67</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
         <v>66.67</v>
       </c>
       <c r="I6">
-        <v>3.85</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="7">
@@ -3790,13 +3790,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>63.34</v>
+        <v>63.22</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -3805,13 +3805,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H7">
         <v>66.67</v>
       </c>
       <c r="I7">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8">
@@ -3819,13 +3819,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>63.25</v>
+        <v>63.12</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -3834,13 +3834,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>66.67</v>
+        <v>60.0</v>
       </c>
       <c r="H8">
         <v>66.67</v>
       </c>
       <c r="I8">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>62.67</v>
+        <v>63.02</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>4</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>66.67</v>
+        <v>53.33</v>
       </c>
       <c r="H9">
         <v>66.67</v>
       </c>
       <c r="I9">
-        <v>0.0</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -3877,13 +3877,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>62.47</v>
+        <v>62.77</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>53.33</v>
+        <v>73.33</v>
       </c>
       <c r="H10">
         <v>66.67</v>
@@ -3909,25 +3909,25 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>62.44</v>
+        <v>62.67</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>60.0</v>
+        <v>66.67</v>
       </c>
       <c r="H11">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="I11">
-        <v>26.92</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -3938,7 +3938,7 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>61.18</v>
+        <v>61.63</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -3947,7 +3947,7 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>53.33</v>
@@ -3956,7 +3956,7 @@
         <v>50.0</v>
       </c>
       <c r="I12">
-        <v>19.23</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>60.8</v>
+        <v>61.18</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>53.33</v>
+        <v>60.0</v>
       </c>
       <c r="H13">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="I13">
-        <v>100.0</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14">
-        <v>60.71</v>
+        <v>60.8</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G14">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H14">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I14">
-        <v>15.38</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="15">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>60.23</v>
+        <v>60.72</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -4034,7 +4034,7 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15">
         <v>66.67</v>
@@ -4043,7 +4043,7 @@
         <v>50.0</v>
       </c>
       <c r="I15">
-        <v>11.54</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="16">
@@ -4054,7 +4054,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>59.73</v>
+        <v>60.09</v>
       </c>
       <c r="D16">
         <v>12</v>
@@ -4063,7 +4063,7 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>80.0</v>
@@ -4072,7 +4072,7 @@
         <v>33.33</v>
       </c>
       <c r="I16">
-        <v>34.62</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="17">
@@ -4083,7 +4083,7 @@
         <v>28</v>
       </c>
       <c r="C17">
-        <v>58.98</v>
+        <v>59.51</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -4092,7 +4092,7 @@
         <v>3</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17">
         <v>60.0</v>
@@ -4101,7 +4101,7 @@
         <v>50.0</v>
       </c>
       <c r="I17">
-        <v>3.85</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="18">
@@ -4109,13 +4109,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C18">
-        <v>58.98</v>
+        <v>58.85</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -4124,13 +4124,13 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H18">
         <v>50.0</v>
       </c>
       <c r="I18">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -4138,7 +4138,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>58.3</v>
@@ -4170,7 +4170,7 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>55.95</v>
+        <v>56.47</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -4179,7 +4179,7 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>46.67</v>
@@ -4188,7 +4188,7 @@
         <v>50.0</v>
       </c>
       <c r="I20">
-        <v>7.69</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="21">
@@ -4199,7 +4199,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>54.8</v>
+        <v>55.36</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>46.67</v>
@@ -4217,7 +4217,7 @@
         <v>50.0</v>
       </c>
       <c r="I21">
-        <v>0.0</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C22">
-        <v>54.67</v>
+        <v>55.24</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>46.67</v>
+        <v>53.33</v>
       </c>
       <c r="H22">
         <v>33.33</v>
       </c>
       <c r="I22">
-        <v>26.92</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C23">
-        <v>53.55</v>
+        <v>54.43</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>100.0</v>
+        <v>73.33</v>
       </c>
       <c r="H23">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I23">
-        <v>19.23</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24">
-        <v>53.52</v>
+        <v>54.0</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>46.67</v>
+        <v>100.0</v>
       </c>
       <c r="H24">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I24">
-        <v>19.23</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25">
-        <v>52.57</v>
+        <v>53.97</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>73.33</v>
+        <v>46.67</v>
       </c>
       <c r="H25">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I25">
-        <v>15.38</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="26">
@@ -4344,7 +4344,7 @@
         <v>2</v>
       </c>
       <c r="C26">
-        <v>51.35</v>
+        <v>51.73</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -4353,7 +4353,7 @@
         <v>2</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G26">
         <v>40.0</v>
@@ -4362,7 +4362,7 @@
         <v>33.33</v>
       </c>
       <c r="I26">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C27">
-        <v>50.65</v>
+        <v>50.82</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>40.0</v>
+        <v>73.33</v>
       </c>
       <c r="H27">
         <v>16.67</v>
       </c>
       <c r="I27">
-        <v>53.85</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C28">
-        <v>50.37</v>
+        <v>46.73</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>80.0</v>
+        <v>40.0</v>
       </c>
       <c r="H28">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I28">
-        <v>0.0</v>
+        <v>55.56</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>18</v>
       </c>
       <c r="C29">
-        <v>45.28</v>
+        <v>45.6</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -4440,7 +4440,7 @@
         <v>2</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>26.67</v>
@@ -4449,7 +4449,7 @@
         <v>33.33</v>
       </c>
       <c r="I29">
-        <v>42.31</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="30">
@@ -4460,7 +4460,7 @@
         <v>3</v>
       </c>
       <c r="C30">
-        <v>44.31</v>
+        <v>44.5</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4469,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G30">
         <v>33.33</v>
@@ -4478,7 +4478,7 @@
         <v>0.0</v>
       </c>
       <c r="I30">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C31">
-        <v>43.86</v>
+        <v>42.83</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>33.33</v>
       </c>
       <c r="H31">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I31">
-        <v>34.62</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -4518,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="C32">
-        <v>40.99</v>
+        <v>41.16</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32">
         <v>26.67</v>
@@ -4536,7 +4536,7 @@
         <v>0.0</v>
       </c>
       <c r="I32">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>40.66</v>
+        <v>41.16</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -4556,7 +4556,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33">
         <v>26.67</v>
@@ -4565,7 +4565,7 @@
         <v>33.33</v>
       </c>
       <c r="I33">
-        <v>11.54</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="34">
@@ -4576,7 +4576,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>39.96</v>
+        <v>40.32</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34">
         <v>26.67</v>
@@ -4594,7 +4594,7 @@
         <v>16.67</v>
       </c>
       <c r="I34">
-        <v>34.62</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>38.95</v>
+        <v>40.32</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>20.0</v>
+        <v>26.67</v>
       </c>
       <c r="H35">
         <v>16.67</v>
       </c>
       <c r="I35">
-        <v>53.85</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="36">
@@ -4634,7 +4634,7 @@
         <v>30</v>
       </c>
       <c r="C36">
-        <v>38.81</v>
+        <v>39.21</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36">
         <v>26.67</v>
@@ -4652,7 +4652,7 @@
         <v>16.67</v>
       </c>
       <c r="I36">
-        <v>26.92</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="37">
@@ -4660,10 +4660,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C37">
-        <v>38.23</v>
+        <v>34.77</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>26.67</v>
@@ -4681,7 +4681,7 @@
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>23.08</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38">
-        <v>37.08</v>
+        <v>34.76</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G38">
-        <v>26.67</v>
+        <v>20.0</v>
       </c>
       <c r="H38">
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>15.38</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>32.74</v>
+        <v>33.08</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39">
         <v>13.33</v>
@@ -4739,7 +4739,7 @@
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
     </row>
   </sheetData>
@@ -4798,30 +4798,30 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I2">
         <v>7</v>
@@ -4829,30 +4829,30 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>17</v>
+      </c>
+      <c r="F3">
         <v>19</v>
       </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>28</v>
-      </c>
-      <c r="F3">
-        <v>31</v>
-      </c>
       <c r="G3">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -4860,30 +4860,30 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -4891,24 +4891,24 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>13</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5">
         <v>29</v>
@@ -4917,97 +4917,97 @@
         <v>31</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
         <v>23</v>
       </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
+      <c r="G6">
         <v>29</v>
       </c>
-      <c r="G6">
-        <v>34</v>
-      </c>
       <c r="H6">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
         <v>29</v>
       </c>
-      <c r="F7">
-        <v>32</v>
-      </c>
       <c r="G7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>35</v>
       </c>
       <c r="H8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -5015,402 +5015,402 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
         <v>6</v>
       </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
       <c r="E12">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G13">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H13">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>23</v>
+      </c>
+      <c r="I15">
         <v>4</v>
-      </c>
-      <c r="D15">
-        <v>17</v>
-      </c>
-      <c r="E15">
-        <v>19</v>
-      </c>
-      <c r="F15">
-        <v>25</v>
-      </c>
-      <c r="G15">
-        <v>28</v>
-      </c>
-      <c r="H15">
-        <v>29</v>
-      </c>
-      <c r="I15">
-        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H16">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H17">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <v>28</v>
       </c>
       <c r="H18">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G19">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H19">
         <v>35</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E20">
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <v>15</v>
+      </c>
+      <c r="G20">
         <v>24</v>
       </c>
-      <c r="F20">
-        <v>31</v>
-      </c>
-      <c r="G20">
-        <v>34</v>
-      </c>
       <c r="H20">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G21">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H21">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I21">
         <v>3</v>
@@ -5418,554 +5418,554 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H22">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G23">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H23">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F24">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H24">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C25">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G25">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H25">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G26">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H26">
         <v>38</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H27">
         <v>38</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E28">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G28">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I28">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>13</v>
+      </c>
+      <c r="F29">
+        <v>19</v>
+      </c>
+      <c r="G29">
+        <v>27</v>
+      </c>
+      <c r="H29">
+        <v>30</v>
+      </c>
+      <c r="I29">
         <v>8</v>
-      </c>
-      <c r="E29">
-        <v>27</v>
-      </c>
-      <c r="F29">
-        <v>33</v>
-      </c>
-      <c r="G29">
-        <v>35</v>
-      </c>
-      <c r="H29">
-        <v>38</v>
-      </c>
-      <c r="I29">
-        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G30">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H30">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G31">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H31">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I31">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G32">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H32">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G33">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H33">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F34">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G34">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H34">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F35">
         <v>27</v>
       </c>
       <c r="G35">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H35">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C36">
         <v>5</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F36">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G36">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E37">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G37">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H37">
         <v>34</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
         <v>13</v>
       </c>
-      <c r="D38">
-        <v>14</v>
-      </c>
       <c r="E38">
+        <v>21</v>
+      </c>
+      <c r="F38">
         <v>22</v>
       </c>
-      <c r="F38">
-        <v>28</v>
-      </c>
       <c r="G38">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F39">
         <v>28</v>
       </c>
       <c r="G39">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H39">
         <v>38</v>
@@ -5976,58 +5976,58 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
         <v>9</v>
       </c>
-      <c r="D40">
-        <v>13</v>
-      </c>
       <c r="E40">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F40">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G40">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H40">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C41">
+        <v>9</v>
+      </c>
+      <c r="D41">
+        <v>13</v>
+      </c>
+      <c r="E41">
         <v>14</v>
       </c>
-      <c r="D41">
-        <v>26</v>
-      </c>
-      <c r="E41">
-        <v>28</v>
-      </c>
       <c r="F41">
+        <v>18</v>
+      </c>
+      <c r="G41">
         <v>31</v>
-      </c>
-      <c r="G41">
-        <v>32</v>
       </c>
       <c r="H41">
         <v>34</v>
@@ -6038,61 +6038,61 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D42">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G42">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H42">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F43">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G43">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H43">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -6100,15 +6100,15 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>11</v>
@@ -6117,106 +6117,106 @@
         <v>14</v>
       </c>
       <c r="F44">
+        <v>17</v>
+      </c>
+      <c r="G44">
+        <v>29</v>
+      </c>
+      <c r="H44">
         <v>32</v>
       </c>
-      <c r="G44">
-        <v>36</v>
-      </c>
-      <c r="H44">
-        <v>38</v>
-      </c>
       <c r="I44">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C45">
         <v>7</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F45">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G45">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H45">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000017</v>
+        <v>115000018</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E46">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F46">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G46">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H46">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I46">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000016</v>
+        <v>115000017</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F47">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G47">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H47">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I47">
         <v>2</v>
@@ -6224,92 +6224,92 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000015</v>
+        <v>115000016</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48">
+        <v>13</v>
+      </c>
+      <c r="F48">
+        <v>24</v>
+      </c>
+      <c r="G48">
+        <v>31</v>
+      </c>
+      <c r="H48">
+        <v>35</v>
+      </c>
+      <c r="I48">
         <v>2</v>
-      </c>
-      <c r="D48">
-        <v>3</v>
-      </c>
-      <c r="E48">
-        <v>6</v>
-      </c>
-      <c r="F48">
-        <v>12</v>
-      </c>
-      <c r="G48">
-        <v>23</v>
-      </c>
-      <c r="H48">
-        <v>27</v>
-      </c>
-      <c r="I48">
-        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000014</v>
+        <v>115000015</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
         <v>6</v>
       </c>
-      <c r="E49">
-        <v>19</v>
-      </c>
       <c r="F49">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G49">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H49">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000013</v>
+        <v>115000014</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
         <v>6</v>
       </c>
-      <c r="D50">
-        <v>10</v>
-      </c>
       <c r="E50">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F50">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G50">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H50">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I50">
         <v>3</v>
@@ -6317,33 +6317,33 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000012</v>
+        <v>115000013</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C51">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E51">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F51">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G51">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H51">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-07-31 第 115000075 期；威力彩 2026-08-03 第 115000062 期</t>
+          <t>大樂透 2026-08-04 第 115000076 期；威力彩 2026-08-03 第 115000062 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11, 15, 16, 19, 29, 34</t>
+          <t>4, 11, 15, 19, 29, 34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.048 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.071 碼/期</t>
         </is>
       </c>
     </row>
@@ -251,29 +251,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>隨機基準</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B4">
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.69</v>
+        <v>0.667</v>
       </c>
       <c r="D4">
-        <v>9.5</v>
+        <v>19.0</v>
       </c>
       <c r="E4">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B5">
@@ -283,7 +283,7 @@
         <v>0.667</v>
       </c>
       <c r="D5">
-        <v>19.0</v>
+        <v>16.7</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -295,7 +295,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>隨機基準</t>
         </is>
       </c>
       <c r="B6">
@@ -305,13 +305,13 @@
         <v>0.667</v>
       </c>
       <c r="D6">
-        <v>16.7</v>
+        <v>9.5</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>0.0</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -324,7 +324,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D7">
         <v>11.9</v>
@@ -398,7 +398,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>78.15</v>
+        <v>78.5</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>17.65</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +424,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>73.85</v>
@@ -453,13 +453,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>69.95</v>
+        <v>70.5</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="H4">
         <v>80.0</v>
@@ -482,13 +482,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>69.84</v>
+        <v>70.38</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -497,13 +497,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>69.73</v>
+        <v>70.26</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -526,13 +526,13 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>5.88</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>68.48</v>
+        <v>69.28</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
       <c r="H7">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
-        <v>23.53</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>36</v>
+      </c>
+      <c r="C8">
+        <v>68.85</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="C8">
-        <v>67.6</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
       <c r="F8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
       <c r="H8">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I8">
-        <v>17.65</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>67.05</v>
+        <v>67.4</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -610,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>80.0</v>
@@ -619,7 +619,7 @@
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>17.65</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>66.71</v>
+        <v>67.09</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -639,7 +639,7 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>90.0</v>
@@ -648,7 +648,7 @@
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>11.76</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         <v>26</v>
       </c>
       <c r="C11">
-        <v>65.39</v>
+        <v>65.81</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -668,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>90.0</v>
@@ -677,7 +677,7 @@
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>2.94</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>64.91</v>
+        <v>64.83</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>14.71</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="13">
@@ -714,10 +714,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C13">
-        <v>64.46</v>
+        <v>63.99</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -726,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>60.0</v>
@@ -735,7 +735,7 @@
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>11.76</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>64.4</v>
+        <v>63.81</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="H14">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="15">
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>63.58</v>
+        <v>63.56</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -793,7 +793,7 @@
         <v>60.0</v>
       </c>
       <c r="I15">
-        <v>5.88</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C16">
-        <v>63.14</v>
+        <v>63.27</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>60.0</v>
       </c>
       <c r="H16">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I16">
-        <v>2.94</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C17">
-        <v>62.99</v>
+        <v>62.71</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>35.29</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="18">
@@ -859,10 +859,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>62.38</v>
+        <v>61.42</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>70.0</v>
@@ -880,7 +880,7 @@
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>23.53</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="19">
@@ -891,25 +891,25 @@
         <v>45</v>
       </c>
       <c r="C19">
-        <v>61.61</v>
+        <v>61.42</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>14.71</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20">
-        <v>61.5</v>
+        <v>59.97</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I20">
-        <v>17.65</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="21">
@@ -946,13 +946,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>61.06</v>
+        <v>59.84</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -961,13 +961,13 @@
         <v>5</v>
       </c>
       <c r="G21">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>14.71</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="22">
@@ -975,10 +975,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C22">
-        <v>60.61</v>
+        <v>58.85</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -987,7 +987,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>70.0</v>
@@ -996,7 +996,7 @@
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>11.76</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23">
-        <v>59.69</v>
+        <v>58.81</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="H23">
         <v>20.0</v>
       </c>
       <c r="I23">
-        <v>35.29</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C24">
-        <v>58.48</v>
+        <v>58.13</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>8</v>
-      </c>
       <c r="G24">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="H24">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I24">
-        <v>23.53</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C25">
-        <v>57.7</v>
+        <v>57.52</v>
       </c>
       <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
         <v>6</v>
       </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
       <c r="G25">
-        <v>60.0</v>
+        <v>90.0</v>
       </c>
       <c r="H25">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>57.7</v>
+        <v>57.25</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G26">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="H26">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C27">
-        <v>57.25</v>
+        <v>56.56</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G27">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="H27">
         <v>0.0</v>
       </c>
       <c r="I27">
-        <v>100.0</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="28">
@@ -1149,13 +1149,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>57.16</v>
+        <v>55.99</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1164,13 +1164,13 @@
         <v>5</v>
       </c>
       <c r="G28">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
       <c r="H28">
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>14.71</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C29">
-        <v>56.96</v>
+        <v>55.99</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="H29">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I29">
-        <v>61.76</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="30">
@@ -1207,10 +1207,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C30">
-        <v>56.35</v>
+        <v>55.71</v>
       </c>
       <c r="D30">
         <v>7</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G30">
         <v>70.0</v>
@@ -1228,7 +1228,7 @@
         <v>0.0</v>
       </c>
       <c r="I30">
-        <v>50.0</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="31">
@@ -1236,10 +1236,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C31">
-        <v>55.61</v>
+        <v>54.71</v>
       </c>
       <c r="D31">
         <v>7</v>
@@ -1248,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31">
         <v>70.0</v>
@@ -1257,7 +1257,7 @@
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>11.76</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C32">
-        <v>55.47</v>
+        <v>53.13</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="H32">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>44.12</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33">
-        <v>54.29</v>
+        <v>52.68</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="H33">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I33">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="34">
@@ -1323,10 +1323,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C34">
-        <v>53.72</v>
+        <v>51.68</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G34">
         <v>50.0</v>
@@ -1344,7 +1344,7 @@
         <v>0.0</v>
       </c>
       <c r="I34">
-        <v>76.47</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>52.25</v>
+        <v>50.68</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G35">
         <v>50.0</v>
       </c>
       <c r="H35">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="36">
@@ -1381,10 +1381,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C36">
-        <v>50.34</v>
+        <v>49.39</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>50.0</v>
@@ -1402,7 +1402,7 @@
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>20.59</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="37">
@@ -1410,10 +1410,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C37">
-        <v>49.01</v>
+        <v>48.54</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37">
         <v>50.0</v>
@@ -1431,7 +1431,7 @@
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>11.76</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>48.13</v>
+        <v>48.51</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I38">
-        <v>5.88</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="39">
@@ -1468,10 +1468,10 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C39">
-        <v>48.12</v>
+        <v>48.51</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -1480,7 +1480,7 @@
         <v>2</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
         <v>40.0</v>
@@ -1489,7 +1489,7 @@
         <v>40.0</v>
       </c>
       <c r="I39">
-        <v>8.82</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>48.12</v>
+        <v>48.37</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G40">
         <v>40.0</v>
       </c>
       <c r="H40">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I40">
-        <v>8.82</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="41">
@@ -1529,7 +1529,7 @@
         <v>24</v>
       </c>
       <c r="C41">
-        <v>47.24</v>
+        <v>47.66</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>2</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41">
         <v>40.0</v>
@@ -1547,7 +1547,7 @@
         <v>40.0</v>
       </c>
       <c r="I41">
-        <v>2.94</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>46.06</v>
+        <v>46.8</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
         <v>0</v>
-      </c>
-      <c r="F42">
-        <v>21</v>
       </c>
       <c r="G42">
         <v>40.0</v>
       </c>
       <c r="H42">
+        <v>40.0</v>
+      </c>
+      <c r="I42">
         <v>0.0</v>
-      </c>
-      <c r="I42">
-        <v>61.76</v>
       </c>
     </row>
     <row r="43">
@@ -1587,7 +1587,7 @@
         <v>32</v>
       </c>
       <c r="C43">
-        <v>42.24</v>
+        <v>42.66</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43">
         <v>40.0</v>
@@ -1605,7 +1605,7 @@
         <v>20.0</v>
       </c>
       <c r="I43">
-        <v>2.94</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>3</v>
       </c>
       <c r="C44">
-        <v>42.23</v>
+        <v>42.64</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1625,7 +1625,7 @@
         <v>2</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44">
         <v>30.0</v>
@@ -1634,7 +1634,7 @@
         <v>40.0</v>
       </c>
       <c r="I44">
-        <v>5.88</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C45">
-        <v>42.09</v>
+        <v>41.8</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H45">
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>38.24</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>41</v>
       </c>
       <c r="C46">
-        <v>40.76</v>
+        <v>41.06</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G46">
         <v>30.0</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>29.41</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="47">
@@ -1700,10 +1700,10 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="C47">
-        <v>40.17</v>
+        <v>40.78</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G47">
         <v>30.0</v>
@@ -1721,7 +1721,7 @@
         <v>0.0</v>
       </c>
       <c r="I47">
-        <v>58.82</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C48">
-        <v>39.44</v>
+        <v>40.35</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G48">
         <v>30.0</v>
       </c>
       <c r="H48">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I48">
-        <v>20.59</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C49">
-        <v>38.41</v>
+        <v>39.78</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G49">
         <v>30.0</v>
       </c>
       <c r="H49">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I49">
-        <v>47.06</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>28.39</v>
+        <v>28.59</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G50">
         <v>10.0</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>52.94</v>
+        <v>54.29</v>
       </c>
     </row>
   </sheetData>
@@ -1867,235 +1867,235 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I3">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G5">
         <v>35</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H7">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H8">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <v>15</v>
@@ -2104,345 +2104,345 @@
         <v>18</v>
       </c>
       <c r="G9">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I9">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <v>18</v>
+      </c>
+      <c r="G10">
         <v>19</v>
       </c>
-      <c r="F10">
-        <v>23</v>
-      </c>
-      <c r="G10">
-        <v>39</v>
-      </c>
       <c r="H10">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H11">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I11">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H12">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>24</v>
+      </c>
+      <c r="G13">
         <v>29</v>
       </c>
-      <c r="F13">
-        <v>33</v>
-      </c>
-      <c r="G13">
-        <v>34</v>
-      </c>
       <c r="H13">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H14">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I14">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G15">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I15">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H16">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G17">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H17">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I17">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>25</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G18">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I18">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H19">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C20">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <v>9</v>
+      </c>
+      <c r="E20">
+        <v>16</v>
+      </c>
+      <c r="F20">
         <v>20</v>
-      </c>
-      <c r="D20">
-        <v>26</v>
-      </c>
-      <c r="E20">
-        <v>29</v>
-      </c>
-      <c r="F20">
-        <v>31</v>
       </c>
       <c r="G20">
         <v>37</v>
@@ -2451,810 +2451,810 @@
         <v>49</v>
       </c>
       <c r="I20">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D21">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21">
         <v>29</v>
       </c>
       <c r="F21">
+        <v>31</v>
+      </c>
+      <c r="G21">
         <v>37</v>
       </c>
-      <c r="G21">
-        <v>47</v>
-      </c>
       <c r="H21">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I21">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G22">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H22">
         <v>48</v>
       </c>
       <c r="I22">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G23">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H23">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C24">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E24">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F24">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G24">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H24">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G25">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H25">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I25">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26">
+        <v>12</v>
+      </c>
+      <c r="E26">
         <v>18</v>
       </c>
-      <c r="E26">
-        <v>25</v>
-      </c>
       <c r="F26">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G26">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H26">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I26">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F27">
         <v>28</v>
       </c>
       <c r="G27">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H27">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I27">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G28">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H28">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I28">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F29">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G29">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H29">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I29">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C30">
+        <v>6</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30">
+        <v>14</v>
+      </c>
+      <c r="F30">
+        <v>25</v>
+      </c>
+      <c r="G30">
+        <v>26</v>
+      </c>
+      <c r="H30">
+        <v>32</v>
+      </c>
+      <c r="I30">
         <v>7</v>
-      </c>
-      <c r="D30">
-        <v>14</v>
-      </c>
-      <c r="E30">
-        <v>16</v>
-      </c>
-      <c r="F30">
-        <v>37</v>
-      </c>
-      <c r="G30">
-        <v>39</v>
-      </c>
-      <c r="H30">
-        <v>47</v>
-      </c>
-      <c r="I30">
-        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G31">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H31">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I31">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F32">
+        <v>19</v>
+      </c>
+      <c r="G32">
+        <v>20</v>
+      </c>
+      <c r="H32">
+        <v>40</v>
+      </c>
+      <c r="I32">
         <v>22</v>
-      </c>
-      <c r="G32">
-        <v>40</v>
-      </c>
-      <c r="H32">
-        <v>45</v>
-      </c>
-      <c r="I32">
-        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F33">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G33">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H33">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I33">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C34">
         <v>4</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F34">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G34">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H34">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I34">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H35">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I35">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G36">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H36">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C37">
         <v>5</v>
       </c>
       <c r="D37">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E37">
+        <v>13</v>
+      </c>
+      <c r="F37">
         <v>25</v>
       </c>
-      <c r="F37">
-        <v>40</v>
-      </c>
       <c r="G37">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H37">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I37">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E38">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F38">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G38">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H38">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I38">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G39">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H39">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I39">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E40">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F40">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G40">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H40">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I40">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E41">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F41">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G41">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H41">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I41">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G42">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H42">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C43">
         <v>5</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E43">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F43">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G43">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H43">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I43">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C44">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>11</v>
       </c>
       <c r="E44">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F44">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G44">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H44">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I44">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D45">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E45">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F45">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G45">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H45">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I45">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C46">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E46">
         <v>27</v>
       </c>
       <c r="F46">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G46">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H46">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I46">
         <v>37</v>
@@ -3262,30 +3262,30 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D47">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E47">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F47">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G47">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H47">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I47">
         <v>37</v>
@@ -3293,126 +3293,126 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E48">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F48">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G48">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H48">
         <v>49</v>
       </c>
       <c r="I48">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D49">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E49">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F49">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G49">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H49">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I49">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D50">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F50">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G50">
+        <v>45</v>
+      </c>
+      <c r="H50">
         <v>47</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>48</v>
-      </c>
-      <c r="I50">
-        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E51">
         <v>22</v>
       </c>
       <c r="F51">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G51">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H51">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I51">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-04 第 115000076 期；威力彩 2026-08-03 第 115000062 期</t>
+          <t>大樂透 2026-08-07 第 115000077 期；威力彩 2026-08-06 第 115000063 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 11, 15, 19, 29, 34</t>
+          <t>4, 12, 15, 19, 29, 34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.071 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.072 碼/期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.476 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.452 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,10 +214,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.738</v>
+        <v>0.762</v>
       </c>
       <c r="D2">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="E2">
         <v>0.0</v>
@@ -236,10 +236,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.714</v>
+        <v>0.738</v>
       </c>
       <c r="D3">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3">
         <v>0.0</v>
@@ -251,29 +251,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>隨機基準</t>
         </is>
       </c>
       <c r="B4">
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.667</v>
+        <v>0.69</v>
       </c>
       <c r="D4">
-        <v>19.0</v>
+        <v>9.5</v>
       </c>
       <c r="E4">
-        <v>2.4</v>
+        <v>0.0</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B5">
@@ -283,41 +283,41 @@
         <v>0.667</v>
       </c>
       <c r="D5">
-        <v>16.7</v>
+        <v>11.9</v>
       </c>
       <c r="E5">
-        <v>2.4</v>
+        <v>0.0</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>隨機基準</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D6">
-        <v>9.5</v>
+        <v>16.7</v>
       </c>
       <c r="E6">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B7">
@@ -327,13 +327,13 @@
         <v>0.643</v>
       </c>
       <c r="D7">
-        <v>11.9</v>
+        <v>14.3</v>
       </c>
       <c r="E7">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -398,7 +398,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>78.5</v>
+        <v>78.83</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>20.0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="3">
@@ -424,13 +424,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>73.85</v>
+        <v>74.95</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -439,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="H3">
         <v>100.0</v>
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>70.5</v>
+        <v>74.27</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>70.0</v>
+      </c>
+      <c r="H4">
         <v>100.0</v>
       </c>
-      <c r="H4">
-        <v>80.0</v>
-      </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
@@ -482,13 +482,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>70.38</v>
+        <v>70.92</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -497,13 +497,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>70.26</v>
+        <v>70.5</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>5.71</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>69.28</v>
+        <v>69.68</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -552,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>70.0</v>
@@ -561,7 +561,7 @@
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>68.85</v>
+        <v>67.73</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="H8">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C9">
-        <v>67.4</v>
+        <v>66.2</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>20.0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="10">
@@ -627,10 +627,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>67.09</v>
+        <v>65.78</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -639,7 +639,7 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10">
         <v>90.0</v>
@@ -648,7 +648,7 @@
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>14.29</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="11">
@@ -656,13 +656,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>65.81</v>
+        <v>65.23</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -671,13 +671,13 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>90.0</v>
+        <v>80.0</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C12">
-        <v>64.83</v>
+        <v>64.37</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>2.86</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13">
-        <v>63.99</v>
+        <v>64.27</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>8.57</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>63.81</v>
+        <v>63.95</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="H14">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I14">
-        <v>25.71</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>63.57</v>
+      </c>
+      <c r="D15">
         <v>8</v>
       </c>
-      <c r="C15">
-        <v>63.56</v>
-      </c>
-      <c r="D15">
-        <v>6</v>
-      </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="H15">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I15">
-        <v>5.71</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C16">
-        <v>63.27</v>
+        <v>63.02</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>37.14</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="17">
@@ -830,10 +830,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>62.71</v>
+        <v>61.77</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>70.0</v>
@@ -851,7 +851,7 @@
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>25.71</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="18">
@@ -859,10 +859,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C18">
-        <v>61.42</v>
+        <v>61.77</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>70.0</v>
@@ -880,7 +880,7 @@
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>17.14</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>61.42</v>
+        <v>60.5</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>70.0</v>
+        <v>100.0</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>17.14</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -920,25 +920,25 @@
         <v>48</v>
       </c>
       <c r="C20">
-        <v>59.97</v>
+        <v>59.68</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H20">
         <v>20.0</v>
       </c>
       <c r="I20">
-        <v>37.14</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
+        <v>49</v>
+      </c>
+      <c r="C21">
+        <v>59.27</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="C21">
-        <v>59.84</v>
-      </c>
-      <c r="D21">
-        <v>6</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
       <c r="G21">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>14.29</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22">
-        <v>58.85</v>
+        <v>58.57</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="H22">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>58.81</v>
+        <v>58.53</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G23">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="H23">
         <v>20.0</v>
       </c>
       <c r="I23">
-        <v>25.71</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="24">
@@ -1036,7 +1036,7 @@
         <v>33</v>
       </c>
       <c r="C24">
-        <v>58.13</v>
+        <v>58.53</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -1045,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <v>60.0</v>
@@ -1054,7 +1054,7 @@
         <v>40.0</v>
       </c>
       <c r="I24">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C25">
-        <v>57.52</v>
+        <v>57.25</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G25">
-        <v>90.0</v>
+        <v>50.0</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I25">
-        <v>17.14</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C26">
-        <v>57.25</v>
+        <v>56.77</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G26">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="H26">
         <v>0.0</v>
       </c>
       <c r="I26">
-        <v>100.0</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>56.56</v>
+        <v>56.35</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>70.0</v>
       </c>
       <c r="H27">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I27">
-        <v>51.43</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C28">
-        <v>55.99</v>
+        <v>56.35</v>
       </c>
       <c r="D28">
         <v>7</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>70.0</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C29">
-        <v>55.99</v>
+        <v>55.93</v>
       </c>
       <c r="D29">
         <v>7</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G29">
         <v>70.0</v>
       </c>
       <c r="H29">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29">
-        <v>14.29</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C30">
-        <v>55.71</v>
+        <v>55.1</v>
       </c>
       <c r="D30">
         <v>7</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <v>70.0</v>
       </c>
       <c r="H30">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I30">
-        <v>45.71</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="31">
@@ -1236,13 +1236,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C31">
-        <v>54.71</v>
+        <v>53.53</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -1251,13 +1251,13 @@
         <v>2</v>
       </c>
       <c r="G31">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="H31">
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C32">
-        <v>53.13</v>
+        <v>53.08</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I32">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>52.68</v>
+        <v>52.25</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>50.0</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>2.86</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C34">
-        <v>51.68</v>
+        <v>51.0</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G34">
         <v>50.0</v>
       </c>
       <c r="H34">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I34">
-        <v>62.86</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="35">
@@ -1352,10 +1352,10 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>50.68</v>
+        <v>49.75</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>50.0</v>
@@ -1373,7 +1373,7 @@
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>22.86</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="36">
@@ -1384,7 +1384,7 @@
         <v>17</v>
       </c>
       <c r="C36">
-        <v>49.39</v>
+        <v>49.75</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>50.0</v>
@@ -1402,7 +1402,7 @@
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="37">
@@ -1413,7 +1413,7 @@
         <v>27</v>
       </c>
       <c r="C37">
-        <v>48.54</v>
+        <v>48.92</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>50.0</v>
@@ -1431,7 +1431,7 @@
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>8.57</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="38">
@@ -1439,10 +1439,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C38">
-        <v>48.51</v>
+        <v>48.88</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -1451,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38">
         <v>40.0</v>
@@ -1460,7 +1460,7 @@
         <v>40.0</v>
       </c>
       <c r="I38">
-        <v>11.43</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>48.51</v>
+        <v>48.47</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G39">
         <v>40.0</v>
       </c>
       <c r="H39">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I39">
-        <v>11.43</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C40">
-        <v>48.37</v>
+        <v>46.8</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
         <v>0</v>
-      </c>
-      <c r="F40">
-        <v>27</v>
       </c>
       <c r="G40">
         <v>40.0</v>
       </c>
       <c r="H40">
+        <v>40.0</v>
+      </c>
+      <c r="I40">
         <v>0.0</v>
-      </c>
-      <c r="I40">
-        <v>77.14</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C41">
-        <v>47.66</v>
+        <v>46.38</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G41">
         <v>40.0</v>
       </c>
       <c r="H41">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I41">
-        <v>5.71</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C42">
-        <v>46.8</v>
+        <v>43.05</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G42">
         <v>40.0</v>
       </c>
       <c r="H42">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I42">
-        <v>0.0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>42.66</v>
+        <v>43.02</v>
       </c>
       <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
         <v>4</v>
       </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>2</v>
-      </c>
       <c r="G43">
+        <v>30.0</v>
+      </c>
+      <c r="H43">
         <v>40.0</v>
       </c>
-      <c r="H43">
-        <v>20.0</v>
-      </c>
       <c r="I43">
-        <v>5.71</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="44">
@@ -1613,10 +1613,10 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C44">
-        <v>42.64</v>
+        <v>42.6</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1634,7 +1634,7 @@
         <v>40.0</v>
       </c>
       <c r="I44">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="45">
@@ -1642,10 +1642,10 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C45">
-        <v>41.8</v>
+        <v>42.22</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>40.0</v>
@@ -1663,7 +1663,7 @@
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="46">
@@ -1671,28 +1671,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C46">
-        <v>41.06</v>
+        <v>42.22</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H46">
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>31.43</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C47">
-        <v>40.78</v>
+        <v>41.8</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
         <v>0</v>
       </c>
-      <c r="F47">
-        <v>22</v>
-      </c>
       <c r="G47">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H47">
+        <v>20.0</v>
+      </c>
+      <c r="I47">
         <v>0.0</v>
-      </c>
-      <c r="I47">
-        <v>62.86</v>
       </c>
     </row>
     <row r="48">
@@ -1729,10 +1729,10 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="C48">
-        <v>40.35</v>
+        <v>40.93</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G48">
         <v>30.0</v>
@@ -1750,7 +1750,7 @@
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>60.0</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>42</v>
       </c>
       <c r="C49">
-        <v>39.78</v>
+        <v>40.1</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G49">
         <v>30.0</v>
@@ -1779,7 +1779,7 @@
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>22.86</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>28.59</v>
+        <v>28.78</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50">
         <v>10.0</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>54.29</v>
+        <v>55.56</v>
       </c>
     </row>
   </sheetData>
@@ -1867,266 +1867,266 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G6">
         <v>35</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I7">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H9">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <v>15</v>
@@ -2135,345 +2135,345 @@
         <v>18</v>
       </c>
       <c r="G10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H10">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I10">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="G11">
         <v>19</v>
       </c>
-      <c r="F11">
-        <v>23</v>
-      </c>
-      <c r="G11">
-        <v>39</v>
-      </c>
       <c r="H11">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G12">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H12">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I12">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G13">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H13">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>24</v>
+      </c>
+      <c r="G14">
         <v>29</v>
       </c>
-      <c r="F14">
-        <v>33</v>
-      </c>
-      <c r="G14">
-        <v>34</v>
-      </c>
       <c r="H14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I15">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G16">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I16">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C18">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G18">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H18">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I18">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>25</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G19">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I19">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H20">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <v>9</v>
+      </c>
+      <c r="E21">
+        <v>16</v>
+      </c>
+      <c r="F21">
         <v>20</v>
-      </c>
-      <c r="D21">
-        <v>26</v>
-      </c>
-      <c r="E21">
-        <v>29</v>
-      </c>
-      <c r="F21">
-        <v>31</v>
       </c>
       <c r="G21">
         <v>37</v>
@@ -2482,810 +2482,810 @@
         <v>49</v>
       </c>
       <c r="I21">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D22">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22">
         <v>29</v>
       </c>
       <c r="F22">
+        <v>31</v>
+      </c>
+      <c r="G22">
         <v>37</v>
       </c>
-      <c r="G22">
-        <v>47</v>
-      </c>
       <c r="H22">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I22">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G23">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H23">
         <v>48</v>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G24">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F25">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G25">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H25">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F26">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G26">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H26">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I26">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27">
+        <v>12</v>
+      </c>
+      <c r="E27">
         <v>18</v>
       </c>
-      <c r="E27">
-        <v>25</v>
-      </c>
       <c r="F27">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G27">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H27">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I27">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>28</v>
       </c>
       <c r="G28">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H28">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I28">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E29">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G29">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H29">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I29">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E30">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F30">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G30">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H30">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
+        <v>14</v>
+      </c>
+      <c r="F31">
+        <v>25</v>
+      </c>
+      <c r="G31">
+        <v>26</v>
+      </c>
+      <c r="H31">
+        <v>32</v>
+      </c>
+      <c r="I31">
         <v>7</v>
-      </c>
-      <c r="D31">
-        <v>14</v>
-      </c>
-      <c r="E31">
-        <v>16</v>
-      </c>
-      <c r="F31">
-        <v>37</v>
-      </c>
-      <c r="G31">
-        <v>39</v>
-      </c>
-      <c r="H31">
-        <v>47</v>
-      </c>
-      <c r="I31">
-        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G32">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H32">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I32">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F33">
+        <v>19</v>
+      </c>
+      <c r="G33">
+        <v>20</v>
+      </c>
+      <c r="H33">
+        <v>40</v>
+      </c>
+      <c r="I33">
         <v>22</v>
-      </c>
-      <c r="G33">
-        <v>40</v>
-      </c>
-      <c r="H33">
-        <v>45</v>
-      </c>
-      <c r="I33">
-        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F34">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G34">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H34">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I34">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C35">
         <v>4</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F35">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G35">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I35">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H36">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I36">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H37">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C38">
         <v>5</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38">
+        <v>13</v>
+      </c>
+      <c r="F38">
         <v>25</v>
       </c>
-      <c r="F38">
-        <v>40</v>
-      </c>
       <c r="G38">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H38">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I38">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F39">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G39">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H39">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I39">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F40">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G40">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H40">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I40">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D41">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E41">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F41">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G41">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H41">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I41">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F42">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G42">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H42">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I42">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G43">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H43">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C44">
         <v>5</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E44">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F44">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G44">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H44">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I44">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>11</v>
       </c>
       <c r="E45">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F45">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G45">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H45">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I45">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D46">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F46">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G46">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H46">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I46">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C47">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47">
         <v>27</v>
       </c>
       <c r="F47">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G47">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H47">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I47">
         <v>37</v>
@@ -3293,30 +3293,30 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E48">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F48">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G48">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H48">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I48">
         <v>37</v>
@@ -3324,95 +3324,95 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E49">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F49">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G49">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H49">
         <v>49</v>
       </c>
       <c r="I49">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D50">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E50">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F50">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G50">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H50">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I50">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E51">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F51">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G51">
+        <v>45</v>
+      </c>
+      <c r="H51">
         <v>47</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>48</v>
-      </c>
-      <c r="I51">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3552,10 +3552,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.857</v>
+        <v>0.905</v>
       </c>
       <c r="D6">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="E6">
         <v>2.4</v>
@@ -3574,7 +3574,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="D7">
         <v>11.9</v>
@@ -3648,16 +3648,16 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>72.97</v>
+        <v>73.44</v>
       </c>
       <c r="D2">
         <v>13</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>86.67</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>66.1</v>
+        <v>69.85</v>
       </c>
       <c r="D3">
         <v>11</v>
@@ -3686,16 +3686,16 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>73.33</v>
       </c>
       <c r="H3">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>22.22</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="4">
@@ -3706,7 +3706,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>64.43</v>
+        <v>68.24</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -3715,16 +3715,16 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>73.33</v>
       </c>
       <c r="H4">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I4">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="5">
@@ -3735,25 +3735,25 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>64.08</v>
+        <v>67.81</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>86.67</v>
+        <v>80.0</v>
       </c>
       <c r="H5">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I5">
-        <v>7.41</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="6">
@@ -3764,7 +3764,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>63.88</v>
+        <v>67.71</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -3773,16 +3773,16 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>73.33</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I6">
-        <v>7.41</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>63.22</v>
+        <v>66.97</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>60.0</v>
       </c>
       <c r="H7">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>63.12</v>
+        <v>66.87</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H8">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I8">
-        <v>3.7</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="9">
@@ -3848,13 +3848,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>63.02</v>
+        <v>66.54</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -3863,13 +3863,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>53.33</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I9">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="10">
@@ -3880,25 +3880,25 @@
         <v>22</v>
       </c>
       <c r="C10">
-        <v>62.77</v>
+        <v>66.54</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>4</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H10">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="11">
@@ -3906,13 +3906,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>62.67</v>
+        <v>65.8</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>4</v>
@@ -3921,10 +3921,10 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>66.67</v>
+        <v>53.33</v>
       </c>
       <c r="H11">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I11">
         <v>0.0</v>
@@ -3938,7 +3938,7 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>61.63</v>
+        <v>64.55</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -3947,16 +3947,16 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>53.33</v>
       </c>
       <c r="H12">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I12">
-        <v>22.22</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="13">
@@ -3964,10 +3964,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>61.18</v>
+        <v>63.58</v>
       </c>
       <c r="D13">
         <v>9</v>
@@ -3982,10 +3982,10 @@
         <v>60.0</v>
       </c>
       <c r="H13">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I13">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>60.8</v>
+        <v>62.09</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>53.33</v>
+        <v>80.0</v>
       </c>
       <c r="H14">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I14">
-        <v>100.0</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="15">
@@ -4022,10 +4022,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>60.72</v>
+        <v>62.07</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -4034,16 +4034,16 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15">
         <v>66.67</v>
       </c>
       <c r="H15">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I15">
-        <v>14.81</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>60.9</v>
+      </c>
+      <c r="D16">
         <v>9</v>
       </c>
-      <c r="C16">
-        <v>60.09</v>
-      </c>
-      <c r="D16">
-        <v>12</v>
-      </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="H16">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I16">
-        <v>37.04</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>60.8</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>28</v>
       </c>
-      <c r="C17">
-        <v>59.51</v>
-      </c>
-      <c r="D17">
-        <v>9</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
       <c r="G17">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H17">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I17">
-        <v>7.41</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C18">
-        <v>58.85</v>
+        <v>59.01</v>
       </c>
       <c r="D18">
         <v>8</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>53.33</v>
       </c>
       <c r="H18">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I18">
-        <v>3.7</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C19">
-        <v>58.3</v>
+        <v>57.51</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
         <v>3</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
       <c r="G19">
-        <v>53.33</v>
+        <v>60.0</v>
       </c>
       <c r="H19">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I19">
-        <v>0.0</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="20">
@@ -4167,10 +4167,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>56.47</v>
+        <v>57.3</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -4179,16 +4179,16 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>46.67</v>
       </c>
       <c r="H20">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I20">
-        <v>11.11</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>56.87</v>
+      </c>
+      <c r="D21">
         <v>8</v>
       </c>
-      <c r="C21">
-        <v>55.36</v>
-      </c>
-      <c r="D21">
-        <v>7</v>
-      </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>46.67</v>
+        <v>53.33</v>
       </c>
       <c r="H21">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I21">
-        <v>3.7</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22">
-        <v>55.24</v>
+        <v>56.63</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>53.33</v>
+        <v>73.33</v>
       </c>
       <c r="H22">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>7.41</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>54.43</v>
+        <v>56.33</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>73.33</v>
+        <v>53.33</v>
       </c>
       <c r="H23">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>54.0</v>
+        <v>55.54</v>
       </c>
       <c r="D24">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>100.0</v>
+        <v>40.0</v>
       </c>
       <c r="H24">
-        <v>16.67</v>
+        <v>60.0</v>
       </c>
       <c r="I24">
-        <v>22.22</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C25">
-        <v>53.97</v>
+        <v>55.25</v>
       </c>
       <c r="D25">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
         <v>7</v>
       </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>6</v>
-      </c>
       <c r="G25">
-        <v>46.67</v>
+        <v>100.0</v>
       </c>
       <c r="H25">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>22.22</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C26">
-        <v>51.73</v>
+        <v>52.17</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>40.0</v>
+        <v>73.33</v>
       </c>
       <c r="H26">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>33.33</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>50.82</v>
+        <v>52.15</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G27">
-        <v>73.33</v>
+        <v>40.0</v>
       </c>
       <c r="H27">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I27">
-        <v>3.7</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C28">
-        <v>46.73</v>
+        <v>47.57</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28">
+        <v>26.67</v>
+      </c>
+      <c r="H28">
         <v>40.0</v>
       </c>
-      <c r="H28">
-        <v>0.0</v>
-      </c>
       <c r="I28">
-        <v>55.56</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>45.6</v>
+        <v>47.3</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>26.67</v>
+        <v>46.67</v>
       </c>
       <c r="H29">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="I29">
-        <v>44.44</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C30">
-        <v>44.5</v>
+        <v>45.03</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>33.33</v>
       </c>
       <c r="H30">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I30">
-        <v>66.67</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>42.83</v>
+        <v>44.68</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G31">
         <v>33.33</v>
       </c>
       <c r="H31">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I31">
-        <v>0.0</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C32">
-        <v>41.16</v>
+        <v>44.5</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
         <v>0</v>
       </c>
-      <c r="F32">
-        <v>19</v>
-      </c>
       <c r="G32">
-        <v>26.67</v>
+        <v>33.33</v>
       </c>
       <c r="H32">
+        <v>40.0</v>
+      </c>
+      <c r="I32">
         <v>0.0</v>
-      </c>
-      <c r="I32">
-        <v>70.37</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>41.16</v>
+        <v>43.28</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -4556,16 +4556,16 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>26.67</v>
       </c>
       <c r="H33">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I33">
-        <v>14.81</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="34">
@@ -4576,7 +4576,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>40.32</v>
+        <v>41.49</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -4585,16 +4585,16 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <v>26.67</v>
       </c>
       <c r="H34">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I34">
-        <v>37.04</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="35">
@@ -4605,7 +4605,7 @@
         <v>16</v>
       </c>
       <c r="C35">
-        <v>40.32</v>
+        <v>41.49</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -4614,16 +4614,16 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35">
         <v>26.67</v>
       </c>
       <c r="H35">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I35">
-        <v>37.04</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>39.21</v>
+        <v>41.32</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G36">
         <v>26.67</v>
       </c>
       <c r="H36">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I36">
-        <v>29.63</v>
+        <v>71.43</v>
       </c>
     </row>
     <row r="37">
@@ -4660,10 +4660,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C37">
-        <v>34.77</v>
+        <v>40.42</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,16 +4672,16 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G37">
         <v>26.67</v>
       </c>
       <c r="H37">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I37">
-        <v>0.0</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>34.76</v>
+        <v>36.7</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>20.0</v>
       </c>
       <c r="H38">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I38">
-        <v>25.93</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -4718,28 +4718,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C39">
-        <v>33.08</v>
+        <v>35.99</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G39">
-        <v>13.33</v>
+        <v>20.0</v>
       </c>
       <c r="H39">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I39">
-        <v>40.74</v>
+        <v>28.57</v>
       </c>
     </row>
   </sheetData>
@@ -4798,61 +4798,61 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>33</v>
+      </c>
+      <c r="I2">
         <v>4</v>
-      </c>
-      <c r="D2">
-        <v>15</v>
-      </c>
-      <c r="E2">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>26</v>
-      </c>
-      <c r="G2">
-        <v>34</v>
-      </c>
-      <c r="H2">
-        <v>36</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I3">
         <v>7</v>
@@ -4860,30 +4860,30 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>17</v>
+      </c>
+      <c r="F4">
         <v>19</v>
       </c>
-      <c r="D4">
-        <v>22</v>
-      </c>
-      <c r="E4">
-        <v>28</v>
-      </c>
-      <c r="F4">
-        <v>31</v>
-      </c>
       <c r="G4">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -4891,30 +4891,30 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -4922,24 +4922,24 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G6">
         <v>29</v>
@@ -4948,97 +4948,97 @@
         <v>31</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
         <v>23</v>
       </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
+      <c r="G7">
         <v>29</v>
       </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
       <c r="H7">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8">
+        <v>25</v>
+      </c>
+      <c r="F8">
         <v>29</v>
       </c>
-      <c r="F8">
-        <v>32</v>
-      </c>
       <c r="G8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G9">
         <v>35</v>
       </c>
       <c r="H9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -5046,402 +5046,402 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G10">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G12">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H12">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
         <v>6</v>
       </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
       <c r="E13">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H13">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>23</v>
+      </c>
+      <c r="I16">
         <v>4</v>
-      </c>
-      <c r="D16">
-        <v>17</v>
-      </c>
-      <c r="E16">
-        <v>19</v>
-      </c>
-      <c r="F16">
-        <v>25</v>
-      </c>
-      <c r="G16">
-        <v>28</v>
-      </c>
-      <c r="H16">
-        <v>29</v>
-      </c>
-      <c r="I16">
-        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H18">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G19">
         <v>28</v>
       </c>
       <c r="H19">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G20">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H20">
         <v>35</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E21">
+        <v>9</v>
+      </c>
+      <c r="F21">
+        <v>15</v>
+      </c>
+      <c r="G21">
         <v>24</v>
       </c>
-      <c r="F21">
-        <v>31</v>
-      </c>
-      <c r="G21">
-        <v>34</v>
-      </c>
       <c r="H21">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G22">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H22">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I22">
         <v>3</v>
@@ -5449,554 +5449,554 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G23">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H23">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F24">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H24">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F25">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G25">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H25">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I25">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G26">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H26">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G27">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H27">
         <v>38</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H28">
         <v>38</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G29">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H29">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <v>19</v>
+      </c>
+      <c r="G30">
+        <v>27</v>
+      </c>
+      <c r="H30">
+        <v>30</v>
+      </c>
+      <c r="I30">
         <v>8</v>
-      </c>
-      <c r="E30">
-        <v>27</v>
-      </c>
-      <c r="F30">
-        <v>33</v>
-      </c>
-      <c r="G30">
-        <v>35</v>
-      </c>
-      <c r="H30">
-        <v>38</v>
-      </c>
-      <c r="I30">
-        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F31">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G31">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F32">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G32">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H32">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I32">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F33">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G33">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H33">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F34">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G34">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H34">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F35">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G35">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H35">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F36">
         <v>27</v>
       </c>
       <c r="G36">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H36">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C37">
         <v>5</v>
       </c>
       <c r="D37">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G37">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E38">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F38">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G38">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H38">
         <v>34</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
         <v>13</v>
       </c>
-      <c r="D39">
-        <v>14</v>
-      </c>
       <c r="E39">
+        <v>21</v>
+      </c>
+      <c r="F39">
         <v>22</v>
       </c>
-      <c r="F39">
-        <v>28</v>
-      </c>
       <c r="G39">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F40">
         <v>28</v>
       </c>
       <c r="G40">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H40">
         <v>38</v>
@@ -6007,58 +6007,58 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
         <v>9</v>
       </c>
-      <c r="D41">
-        <v>13</v>
-      </c>
       <c r="E41">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F41">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G41">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H41">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C42">
+        <v>9</v>
+      </c>
+      <c r="D42">
+        <v>13</v>
+      </c>
+      <c r="E42">
         <v>14</v>
       </c>
-      <c r="D42">
-        <v>26</v>
-      </c>
-      <c r="E42">
-        <v>28</v>
-      </c>
       <c r="F42">
+        <v>18</v>
+      </c>
+      <c r="G42">
         <v>31</v>
-      </c>
-      <c r="G42">
-        <v>32</v>
       </c>
       <c r="H42">
         <v>34</v>
@@ -6069,61 +6069,61 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E43">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F43">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G43">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H43">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F44">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G44">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H44">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I44">
         <v>8</v>
@@ -6131,15 +6131,15 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>11</v>
@@ -6148,106 +6148,106 @@
         <v>14</v>
       </c>
       <c r="F45">
+        <v>17</v>
+      </c>
+      <c r="G45">
+        <v>29</v>
+      </c>
+      <c r="H45">
         <v>32</v>
       </c>
-      <c r="G45">
-        <v>36</v>
-      </c>
-      <c r="H45">
-        <v>38</v>
-      </c>
       <c r="I45">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C46">
         <v>7</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F46">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G46">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H46">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000017</v>
+        <v>115000018</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E47">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F47">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G47">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H47">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I47">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000016</v>
+        <v>115000017</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F48">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G48">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H48">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I48">
         <v>2</v>
@@ -6255,92 +6255,92 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000015</v>
+        <v>115000016</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F49">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G49">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H49">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000014</v>
+        <v>115000015</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C50">
         <v>2</v>
       </c>
       <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
         <v>6</v>
       </c>
-      <c r="E50">
-        <v>19</v>
-      </c>
       <c r="F50">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G50">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H50">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000013</v>
+        <v>115000014</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
         <v>6</v>
       </c>
-      <c r="D51">
-        <v>10</v>
-      </c>
       <c r="E51">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F51">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G51">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H51">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I51">
         <v>3</v>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-07 第 115000077 期；威力彩 2026-08-06 第 115000063 期</t>
+          <t>大樂透 2026-08-07 第 115000077 期；威力彩 2026-08-10 第 115000064 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 13, 14, 29, 35, 38</t>
+          <t>9, 13, 29, 31, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.452 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,13 +3464,13 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.119</v>
+        <v>1.048</v>
       </c>
       <c r="D2">
-        <v>33.3</v>
+        <v>31.0</v>
       </c>
       <c r="E2">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -3486,13 +3486,13 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.119</v>
+        <v>1.048</v>
       </c>
       <c r="D3">
-        <v>33.3</v>
+        <v>31.0</v>
       </c>
       <c r="E3">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3501,20 +3501,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B4">
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.976</v>
+        <v>0.952</v>
       </c>
       <c r="D4">
         <v>21.4</v>
       </c>
       <c r="E4">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3523,17 +3523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.976</v>
+        <v>0.929</v>
       </c>
       <c r="D5">
-        <v>23.8</v>
+        <v>19.0</v>
       </c>
       <c r="E5">
         <v>4.8</v>
@@ -3552,7 +3552,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.905</v>
+        <v>0.881</v>
       </c>
       <c r="D6">
         <v>23.8</v>
@@ -3648,7 +3648,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>73.44</v>
+        <v>75.74</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -3657,16 +3657,16 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>86.67</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>14.29</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>69.85</v>
+        <v>72.91</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>73.33</v>
+        <v>85.71</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -3703,10 +3703,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>68.24</v>
+        <v>71.81</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -3715,16 +3715,16 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G4">
-        <v>73.33</v>
+        <v>78.57</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>14.29</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>67.81</v>
+        <v>70.26</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>80.0</v>
+        <v>78.57</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>10.71</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C6">
-        <v>67.71</v>
+        <v>69.98</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>73.33</v>
+        <v>85.71</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>10.71</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>66.97</v>
+        <v>68.49</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>60.0</v>
+        <v>57.14</v>
       </c>
       <c r="H7">
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>7.14</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="8">
@@ -3819,13 +3819,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>66.87</v>
+        <v>68.46</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -3834,13 +3834,13 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>53.33</v>
+        <v>71.43</v>
       </c>
       <c r="H8">
         <v>80.0</v>
       </c>
       <c r="I8">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>66.54</v>
+        <v>67.19</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>4</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>66.67</v>
+        <v>64.29</v>
       </c>
       <c r="H9">
         <v>80.0</v>
       </c>
       <c r="I9">
-        <v>3.57</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>66.54</v>
+        <v>65.05</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="H10">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I10">
-        <v>3.57</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>65.8</v>
+        <v>63.74</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>53.33</v>
+        <v>64.29</v>
       </c>
       <c r="H11">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I11">
-        <v>0.0</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>64.55</v>
+        <v>63.74</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>53.33</v>
+        <v>64.29</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>25.0</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>63.58</v>
+        <v>63.46</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>60.0</v>
+        <v>71.43</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>17.86</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>62.09</v>
+        <v>62.46</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>80.0</v>
+        <v>57.14</v>
       </c>
       <c r="H14">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I14">
-        <v>39.29</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C15">
-        <v>62.07</v>
+        <v>62.46</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="H15">
         <v>60.0</v>
       </c>
       <c r="I15">
-        <v>7.14</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="16">
@@ -4051,13 +4051,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C16">
-        <v>60.9</v>
+        <v>62.43</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>60.0</v>
+        <v>71.43</v>
       </c>
       <c r="H16">
         <v>60.0</v>
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>60.8</v>
+        <v>62.19</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
         <v>0</v>
       </c>
-      <c r="F17">
-        <v>28</v>
-      </c>
       <c r="G17">
-        <v>53.33</v>
+        <v>64.29</v>
       </c>
       <c r="H17">
+        <v>60.0</v>
+      </c>
+      <c r="I17">
         <v>0.0</v>
-      </c>
-      <c r="I17">
-        <v>100.0</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18">
-        <v>59.01</v>
+        <v>61.94</v>
       </c>
       <c r="D18">
         <v>8</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H18">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18">
-        <v>21.43</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>57.51</v>
+        <v>59.12</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>60.0</v>
+        <v>85.71</v>
       </c>
       <c r="H19">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I19">
-        <v>10.71</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>58.71</v>
+      </c>
+      <c r="D20">
+        <v>11</v>
+      </c>
+      <c r="E20">
         <v>2</v>
       </c>
-      <c r="C20">
-        <v>57.3</v>
-      </c>
-      <c r="D20">
-        <v>7</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>46.67</v>
+        <v>78.57</v>
       </c>
       <c r="H20">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>0.0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="21">
@@ -4199,7 +4199,7 @@
         <v>17</v>
       </c>
       <c r="C21">
-        <v>56.87</v>
+        <v>58.49</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -4208,16 +4208,16 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>7.14</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>56.63</v>
+        <v>57.98</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>73.33</v>
+        <v>57.14</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>3.57</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C23">
-        <v>56.33</v>
+        <v>57.54</v>
       </c>
       <c r="D23">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
         <v>8</v>
       </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
       <c r="G23">
-        <v>53.33</v>
+        <v>100.0</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I23">
-        <v>3.57</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="24">
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>55.54</v>
+        <v>56.84</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -4295,16 +4295,16 @@
         <v>3</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>40.0</v>
+        <v>42.86</v>
       </c>
       <c r="H24">
         <v>60.0</v>
       </c>
       <c r="I24">
-        <v>14.29</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>55.25</v>
+        <v>54.22</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>100.0</v>
+        <v>78.57</v>
       </c>
       <c r="H25">
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>25.0</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C26">
-        <v>52.17</v>
+        <v>53.4</v>
       </c>
       <c r="D26">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>73.33</v>
+        <v>42.86</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I26">
-        <v>7.14</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C27">
-        <v>52.15</v>
+        <v>50.21</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>40.0</v>
+        <v>35.71</v>
       </c>
       <c r="H27">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I27">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>47.57</v>
+        <v>49.78</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>26.67</v>
+        <v>42.86</v>
       </c>
       <c r="H28">
         <v>40.0</v>
       </c>
       <c r="I28">
-        <v>46.43</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>47.3</v>
+        <v>48.82</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -4440,16 +4440,16 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>46.67</v>
+        <v>50.0</v>
       </c>
       <c r="H29">
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>0.0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="30">
@@ -4457,10 +4457,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C30">
-        <v>45.03</v>
+        <v>45.73</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4472,13 +4472,13 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H30">
         <v>40.0</v>
       </c>
       <c r="I30">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="31">
@@ -4489,7 +4489,7 @@
         <v>3</v>
       </c>
       <c r="C31">
-        <v>44.68</v>
+        <v>45.56</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,16 +4498,16 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H31">
         <v>0.0</v>
       </c>
       <c r="I31">
-        <v>67.86</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="32">
@@ -4515,10 +4515,10 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>44.5</v>
+        <v>45.21</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -4530,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H32">
         <v>40.0</v>
@@ -4547,7 +4547,7 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>43.28</v>
+        <v>44.27</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -4556,16 +4556,16 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33">
-        <v>26.67</v>
+        <v>28.57</v>
       </c>
       <c r="H33">
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>17.86</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="34">
@@ -4573,10 +4573,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C34">
-        <v>41.49</v>
+        <v>43.41</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -4585,16 +4585,16 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G34">
-        <v>26.67</v>
+        <v>28.57</v>
       </c>
       <c r="H34">
         <v>20.0</v>
       </c>
       <c r="I34">
-        <v>39.29</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="35">
@@ -4602,10 +4602,10 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>41.49</v>
+        <v>42.38</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -4614,16 +4614,16 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G35">
-        <v>26.67</v>
+        <v>28.57</v>
       </c>
       <c r="H35">
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>39.29</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>41.32</v>
+        <v>42.38</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G36">
-        <v>26.67</v>
+        <v>28.57</v>
       </c>
       <c r="H36">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I36">
-        <v>71.43</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>40.42</v>
+        <v>42.03</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G37">
-        <v>26.67</v>
+        <v>28.57</v>
       </c>
       <c r="H37">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I37">
-        <v>32.14</v>
+        <v>72.41</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>36.7</v>
+        <v>37.65</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,16 +4701,16 @@
         <v>2</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>20.0</v>
+        <v>21.43</v>
       </c>
       <c r="H38">
         <v>40.0</v>
       </c>
       <c r="I38">
-        <v>0.0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>35.99</v>
+        <v>36.78</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,16 +4730,16 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G39">
-        <v>20.0</v>
+        <v>21.43</v>
       </c>
       <c r="H39">
         <v>20.0</v>
       </c>
       <c r="I39">
-        <v>28.57</v>
+        <v>31.03</v>
       </c>
     </row>
   </sheetData>
@@ -4798,92 +4798,92 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>33</v>
+      </c>
+      <c r="I3">
         <v>4</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>26</v>
-      </c>
-      <c r="G3">
-        <v>34</v>
-      </c>
-      <c r="H3">
-        <v>36</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -4891,30 +4891,30 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>31</v>
-      </c>
       <c r="G5">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -4922,30 +4922,30 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -4953,24 +4953,24 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>29</v>
@@ -4979,97 +4979,97 @@
         <v>31</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
         <v>23</v>
       </c>
-      <c r="E8">
-        <v>25</v>
-      </c>
-      <c r="F8">
+      <c r="G8">
         <v>29</v>
       </c>
-      <c r="G8">
-        <v>34</v>
-      </c>
       <c r="H8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
         <v>29</v>
       </c>
-      <c r="F9">
-        <v>32</v>
-      </c>
       <c r="G9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G10">
         <v>35</v>
       </c>
       <c r="H10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -5077,402 +5077,402 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G11">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G12">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G13">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H13">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
         <v>6</v>
       </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
       <c r="E14">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G14">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H15">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G16">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>18</v>
+      </c>
+      <c r="H17">
+        <v>23</v>
+      </c>
+      <c r="I17">
         <v>4</v>
-      </c>
-      <c r="D17">
-        <v>17</v>
-      </c>
-      <c r="E17">
-        <v>19</v>
-      </c>
-      <c r="F17">
-        <v>25</v>
-      </c>
-      <c r="G17">
-        <v>28</v>
-      </c>
-      <c r="H17">
-        <v>29</v>
-      </c>
-      <c r="I17">
-        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H18">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H19">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G20">
         <v>28</v>
       </c>
       <c r="H20">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G21">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H21">
         <v>35</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E22">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>15</v>
+      </c>
+      <c r="G22">
         <v>24</v>
       </c>
-      <c r="F22">
-        <v>31</v>
-      </c>
-      <c r="G22">
-        <v>34</v>
-      </c>
       <c r="H22">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G23">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H23">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I23">
         <v>3</v>
@@ -5480,554 +5480,554 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G24">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H24">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E25">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F25">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G25">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H25">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F26">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G26">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H26">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I26">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G27">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H27">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G28">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H28">
         <v>38</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E29">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H29">
         <v>38</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E30">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G30">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>13</v>
+      </c>
+      <c r="F31">
+        <v>19</v>
+      </c>
+      <c r="G31">
+        <v>27</v>
+      </c>
+      <c r="H31">
+        <v>30</v>
+      </c>
+      <c r="I31">
         <v>8</v>
-      </c>
-      <c r="E31">
-        <v>27</v>
-      </c>
-      <c r="F31">
-        <v>33</v>
-      </c>
-      <c r="G31">
-        <v>35</v>
-      </c>
-      <c r="H31">
-        <v>38</v>
-      </c>
-      <c r="I31">
-        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G32">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G33">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H33">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G34">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H34">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E35">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G35">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H35">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F36">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G36">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H36">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F37">
         <v>27</v>
       </c>
       <c r="G37">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H37">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C38">
         <v>5</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F38">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G38">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F39">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G39">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H39">
         <v>34</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
         <v>13</v>
       </c>
-      <c r="D40">
-        <v>14</v>
-      </c>
       <c r="E40">
+        <v>21</v>
+      </c>
+      <c r="F40">
         <v>22</v>
       </c>
-      <c r="F40">
-        <v>28</v>
-      </c>
       <c r="G40">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H40">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F41">
         <v>28</v>
       </c>
       <c r="G41">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H41">
         <v>38</v>
@@ -6038,58 +6038,58 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
         <v>9</v>
       </c>
-      <c r="D42">
-        <v>13</v>
-      </c>
       <c r="E42">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F42">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G42">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H42">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C43">
+        <v>9</v>
+      </c>
+      <c r="D43">
+        <v>13</v>
+      </c>
+      <c r="E43">
         <v>14</v>
       </c>
-      <c r="D43">
-        <v>26</v>
-      </c>
-      <c r="E43">
-        <v>28</v>
-      </c>
       <c r="F43">
+        <v>18</v>
+      </c>
+      <c r="G43">
         <v>31</v>
-      </c>
-      <c r="G43">
-        <v>32</v>
       </c>
       <c r="H43">
         <v>34</v>
@@ -6100,61 +6100,61 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F44">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G44">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H44">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E45">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F45">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G45">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H45">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I45">
         <v>8</v>
@@ -6162,15 +6162,15 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -6179,106 +6179,106 @@
         <v>14</v>
       </c>
       <c r="F46">
+        <v>17</v>
+      </c>
+      <c r="G46">
+        <v>29</v>
+      </c>
+      <c r="H46">
         <v>32</v>
       </c>
-      <c r="G46">
-        <v>36</v>
-      </c>
-      <c r="H46">
-        <v>38</v>
-      </c>
       <c r="I46">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C47">
         <v>7</v>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E47">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F47">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G47">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H47">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000017</v>
+        <v>115000018</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E48">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G48">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H48">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000016</v>
+        <v>115000017</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F49">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G49">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H49">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I49">
         <v>2</v>
@@ -6286,64 +6286,64 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000015</v>
+        <v>115000016</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50">
+        <v>13</v>
+      </c>
+      <c r="F50">
+        <v>24</v>
+      </c>
+      <c r="G50">
+        <v>31</v>
+      </c>
+      <c r="H50">
+        <v>35</v>
+      </c>
+      <c r="I50">
         <v>2</v>
-      </c>
-      <c r="D50">
-        <v>3</v>
-      </c>
-      <c r="E50">
-        <v>6</v>
-      </c>
-      <c r="F50">
-        <v>12</v>
-      </c>
-      <c r="G50">
-        <v>23</v>
-      </c>
-      <c r="H50">
-        <v>27</v>
-      </c>
-      <c r="I50">
-        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000014</v>
+        <v>115000015</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C51">
         <v>2</v>
       </c>
       <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
         <v>6</v>
       </c>
-      <c r="E51">
-        <v>19</v>
-      </c>
       <c r="F51">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G51">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H51">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-07 第 115000077 期；威力彩 2026-08-10 第 115000064 期</t>
+          <t>大樂透 2026-08-11 第 115000078 期；威力彩 2026-08-10 第 115000064 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 12, 15, 19, 29, 34</t>
+          <t>4, 11, 12, 16, 25, 29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.072 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.096 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,10 +214,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.762</v>
+        <v>0.81</v>
       </c>
       <c r="D2">
-        <v>19.0</v>
+        <v>21.4</v>
       </c>
       <c r="E2">
         <v>0.0</v>
@@ -236,10 +236,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.738</v>
+        <v>0.786</v>
       </c>
       <c r="D3">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="E3">
         <v>0.0</v>
@@ -258,10 +258,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.69</v>
+        <v>0.714</v>
       </c>
       <c r="D4">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="E4">
         <v>0.0</v>
@@ -273,7 +273,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B5">
@@ -283,26 +283,26 @@
         <v>0.667</v>
       </c>
       <c r="D5">
-        <v>11.9</v>
+        <v>19.0</v>
       </c>
       <c r="E5">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="D6">
         <v>16.7</v>
@@ -317,7 +317,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B7">
@@ -327,13 +327,13 @@
         <v>0.643</v>
       </c>
       <c r="D7">
-        <v>14.3</v>
+        <v>11.9</v>
       </c>
       <c r="E7">
-        <v>2.4</v>
+        <v>0.0</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -398,16 +398,16 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>78.83</v>
+        <v>73.05</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>22.22</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>74.95</v>
+        <v>72.75</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>90.0</v>
+        <v>63.64</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="4">
@@ -453,13 +453,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>74.27</v>
+        <v>72.62</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -468,13 +468,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>70.0</v>
+        <v>72.73</v>
       </c>
       <c r="H4">
         <v>100.0</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -482,19 +482,19 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>70.92</v>
+        <v>68.05</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>100.0</v>
@@ -503,7 +503,7 @@
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>2.78</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>70.5</v>
+        <v>67.28</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>100.0</v>
+        <v>54.55</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>69.68</v>
+        <v>66.94</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -552,16 +552,16 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H7">
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>5.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -572,25 +572,25 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>67.73</v>
+        <v>65.59</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>80.0</v>
+        <v>63.64</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>22.22</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>26</v>
       </c>
       <c r="C9">
-        <v>66.2</v>
+        <v>64.12</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -610,16 +610,16 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>90.0</v>
+        <v>81.82</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>8.33</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>65.78</v>
+        <v>63.71</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -639,16 +639,16 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>90.0</v>
+        <v>81.82</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>5.56</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="11">
@@ -656,13 +656,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>65.23</v>
+        <v>63.58</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -671,13 +671,13 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>80.0</v>
+        <v>90.91</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>64.37</v>
+        <v>63.44</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>60.0</v>
+        <v>72.73</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>11.11</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="13">
@@ -717,7 +717,7 @@
         <v>36</v>
       </c>
       <c r="C13">
-        <v>64.27</v>
+        <v>62.75</v>
       </c>
       <c r="D13">
         <v>7</v>
@@ -726,16 +726,16 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>63.95</v>
+        <v>62.5</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>60.0</v>
+        <v>81.82</v>
       </c>
       <c r="H14">
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>8.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C15">
-        <v>63.57</v>
+        <v>61.4</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>80.0</v>
+        <v>63.64</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>27.78</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="16">
@@ -801,10 +801,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>63.02</v>
+        <v>60.19</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -813,16 +813,16 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>27.78</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C17">
-        <v>61.77</v>
+        <v>59.31</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>70.0</v>
+        <v>54.55</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>19.44</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C18">
-        <v>61.77</v>
+        <v>58.18</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>70.0</v>
+        <v>90.91</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>19.44</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C19">
-        <v>60.5</v>
+        <v>58.09</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>100.0</v>
+        <v>54.55</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>0.0</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20">
-        <v>59.68</v>
+        <v>57.75</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H20">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>38.89</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C21">
-        <v>59.27</v>
+        <v>57.28</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>70.0</v>
+        <v>54.55</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>2.78</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="22">
@@ -978,25 +978,25 @@
         <v>47</v>
       </c>
       <c r="C22">
-        <v>58.57</v>
+        <v>56.4</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>80.0</v>
+        <v>63.64</v>
       </c>
       <c r="H22">
         <v>20.0</v>
       </c>
       <c r="I22">
-        <v>27.78</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>58.53</v>
+        <v>55.88</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G23">
-        <v>60.0</v>
+        <v>45.45</v>
       </c>
       <c r="H23">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I23">
-        <v>38.89</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C24">
-        <v>58.53</v>
+        <v>55.88</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24">
+        <v>45.45</v>
+      </c>
+      <c r="H24">
         <v>60.0</v>
       </c>
-      <c r="H24">
-        <v>40.0</v>
-      </c>
       <c r="I24">
-        <v>5.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C25">
-        <v>57.25</v>
+        <v>55.05</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G25">
-        <v>50.0</v>
+        <v>63.64</v>
       </c>
       <c r="H25">
         <v>0.0</v>
       </c>
       <c r="I25">
-        <v>100.0</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>56.77</v>
+        <v>54.78</v>
       </c>
       <c r="D26">
         <v>7</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H26">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>52.78</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C27">
-        <v>56.35</v>
+        <v>54.24</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G27">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H27">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I27">
-        <v>16.67</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="28">
@@ -1152,25 +1152,25 @@
         <v>14</v>
       </c>
       <c r="C28">
-        <v>56.35</v>
+        <v>53.9</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28">
-        <v>70.0</v>
+        <v>54.55</v>
       </c>
       <c r="H28">
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>16.67</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C29">
-        <v>55.93</v>
+        <v>53.56</v>
       </c>
       <c r="D29">
         <v>7</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H29">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I29">
-        <v>47.22</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C30">
-        <v>55.1</v>
+        <v>53.02</v>
       </c>
       <c r="D30">
         <v>7</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G30">
-        <v>70.0</v>
+        <v>63.64</v>
       </c>
       <c r="H30">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30">
-        <v>8.33</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="31">
@@ -1239,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="C31">
-        <v>53.53</v>
+        <v>52.28</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1248,16 +1248,16 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>60.0</v>
+        <v>54.55</v>
       </c>
       <c r="H31">
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>5.56</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C32">
-        <v>53.08</v>
+        <v>52.15</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G32">
-        <v>50.0</v>
+        <v>54.55</v>
       </c>
       <c r="H32">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I32">
-        <v>5.56</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C33">
-        <v>52.25</v>
+        <v>52.1</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,16 +1306,16 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>50.0</v>
+        <v>45.45</v>
       </c>
       <c r="H33">
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>0.0</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>51.0</v>
+        <v>51.29</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
         <v>1</v>
       </c>
-      <c r="F34">
-        <v>9</v>
-      </c>
       <c r="G34">
-        <v>50.0</v>
+        <v>45.45</v>
       </c>
       <c r="H34">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>25.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C35">
-        <v>49.75</v>
+        <v>50.71</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>50.0</v>
+        <v>36.36</v>
       </c>
       <c r="H35">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="I35">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -1381,10 +1381,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>49.75</v>
+        <v>49.94</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -1393,16 +1393,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>50.0</v>
+        <v>45.45</v>
       </c>
       <c r="H36">
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>16.67</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="37">
@@ -1410,10 +1410,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>48.92</v>
+        <v>48.72</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,16 +1422,16 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G37">
-        <v>50.0</v>
+        <v>45.45</v>
       </c>
       <c r="H37">
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>11.11</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C38">
-        <v>48.88</v>
+        <v>48.72</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G38">
-        <v>40.0</v>
+        <v>45.45</v>
       </c>
       <c r="H38">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>13.89</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C39">
-        <v>48.47</v>
+        <v>47.91</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G39">
-        <v>40.0</v>
+        <v>45.45</v>
       </c>
       <c r="H39">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I39">
-        <v>77.78</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>46.8</v>
+        <v>47.47</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G40">
-        <v>40.0</v>
+        <v>36.36</v>
       </c>
       <c r="H40">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I40">
-        <v>0.0</v>
+        <v>78.38</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C41">
-        <v>46.38</v>
+        <v>46.11</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G41">
+        <v>36.36</v>
+      </c>
+      <c r="H41">
         <v>40.0</v>
       </c>
-      <c r="H41">
-        <v>0.0</v>
-      </c>
       <c r="I41">
-        <v>63.89</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C42">
-        <v>43.05</v>
+        <v>45.44</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G42">
-        <v>40.0</v>
+        <v>36.36</v>
       </c>
       <c r="H42">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I42">
-        <v>8.33</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="43">
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="C43">
-        <v>43.02</v>
+        <v>42.56</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>30.0</v>
+        <v>27.27</v>
       </c>
       <c r="H43">
         <v>40.0</v>
       </c>
       <c r="I43">
-        <v>11.11</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="44">
@@ -1613,28 +1613,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C44">
-        <v>42.6</v>
+        <v>42.33</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>30.0</v>
+        <v>36.36</v>
       </c>
       <c r="H44">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I44">
-        <v>8.33</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>9</v>
       </c>
       <c r="C45">
-        <v>42.22</v>
+        <v>41.52</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,16 +1654,16 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>40.0</v>
+        <v>36.36</v>
       </c>
       <c r="H45">
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>30</v>
       </c>
       <c r="C46">
-        <v>42.22</v>
+        <v>41.52</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1683,16 +1683,16 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>40.0</v>
+        <v>36.36</v>
       </c>
       <c r="H46">
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>21</v>
       </c>
       <c r="C47">
-        <v>41.8</v>
+        <v>41.11</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -1712,16 +1712,16 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>40.0</v>
+        <v>36.36</v>
       </c>
       <c r="H47">
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>0.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>38</v>
       </c>
       <c r="C48">
-        <v>40.93</v>
+        <v>40.26</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G48">
-        <v>30.0</v>
+        <v>27.27</v>
       </c>
       <c r="H48">
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>63.89</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>42</v>
       </c>
       <c r="C49">
-        <v>40.1</v>
+        <v>39.59</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,16 +1770,16 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G49">
-        <v>30.0</v>
+        <v>27.27</v>
       </c>
       <c r="H49">
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>25.0</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>28.78</v>
+        <v>28.69</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G50">
-        <v>10.0</v>
+        <v>9.09</v>
       </c>
       <c r="H50">
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>55.56</v>
+        <v>56.76</v>
       </c>
     </row>
   </sheetData>
@@ -1867,297 +1867,297 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I3">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I5">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>35</v>
       </c>
       <c r="H7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I8">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H10">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E11">
         <v>15</v>
@@ -2166,345 +2166,345 @@
         <v>18</v>
       </c>
       <c r="G11">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H11">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I11">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E12">
+        <v>15</v>
+      </c>
+      <c r="F12">
+        <v>18</v>
+      </c>
+      <c r="G12">
         <v>19</v>
       </c>
-      <c r="F12">
-        <v>23</v>
-      </c>
-      <c r="G12">
-        <v>39</v>
-      </c>
       <c r="H12">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G13">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I13">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>24</v>
+      </c>
+      <c r="G15">
         <v>29</v>
       </c>
-      <c r="F15">
-        <v>33</v>
-      </c>
-      <c r="G15">
-        <v>34</v>
-      </c>
       <c r="H15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I15">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G16">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H16">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I16">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G17">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H17">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I17">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H18">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G19">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H19">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I19">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>25</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G20">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H20">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I20">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E21">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G21">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H21">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C22">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <v>16</v>
+      </c>
+      <c r="F22">
         <v>20</v>
-      </c>
-      <c r="D22">
-        <v>26</v>
-      </c>
-      <c r="E22">
-        <v>29</v>
-      </c>
-      <c r="F22">
-        <v>31</v>
       </c>
       <c r="G22">
         <v>37</v>
@@ -2513,810 +2513,810 @@
         <v>49</v>
       </c>
       <c r="I22">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D23">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23">
         <v>29</v>
       </c>
       <c r="F23">
+        <v>31</v>
+      </c>
+      <c r="G23">
         <v>37</v>
       </c>
-      <c r="G23">
-        <v>47</v>
-      </c>
       <c r="H23">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I23">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G24">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H24">
         <v>48</v>
       </c>
       <c r="I24">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F25">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G25">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H25">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C26">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E26">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G26">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H26">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G27">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H27">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I27">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
         <v>18</v>
       </c>
-      <c r="E28">
-        <v>25</v>
-      </c>
       <c r="F28">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G28">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H28">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I28">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F29">
         <v>28</v>
       </c>
       <c r="G29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H29">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I29">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F30">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G30">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H30">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I30">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E31">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G31">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H31">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32">
+        <v>14</v>
+      </c>
+      <c r="F32">
+        <v>25</v>
+      </c>
+      <c r="G32">
+        <v>26</v>
+      </c>
+      <c r="H32">
+        <v>32</v>
+      </c>
+      <c r="I32">
         <v>7</v>
-      </c>
-      <c r="D32">
-        <v>14</v>
-      </c>
-      <c r="E32">
-        <v>16</v>
-      </c>
-      <c r="F32">
-        <v>37</v>
-      </c>
-      <c r="G32">
-        <v>39</v>
-      </c>
-      <c r="H32">
-        <v>47</v>
-      </c>
-      <c r="I32">
-        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G33">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H33">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I33">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F34">
+        <v>19</v>
+      </c>
+      <c r="G34">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <v>40</v>
+      </c>
+      <c r="I34">
         <v>22</v>
-      </c>
-      <c r="G34">
-        <v>40</v>
-      </c>
-      <c r="H34">
-        <v>45</v>
-      </c>
-      <c r="I34">
-        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F35">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G35">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H35">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I35">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C36">
         <v>4</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F36">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G36">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H36">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I36">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H37">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I37">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G38">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H38">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I38">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C39">
         <v>5</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E39">
+        <v>13</v>
+      </c>
+      <c r="F39">
         <v>25</v>
       </c>
-      <c r="F39">
-        <v>40</v>
-      </c>
       <c r="G39">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H39">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I39">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F40">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G40">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H40">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I40">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F41">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G41">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H41">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I41">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D42">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E42">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F42">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G42">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H42">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E43">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F43">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H43">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I43">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F44">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G44">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H44">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C45">
         <v>5</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E45">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F45">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G45">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H45">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I45">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>11</v>
       </c>
       <c r="E46">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F46">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G46">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H46">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I46">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D47">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E47">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F47">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G47">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H47">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I47">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C48">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E48">
         <v>27</v>
       </c>
       <c r="F48">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G48">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H48">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I48">
         <v>37</v>
@@ -3324,30 +3324,30 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D49">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E49">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F49">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G49">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H49">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I49">
         <v>37</v>
@@ -3355,64 +3355,64 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F50">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G50">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H50">
         <v>49</v>
       </c>
       <c r="I50">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C51">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D51">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E51">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F51">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G51">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H51">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I51">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-11 第 115000078 期；威力彩 2026-08-10 第 115000064 期</t>
+          <t>大樂透 2026-08-11 第 115000078 期；威力彩 2026-08-13 第 115000065 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.333 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,10 +3464,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.048</v>
+        <v>1.0</v>
       </c>
       <c r="D2">
-        <v>31.0</v>
+        <v>28.6</v>
       </c>
       <c r="E2">
         <v>2.4</v>
@@ -3486,10 +3486,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.048</v>
+        <v>1.0</v>
       </c>
       <c r="D3">
-        <v>31.0</v>
+        <v>28.6</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -3508,7 +3508,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D4">
         <v>21.4</v>
@@ -3530,7 +3530,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.929</v>
+        <v>0.905</v>
       </c>
       <c r="D5">
         <v>19.0</v>
@@ -3552,10 +3552,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.881</v>
+        <v>0.905</v>
       </c>
       <c r="D6">
-        <v>23.8</v>
+        <v>26.2</v>
       </c>
       <c r="E6">
         <v>2.4</v>
@@ -3648,7 +3648,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>75.74</v>
+        <v>76.16</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -3657,7 +3657,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>92.86</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>17.24</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>72.91</v>
+        <v>73.41</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -3686,7 +3686,7 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>85.71</v>
@@ -3695,7 +3695,7 @@
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4">
-        <v>71.81</v>
+        <v>70.41</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>78.57</v>
+        <v>85.71</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>27.59</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>70.26</v>
+        <v>68.93</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>78.57</v>
+        <v>71.43</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>17.24</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>69.98</v>
+        <v>67.17</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>85.71</v>
+        <v>78.57</v>
       </c>
       <c r="H6">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I6">
-        <v>13.79</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>68.49</v>
+        <v>65.67</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>57.14</v>
+        <v>78.57</v>
       </c>
       <c r="H7">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I7">
-        <v>10.34</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>68.46</v>
+        <v>63.94</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
         <v>4</v>
       </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
       <c r="G8">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H8">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I8">
-        <v>6.9</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C9">
-        <v>67.19</v>
+        <v>63.94</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
         <v>4</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>64.29</v>
+        <v>57.14</v>
       </c>
       <c r="H9">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I9">
-        <v>0.0</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>65.05</v>
+        <v>63.93</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>57.14</v>
+        <v>71.43</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>20.69</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>63.74</v>
+        <v>63.3</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>64.29</v>
+        <v>50.0</v>
       </c>
       <c r="H11">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I11">
-        <v>10.34</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>63.74</v>
+        <v>62.94</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>64.29</v>
+        <v>57.14</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>10.34</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="13">
@@ -3964,13 +3964,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C13">
-        <v>63.46</v>
+        <v>62.94</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3979,13 +3979,13 @@
         <v>2</v>
       </c>
       <c r="G13">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="14">
@@ -3993,13 +3993,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C14">
-        <v>62.46</v>
+        <v>62.93</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -4008,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>57.14</v>
+        <v>71.43</v>
       </c>
       <c r="H14">
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="15">
@@ -4022,13 +4022,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C15">
-        <v>62.46</v>
+        <v>62.69</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -4037,13 +4037,13 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>57.14</v>
+        <v>64.29</v>
       </c>
       <c r="H15">
         <v>60.0</v>
       </c>
       <c r="I15">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>62.43</v>
+        <v>62.69</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>71.43</v>
+        <v>64.29</v>
       </c>
       <c r="H16">
         <v>60.0</v>
       </c>
       <c r="I16">
-        <v>0.0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="17">
@@ -4080,13 +4080,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C17">
-        <v>62.19</v>
+        <v>62.43</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>64.29</v>
+        <v>71.43</v>
       </c>
       <c r="H17">
         <v>60.0</v>
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>61.94</v>
+        <v>62.19</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
         <v>0</v>
       </c>
-      <c r="F18">
-        <v>29</v>
-      </c>
       <c r="G18">
-        <v>57.14</v>
+        <v>64.29</v>
       </c>
       <c r="H18">
+        <v>60.0</v>
+      </c>
+      <c r="I18">
         <v>0.0</v>
-      </c>
-      <c r="I18">
-        <v>100.0</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>59.12</v>
+        <v>61.8</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>85.71</v>
+        <v>50.0</v>
       </c>
       <c r="H19">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="I19">
-        <v>41.38</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C20">
-        <v>58.71</v>
+        <v>59.41</v>
       </c>
       <c r="D20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>78.57</v>
+        <v>85.71</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I20">
-        <v>6.9</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="21">
@@ -4196,13 +4196,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C21">
-        <v>58.49</v>
+        <v>59.17</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -4211,13 +4211,13 @@
         <v>3</v>
       </c>
       <c r="G21">
-        <v>57.14</v>
+        <v>78.57</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>10.34</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="22">
@@ -4225,10 +4225,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C22">
-        <v>57.98</v>
+        <v>58.94</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22">
         <v>57.14</v>
@@ -4246,7 +4246,7 @@
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>6.9</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C23">
-        <v>57.54</v>
+        <v>58.3</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G23">
+        <v>50.0</v>
+      </c>
+      <c r="H23">
+        <v>0.0</v>
+      </c>
+      <c r="I23">
         <v>100.0</v>
-      </c>
-      <c r="H23">
-        <v>20.0</v>
-      </c>
-      <c r="I23">
-        <v>27.59</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C24">
-        <v>56.84</v>
+        <v>57.9</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <v>42.86</v>
+        <v>100.0</v>
       </c>
       <c r="H24">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>17.24</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C25">
-        <v>54.22</v>
+        <v>56.94</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>78.57</v>
+        <v>57.14</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I25">
-        <v>10.34</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C26">
-        <v>53.4</v>
+        <v>54.67</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>42.86</v>
+        <v>78.57</v>
       </c>
       <c r="H26">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>27.59</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>50.21</v>
+        <v>53.76</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>35.71</v>
+        <v>42.86</v>
       </c>
       <c r="H27">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I27">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C28">
-        <v>49.78</v>
+        <v>50.71</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>42.86</v>
+        <v>35.71</v>
       </c>
       <c r="H28">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I28">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>48.82</v>
+        <v>46.21</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>50.0</v>
+        <v>35.71</v>
       </c>
       <c r="H29">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I29">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="30">
@@ -4460,7 +4460,7 @@
         <v>26</v>
       </c>
       <c r="C30">
-        <v>45.73</v>
+        <v>46.21</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4469,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>35.71</v>
@@ -4478,7 +4478,7 @@
         <v>40.0</v>
       </c>
       <c r="I30">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C31">
-        <v>45.56</v>
+        <v>45.71</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>35.71</v>
       </c>
       <c r="H31">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>68.97</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C32">
-        <v>45.21</v>
+        <v>42.67</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G32">
-        <v>35.71</v>
+        <v>28.57</v>
       </c>
       <c r="H32">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C33">
-        <v>44.27</v>
+        <v>42.67</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>28.57</v>
       </c>
       <c r="H33">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I33">
-        <v>20.69</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C34">
-        <v>43.41</v>
+        <v>40.63</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
       <c r="H34">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>48.28</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>40.21</v>
+      </c>
+      <c r="D35">
         <v>5</v>
-      </c>
-      <c r="C35">
-        <v>42.38</v>
-      </c>
-      <c r="D35">
-        <v>4</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>28.57</v>
+        <v>35.71</v>
       </c>
       <c r="H35">
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>41.38</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>42.38</v>
+        <v>40.21</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>28.57</v>
+        <v>35.71</v>
       </c>
       <c r="H36">
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>41.38</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -4660,10 +4660,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C37">
-        <v>42.03</v>
+        <v>38.67</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G37">
         <v>28.57</v>
@@ -4681,7 +4681,7 @@
         <v>0.0</v>
       </c>
       <c r="I37">
-        <v>72.41</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>37.65</v>
+        <v>38.13</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,7 +4701,7 @@
         <v>2</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38">
         <v>21.43</v>
@@ -4710,7 +4710,7 @@
         <v>40.0</v>
       </c>
       <c r="I38">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>36.78</v>
+        <v>37.13</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>21.43</v>
@@ -4739,7 +4739,7 @@
         <v>20.0</v>
       </c>
       <c r="I39">
-        <v>31.03</v>
+        <v>33.33</v>
       </c>
     </row>
   </sheetData>
@@ -4798,123 +4798,123 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>26</v>
+      </c>
+      <c r="H4">
+        <v>33</v>
+      </c>
+      <c r="I4">
         <v>4</v>
-      </c>
-      <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>26</v>
-      </c>
-      <c r="G4">
-        <v>34</v>
-      </c>
-      <c r="H4">
-        <v>36</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H5">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -4922,30 +4922,30 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
         <v>19</v>
       </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>31</v>
-      </c>
       <c r="G6">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -4953,30 +4953,30 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -4984,24 +4984,24 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>13</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>29</v>
@@ -5010,97 +5010,97 @@
         <v>31</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>13</v>
+      </c>
+      <c r="F9">
         <v>23</v>
       </c>
-      <c r="E9">
-        <v>25</v>
-      </c>
-      <c r="F9">
+      <c r="G9">
         <v>29</v>
       </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
       <c r="H9">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10">
+        <v>25</v>
+      </c>
+      <c r="F10">
         <v>29</v>
       </c>
-      <c r="F10">
-        <v>32</v>
-      </c>
       <c r="G10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G11">
         <v>35</v>
       </c>
       <c r="H11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -5108,402 +5108,402 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G13">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H13">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
         <v>6</v>
       </c>
-      <c r="D15">
-        <v>10</v>
-      </c>
       <c r="E15">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G15">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G16">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H16">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>18</v>
+      </c>
+      <c r="H18">
+        <v>23</v>
+      </c>
+      <c r="I18">
         <v>4</v>
-      </c>
-      <c r="D18">
-        <v>17</v>
-      </c>
-      <c r="E18">
-        <v>19</v>
-      </c>
-      <c r="F18">
-        <v>25</v>
-      </c>
-      <c r="G18">
-        <v>28</v>
-      </c>
-      <c r="H18">
-        <v>29</v>
-      </c>
-      <c r="I18">
-        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H20">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E21">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G21">
         <v>28</v>
       </c>
       <c r="H21">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G22">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H22">
         <v>35</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E23">
+        <v>9</v>
+      </c>
+      <c r="F23">
+        <v>15</v>
+      </c>
+      <c r="G23">
         <v>24</v>
       </c>
-      <c r="F23">
-        <v>31</v>
-      </c>
-      <c r="G23">
-        <v>34</v>
-      </c>
       <c r="H23">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F24">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G24">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H24">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I24">
         <v>3</v>
@@ -5511,554 +5511,554 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F25">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G25">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H25">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F26">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G26">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H26">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C27">
         <v>6</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F27">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G27">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H27">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G28">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H28">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D29">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G29">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H29">
         <v>38</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F30">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H30">
         <v>38</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G31">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H31">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I31">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <v>19</v>
+      </c>
+      <c r="G32">
+        <v>27</v>
+      </c>
+      <c r="H32">
+        <v>30</v>
+      </c>
+      <c r="I32">
         <v>8</v>
-      </c>
-      <c r="E32">
-        <v>27</v>
-      </c>
-      <c r="F32">
-        <v>33</v>
-      </c>
-      <c r="G32">
-        <v>35</v>
-      </c>
-      <c r="H32">
-        <v>38</v>
-      </c>
-      <c r="I32">
-        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G33">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F34">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G34">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H34">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I34">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E35">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F35">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G35">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H35">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G36">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H36">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F37">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H37">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E38">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F38">
         <v>27</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C39">
         <v>5</v>
       </c>
       <c r="D39">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F39">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G39">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H39">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E40">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G40">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H40">
         <v>34</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
         <v>13</v>
       </c>
-      <c r="D41">
-        <v>14</v>
-      </c>
       <c r="E41">
+        <v>21</v>
+      </c>
+      <c r="F41">
         <v>22</v>
       </c>
-      <c r="F41">
-        <v>28</v>
-      </c>
       <c r="G41">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H41">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D42">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F42">
         <v>28</v>
       </c>
       <c r="G42">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H42">
         <v>38</v>
@@ -6069,58 +6069,58 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
         <v>9</v>
       </c>
-      <c r="D43">
-        <v>13</v>
-      </c>
       <c r="E43">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F43">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G43">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H43">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C44">
+        <v>9</v>
+      </c>
+      <c r="D44">
+        <v>13</v>
+      </c>
+      <c r="E44">
         <v>14</v>
       </c>
-      <c r="D44">
-        <v>26</v>
-      </c>
-      <c r="E44">
-        <v>28</v>
-      </c>
       <c r="F44">
+        <v>18</v>
+      </c>
+      <c r="G44">
         <v>31</v>
-      </c>
-      <c r="G44">
-        <v>32</v>
       </c>
       <c r="H44">
         <v>34</v>
@@ -6131,61 +6131,61 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E45">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F45">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G45">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H45">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I45">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E46">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F46">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G46">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H46">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I46">
         <v>8</v>
@@ -6193,15 +6193,15 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>11</v>
@@ -6210,106 +6210,106 @@
         <v>14</v>
       </c>
       <c r="F47">
+        <v>17</v>
+      </c>
+      <c r="G47">
+        <v>29</v>
+      </c>
+      <c r="H47">
         <v>32</v>
       </c>
-      <c r="G47">
-        <v>36</v>
-      </c>
-      <c r="H47">
-        <v>38</v>
-      </c>
       <c r="I47">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C48">
         <v>7</v>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F48">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G48">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H48">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000017</v>
+        <v>115000018</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E49">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F49">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G49">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H49">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000016</v>
+        <v>115000017</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F50">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G50">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H50">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I50">
         <v>2</v>
@@ -6317,33 +6317,33 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000015</v>
+        <v>115000016</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51">
+        <v>13</v>
+      </c>
+      <c r="F51">
+        <v>24</v>
+      </c>
+      <c r="G51">
+        <v>31</v>
+      </c>
+      <c r="H51">
+        <v>35</v>
+      </c>
+      <c r="I51">
         <v>2</v>
-      </c>
-      <c r="D51">
-        <v>3</v>
-      </c>
-      <c r="E51">
-        <v>6</v>
-      </c>
-      <c r="F51">
-        <v>12</v>
-      </c>
-      <c r="G51">
-        <v>23</v>
-      </c>
-      <c r="H51">
-        <v>27</v>
-      </c>
-      <c r="I51">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-11 第 115000078 期；威力彩 2026-08-13 第 115000065 期</t>
+          <t>大樂透 2026-08-14 第 115000079 期；威力彩 2026-08-13 第 115000065 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.096 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.143 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,10 +214,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.81</v>
+        <v>0.857</v>
       </c>
       <c r="D2">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="E2">
         <v>0.0</v>
@@ -236,10 +236,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.786</v>
+        <v>0.833</v>
       </c>
       <c r="D3">
-        <v>19.0</v>
+        <v>21.4</v>
       </c>
       <c r="E3">
         <v>0.0</v>
@@ -251,7 +251,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>隨機基準</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B4">
@@ -261,26 +261,26 @@
         <v>0.714</v>
       </c>
       <c r="D4">
-        <v>11.9</v>
+        <v>21.4</v>
       </c>
       <c r="E4">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="D5">
         <v>19.0</v>
@@ -295,23 +295,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>隨機基準</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="D6">
-        <v>16.7</v>
+        <v>11.9</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>0.0</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -324,7 +324,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="D7">
         <v>11.9</v>
@@ -395,28 +395,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>73.05</v>
+        <v>71.85</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>100.0</v>
+        <v>58.33</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,13 +424,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>72.75</v>
+        <v>71.4</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -439,13 +439,13 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>5.41</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C4">
-        <v>72.62</v>
+        <v>66.05</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>72.73</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I4">
-        <v>2.7</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>68.05</v>
+        <v>65.85</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>100.0</v>
+        <v>58.33</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>67.28</v>
+        <v>65.6</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>54.55</v>
+        <v>100.0</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>8.11</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>66.94</v>
+        <v>65.35</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="H7">
         <v>80.0</v>
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C8">
-        <v>65.59</v>
+        <v>62.95</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>63.64</v>
+        <v>75.0</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>24.32</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9">
@@ -598,10 +598,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>64.12</v>
+        <v>62.45</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -613,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="G9">
-        <v>81.82</v>
+        <v>75.0</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>10.81</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>63.71</v>
+        <v>62.35</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>81.82</v>
+        <v>58.33</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>8.11</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>63.58</v>
+        <v>62.0</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -668,16 +668,16 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>90.91</v>
+        <v>83.33</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>5.41</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="12">
@@ -685,13 +685,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C12">
-        <v>63.44</v>
+        <v>61.85</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -700,13 +700,13 @@
         <v>3</v>
       </c>
       <c r="G12">
-        <v>72.73</v>
+        <v>58.33</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>8.11</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>62.75</v>
+        <v>60.95</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>63.64</v>
+        <v>75.0</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>5.41</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="14">
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C14">
-        <v>62.5</v>
+        <v>60.55</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>81.82</v>
+        <v>91.67</v>
       </c>
       <c r="H14">
         <v>60.0</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>61.4</v>
+        <v>60.35</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -784,16 +784,16 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>29.73</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C16">
-        <v>60.19</v>
+        <v>60.35</v>
       </c>
       <c r="D16">
         <v>7</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="H16">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I16">
-        <v>21.62</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>59.31</v>
+        <v>59.85</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>21.62</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C18">
-        <v>58.18</v>
+        <v>59.2</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G18">
-        <v>90.91</v>
+        <v>50.0</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>2.7</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C19">
-        <v>58.09</v>
+        <v>56.35</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="H19">
+        <v>20.0</v>
+      </c>
+      <c r="I19">
         <v>40.0</v>
-      </c>
-      <c r="I19">
-        <v>13.51</v>
       </c>
     </row>
     <row r="20">
@@ -920,25 +920,25 @@
         <v>49</v>
       </c>
       <c r="C20">
-        <v>57.75</v>
+        <v>56.2</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>63.64</v>
+        <v>50.0</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>5.41</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C21">
-        <v>57.28</v>
+        <v>55.7</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G21">
-        <v>54.55</v>
+        <v>50.0</v>
       </c>
       <c r="H21">
+        <v>20.0</v>
+      </c>
+      <c r="I21">
         <v>40.0</v>
-      </c>
-      <c r="I21">
-        <v>8.11</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C22">
-        <v>56.4</v>
+        <v>55.35</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="H22">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>29.73</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="C23">
-        <v>55.88</v>
+        <v>55.25</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="H23">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
       <c r="I23">
-        <v>100.0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C24">
-        <v>55.88</v>
+        <v>55.2</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G24">
-        <v>45.45</v>
+        <v>50.0</v>
       </c>
       <c r="H24">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="25">
@@ -1062,10 +1062,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C25">
-        <v>55.05</v>
+        <v>54.85</v>
       </c>
       <c r="D25">
         <v>7</v>
@@ -1074,16 +1074,16 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="H25">
         <v>0.0</v>
       </c>
       <c r="I25">
-        <v>54.05</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="26">
@@ -1094,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>54.78</v>
+        <v>54.35</v>
       </c>
       <c r="D26">
         <v>7</v>
@@ -1103,16 +1103,16 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>18.92</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C27">
-        <v>54.24</v>
+        <v>53.7</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G27">
-        <v>63.64</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I27">
-        <v>48.65</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C28">
-        <v>53.9</v>
+        <v>53.35</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G28">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="H28">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28">
-        <v>18.92</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="29">
@@ -1181,7 +1181,7 @@
         <v>43</v>
       </c>
       <c r="C29">
-        <v>53.56</v>
+        <v>52.85</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -1190,16 +1190,16 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="H29">
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>10.81</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C30">
-        <v>53.02</v>
+        <v>52.7</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30">
-        <v>63.64</v>
+        <v>50.0</v>
       </c>
       <c r="H30">
         <v>0.0</v>
       </c>
       <c r="I30">
-        <v>40.54</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C31">
-        <v>52.28</v>
+        <v>51.75</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>54.55</v>
+        <v>41.67</v>
       </c>
       <c r="H31">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>8.11</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C32">
-        <v>52.15</v>
+        <v>51.7</v>
       </c>
       <c r="D32">
         <v>6</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>54.55</v>
+        <v>50.0</v>
       </c>
       <c r="H32">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>40.54</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>52.1</v>
+        <v>50.75</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,16 +1306,16 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="H33">
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>8.11</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C34">
-        <v>51.29</v>
+        <v>50.3</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34">
-        <v>45.45</v>
+        <v>33.33</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I34">
-        <v>2.7</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>50.71</v>
+        <v>50.25</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="H35">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>49.94</v>
+        <v>49.8</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G36">
-        <v>45.45</v>
+        <v>33.33</v>
       </c>
       <c r="H36">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I36">
-        <v>27.03</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>48.72</v>
+        <v>49.7</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>45.45</v>
+        <v>50.0</v>
       </c>
       <c r="H37">
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>18.92</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -1439,10 +1439,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>48.72</v>
+        <v>48.75</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -1451,16 +1451,16 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="H38">
         <v>20.0</v>
       </c>
       <c r="I38">
-        <v>18.92</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="39">
@@ -1471,7 +1471,7 @@
         <v>27</v>
       </c>
       <c r="C39">
-        <v>47.91</v>
+        <v>47.75</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -1480,16 +1480,16 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G39">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="H39">
         <v>20.0</v>
       </c>
       <c r="I39">
-        <v>13.51</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="40">
@@ -1497,10 +1497,10 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C40">
-        <v>47.47</v>
+        <v>47.3</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1509,16 +1509,16 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G40">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="H40">
         <v>0.0</v>
       </c>
       <c r="I40">
-        <v>78.38</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="41">
@@ -1529,7 +1529,7 @@
         <v>41</v>
       </c>
       <c r="C41">
-        <v>46.11</v>
+        <v>45.8</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,16 +1538,16 @@
         <v>2</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="H41">
         <v>40.0</v>
       </c>
       <c r="I41">
-        <v>2.7</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C42">
-        <v>45.44</v>
+        <v>43.8</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G42">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="H42">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I42">
-        <v>64.86</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="43">
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="C43">
-        <v>42.56</v>
+        <v>42.85</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G43">
-        <v>27.27</v>
+        <v>25.0</v>
       </c>
       <c r="H43">
         <v>40.0</v>
       </c>
       <c r="I43">
-        <v>13.51</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="44">
@@ -1613,28 +1613,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C44">
-        <v>42.33</v>
+        <v>42.35</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G44">
-        <v>36.36</v>
+        <v>25.0</v>
       </c>
       <c r="H44">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I44">
-        <v>10.81</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="45">
@@ -1642,10 +1642,10 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C45">
-        <v>41.52</v>
+        <v>42.3</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,16 +1654,16 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G45">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="H45">
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>5.41</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="46">
@@ -1671,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C46">
-        <v>41.52</v>
+        <v>41.3</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1683,16 +1683,16 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="H46">
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>5.41</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>21</v>
       </c>
       <c r="C47">
-        <v>41.11</v>
+        <v>40.8</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -1712,16 +1712,16 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="H47">
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>2.7</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C48">
-        <v>40.26</v>
+        <v>40.35</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G48">
-        <v>27.27</v>
+        <v>25.0</v>
       </c>
       <c r="H48">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I48">
-        <v>64.86</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="49">
@@ -1758,10 +1758,10 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C49">
-        <v>39.59</v>
+        <v>36.35</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,16 +1770,16 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>27.27</v>
+        <v>25.0</v>
       </c>
       <c r="H49">
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>27.03</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>28.69</v>
+        <v>30.95</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G50">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="H50">
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>56.76</v>
+        <v>73.33</v>
       </c>
     </row>
   </sheetData>
@@ -1867,328 +1867,328 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H5">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I6">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G8">
         <v>35</v>
       </c>
       <c r="H8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G9">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H10">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H11">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>15</v>
@@ -2197,345 +2197,345 @@
         <v>18</v>
       </c>
       <c r="G12">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H12">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I12">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13">
+        <v>15</v>
+      </c>
+      <c r="F13">
+        <v>18</v>
+      </c>
+      <c r="G13">
         <v>19</v>
       </c>
-      <c r="F13">
-        <v>23</v>
-      </c>
-      <c r="G13">
-        <v>39</v>
-      </c>
       <c r="H13">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I13">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G15">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H15">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>24</v>
+      </c>
+      <c r="G16">
         <v>29</v>
       </c>
-      <c r="F16">
-        <v>33</v>
-      </c>
-      <c r="G16">
-        <v>34</v>
-      </c>
       <c r="H16">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I16">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G17">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I17">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H18">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I18">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H19">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G20">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H20">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I20">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>25</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G21">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H21">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I21">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G22">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H22">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C23">
+        <v>8</v>
+      </c>
+      <c r="D23">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>16</v>
+      </c>
+      <c r="F23">
         <v>20</v>
-      </c>
-      <c r="D23">
-        <v>26</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-      <c r="F23">
-        <v>31</v>
       </c>
       <c r="G23">
         <v>37</v>
@@ -2544,810 +2544,810 @@
         <v>49</v>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24">
         <v>29</v>
       </c>
       <c r="F24">
+        <v>31</v>
+      </c>
+      <c r="G24">
         <v>37</v>
       </c>
-      <c r="G24">
-        <v>47</v>
-      </c>
       <c r="H24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I24">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G25">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H25">
         <v>48</v>
       </c>
       <c r="I25">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D26">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F26">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G26">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H26">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I26">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G27">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H27">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G28">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H28">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I28">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D29">
+        <v>12</v>
+      </c>
+      <c r="E29">
         <v>18</v>
       </c>
-      <c r="E29">
-        <v>25</v>
-      </c>
       <c r="F29">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G29">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H29">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I29">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F30">
         <v>28</v>
       </c>
       <c r="G30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I30">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E31">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F31">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G31">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H31">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I31">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E32">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G32">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H32">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I32">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>25</v>
+      </c>
+      <c r="G33">
+        <v>26</v>
+      </c>
+      <c r="H33">
+        <v>32</v>
+      </c>
+      <c r="I33">
         <v>7</v>
-      </c>
-      <c r="D33">
-        <v>14</v>
-      </c>
-      <c r="E33">
-        <v>16</v>
-      </c>
-      <c r="F33">
-        <v>37</v>
-      </c>
-      <c r="G33">
-        <v>39</v>
-      </c>
-      <c r="H33">
-        <v>47</v>
-      </c>
-      <c r="I33">
-        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E34">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G34">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H34">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I34">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F35">
+        <v>19</v>
+      </c>
+      <c r="G35">
+        <v>20</v>
+      </c>
+      <c r="H35">
+        <v>40</v>
+      </c>
+      <c r="I35">
         <v>22</v>
-      </c>
-      <c r="G35">
-        <v>40</v>
-      </c>
-      <c r="H35">
-        <v>45</v>
-      </c>
-      <c r="I35">
-        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G36">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H36">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I36">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F37">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G37">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H37">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I37">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H38">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I38">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G39">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H39">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I39">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C40">
         <v>5</v>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E40">
+        <v>13</v>
+      </c>
+      <c r="F40">
         <v>25</v>
       </c>
-      <c r="F40">
-        <v>40</v>
-      </c>
       <c r="G40">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H40">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I40">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F41">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G41">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H41">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I41">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F42">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G42">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H42">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I42">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E43">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F43">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G43">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H43">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I43">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E44">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F44">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H44">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I44">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E45">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F45">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G45">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H45">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C46">
         <v>5</v>
       </c>
       <c r="D46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E46">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F46">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G46">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H46">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I46">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>11</v>
       </c>
       <c r="E47">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F47">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G47">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H47">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I47">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D48">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F48">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G48">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H48">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I48">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C49">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D49">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E49">
         <v>27</v>
       </c>
       <c r="F49">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G49">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H49">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I49">
         <v>37</v>
@@ -3355,30 +3355,30 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E50">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F50">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G50">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H50">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I50">
         <v>37</v>
@@ -3386,33 +3386,33 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E51">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F51">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G51">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H51">
         <v>49</v>
       </c>
       <c r="I51">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-14 第 115000079 期；威力彩 2026-08-13 第 115000065 期</t>
+          <t>大樂透 2026-08-14 第 115000079 期；威力彩 2026-08-17 第 115000066 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 13, 29, 31, 35, 38</t>
+          <t>9, 14, 19, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.333 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.357 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,10 +3464,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.0</v>
+        <v>1.024</v>
       </c>
       <c r="D2">
-        <v>28.6</v>
+        <v>31.0</v>
       </c>
       <c r="E2">
         <v>2.4</v>
@@ -3486,10 +3486,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.0</v>
+        <v>1.024</v>
       </c>
       <c r="D3">
-        <v>28.6</v>
+        <v>31.0</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -3508,7 +3508,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.929</v>
+        <v>0.952</v>
       </c>
       <c r="D4">
         <v>21.4</v>
@@ -3523,20 +3523,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="D5">
-        <v>19.0</v>
+        <v>28.6</v>
       </c>
       <c r="E5">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3545,20 +3545,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.905</v>
+        <v>0.929</v>
       </c>
       <c r="D6">
-        <v>26.2</v>
+        <v>19.0</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3648,7 +3648,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>76.16</v>
+        <v>74.69</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -3657,16 +3657,16 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>20.0</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="3">
@@ -3677,25 +3677,25 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>73.41</v>
+        <v>72.07</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>85.71</v>
+        <v>73.33</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>3.33</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="4">
@@ -3706,25 +3706,25 @@
         <v>35</v>
       </c>
       <c r="C4">
-        <v>70.41</v>
+        <v>71.2</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>85.71</v>
+        <v>80.0</v>
       </c>
       <c r="H4">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I4">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -3735,7 +3735,7 @@
         <v>22</v>
       </c>
       <c r="C5">
-        <v>68.93</v>
+        <v>67.94</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -3744,16 +3744,16 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>71.43</v>
+        <v>66.67</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>10.0</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>67.17</v>
+        <v>66.1</v>
       </c>
       <c r="D6">
         <v>11</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>78.57</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I6">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>65.67</v>
+        <v>66.0</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>78.57</v>
+        <v>66.67</v>
       </c>
       <c r="H7">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>63.94</v>
+        <v>65.84</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>13.33</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>63.94</v>
+        <v>64.39</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>13.33</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C10">
-        <v>63.93</v>
+        <v>63.22</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>71.43</v>
+        <v>53.33</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>10.0</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>63.3</v>
+        <v>63.22</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>50.0</v>
+        <v>53.33</v>
       </c>
       <c r="H11">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I11">
-        <v>0.0</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>62.94</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>6.67</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="13">
@@ -3964,10 +3964,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>62.94</v>
+        <v>62.25</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -3976,16 +3976,16 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>6.67</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C14">
-        <v>62.93</v>
+        <v>62.25</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>71.43</v>
+        <v>53.33</v>
       </c>
       <c r="H14">
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>3.33</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="15">
@@ -4022,13 +4022,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>62.69</v>
+        <v>61.28</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -4037,13 +4037,13 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>64.29</v>
+        <v>53.33</v>
       </c>
       <c r="H15">
         <v>60.0</v>
       </c>
       <c r="I15">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>62.69</v>
+        <v>58.22</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>64.29</v>
+        <v>53.33</v>
       </c>
       <c r="H16">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I16">
-        <v>3.33</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C17">
-        <v>62.43</v>
+        <v>58.03</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>71.43</v>
+        <v>73.33</v>
       </c>
       <c r="H17">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I17">
-        <v>0.0</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>62.19</v>
+        <v>57.97</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>64.29</v>
+        <v>80.0</v>
       </c>
       <c r="H18">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I18">
-        <v>0.0</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C19">
-        <v>61.8</v>
+        <v>57.3</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G19">
-        <v>50.0</v>
+        <v>46.67</v>
       </c>
       <c r="H19">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="I19">
-        <v>23.33</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C20">
-        <v>59.41</v>
+        <v>56.97</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>85.71</v>
+        <v>66.67</v>
       </c>
       <c r="H20">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>43.33</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>59.17</v>
+        <v>56.87</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>78.57</v>
+        <v>60.0</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>10.0</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C22">
-        <v>58.94</v>
+        <v>56.5</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>57.14</v>
+        <v>100.0</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>13.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>58.3</v>
+        <v>56.28</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>50.0</v>
+        <v>53.33</v>
       </c>
       <c r="H23">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>100.0</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>57.9</v>
+        <v>56.17</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>100.0</v>
+        <v>46.67</v>
       </c>
       <c r="H24">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I24">
-        <v>30.0</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>56.94</v>
+        <v>53.88</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>57.14</v>
+        <v>40.0</v>
       </c>
       <c r="H25">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="26">
@@ -4344,7 +4344,7 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>54.67</v>
+        <v>53.52</v>
       </c>
       <c r="D26">
         <v>11</v>
@@ -4353,16 +4353,16 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>78.57</v>
+        <v>73.33</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>13.33</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C27">
-        <v>53.76</v>
+        <v>50.47</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
         <v>2</v>
       </c>
-      <c r="F27">
-        <v>9</v>
-      </c>
       <c r="G27">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="H27">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I27">
-        <v>30.0</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>50.71</v>
+        <v>48.24</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>35.71</v>
+        <v>40.0</v>
       </c>
       <c r="H28">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I28">
-        <v>3.33</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>46.21</v>
+        <v>45.95</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -4440,16 +4440,16 @@
         <v>2</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H29">
         <v>40.0</v>
       </c>
       <c r="I29">
-        <v>6.67</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="30">
@@ -4460,7 +4460,7 @@
         <v>26</v>
       </c>
       <c r="C30">
-        <v>46.21</v>
+        <v>45.95</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4469,16 +4469,16 @@
         <v>2</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H30">
         <v>40.0</v>
       </c>
       <c r="I30">
-        <v>6.67</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="31">
@@ -4489,7 +4489,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>45.71</v>
+        <v>45.47</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,16 +4498,16 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H31">
         <v>40.0</v>
       </c>
       <c r="I31">
-        <v>3.33</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="32">
@@ -4518,25 +4518,25 @@
         <v>5</v>
       </c>
       <c r="C32">
-        <v>42.67</v>
+        <v>44.5</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I32">
-        <v>43.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>16</v>
       </c>
       <c r="C33">
-        <v>42.67</v>
+        <v>42.38</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -4556,16 +4556,16 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H33">
         <v>20.0</v>
       </c>
       <c r="I33">
-        <v>43.33</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="34">
@@ -4576,7 +4576,7 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>40.63</v>
+        <v>40.57</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -4585,16 +4585,16 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34">
-        <v>21.43</v>
+        <v>20.0</v>
       </c>
       <c r="H34">
         <v>40.0</v>
       </c>
       <c r="I34">
-        <v>23.33</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="35">
@@ -4605,7 +4605,7 @@
         <v>1</v>
       </c>
       <c r="C35">
-        <v>40.21</v>
+        <v>39.98</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -4614,16 +4614,16 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H35">
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="36">
@@ -4634,7 +4634,7 @@
         <v>3</v>
       </c>
       <c r="C36">
-        <v>40.21</v>
+        <v>39.98</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -4643,16 +4643,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H36">
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>0.0</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="37">
@@ -4663,25 +4663,25 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>38.67</v>
+        <v>39.5</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
         <v>0</v>
       </c>
-      <c r="F37">
-        <v>15</v>
-      </c>
       <c r="G37">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="H37">
+        <v>20.0</v>
+      </c>
+      <c r="I37">
         <v>0.0</v>
-      </c>
-      <c r="I37">
-        <v>50.0</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C38">
-        <v>38.13</v>
+        <v>37.02</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G38">
-        <v>21.43</v>
+        <v>20.0</v>
       </c>
       <c r="H38">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>6.67</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="39">
@@ -4718,10 +4718,10 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C39">
-        <v>37.13</v>
+        <v>33.15</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,16 +4730,16 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>21.43</v>
+        <v>20.0</v>
       </c>
       <c r="H39">
         <v>20.0</v>
       </c>
       <c r="I39">
-        <v>33.33</v>
+        <v>9.68</v>
       </c>
     </row>
   </sheetData>
@@ -4798,154 +4798,154 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>33</v>
+      </c>
+      <c r="I5">
         <v>4</v>
-      </c>
-      <c r="D5">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>26</v>
-      </c>
-      <c r="G5">
-        <v>34</v>
-      </c>
-      <c r="H5">
-        <v>36</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -4953,30 +4953,30 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
         <v>19</v>
       </c>
-      <c r="D7">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>31</v>
-      </c>
       <c r="G7">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -4984,30 +4984,30 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H8">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -5015,24 +5015,24 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>13</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G9">
         <v>29</v>
@@ -5041,97 +5041,97 @@
         <v>31</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>13</v>
+      </c>
+      <c r="F10">
         <v>23</v>
       </c>
-      <c r="E10">
-        <v>25</v>
-      </c>
-      <c r="F10">
+      <c r="G10">
         <v>29</v>
       </c>
-      <c r="G10">
-        <v>34</v>
-      </c>
       <c r="H10">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11">
+        <v>25</v>
+      </c>
+      <c r="F11">
         <v>29</v>
       </c>
-      <c r="F11">
-        <v>32</v>
-      </c>
       <c r="G11">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>35</v>
       </c>
       <c r="H12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -5139,402 +5139,402 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G13">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G15">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
         <v>6</v>
       </c>
-      <c r="D16">
-        <v>10</v>
-      </c>
       <c r="E16">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G17">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G18">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>9</v>
+      </c>
+      <c r="F19">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
+      </c>
+      <c r="H19">
+        <v>23</v>
+      </c>
+      <c r="I19">
         <v>4</v>
-      </c>
-      <c r="D19">
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <v>19</v>
-      </c>
-      <c r="F19">
-        <v>25</v>
-      </c>
-      <c r="G19">
-        <v>28</v>
-      </c>
-      <c r="H19">
-        <v>29</v>
-      </c>
-      <c r="I19">
-        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H20">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G21">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H21">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G22">
         <v>28</v>
       </c>
       <c r="H22">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G23">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H23">
         <v>35</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E24">
+        <v>9</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
         <v>24</v>
       </c>
-      <c r="F24">
-        <v>31</v>
-      </c>
-      <c r="G24">
-        <v>34</v>
-      </c>
       <c r="H24">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F25">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G25">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H25">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I25">
         <v>3</v>
@@ -5542,554 +5542,554 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G26">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H26">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C27">
         <v>6</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H27">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F28">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G28">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H28">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I28">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D29">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G29">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H29">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G30">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H30">
         <v>38</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H31">
         <v>38</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E32">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G32">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H32">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I32">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>19</v>
+      </c>
+      <c r="G33">
+        <v>27</v>
+      </c>
+      <c r="H33">
+        <v>30</v>
+      </c>
+      <c r="I33">
         <v>8</v>
-      </c>
-      <c r="E33">
-        <v>27</v>
-      </c>
-      <c r="F33">
-        <v>33</v>
-      </c>
-      <c r="G33">
-        <v>35</v>
-      </c>
-      <c r="H33">
-        <v>38</v>
-      </c>
-      <c r="I33">
-        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G34">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H34">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G35">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H35">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I35">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F36">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G36">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H36">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E37">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G37">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H37">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G38">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H38">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E39">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F39">
         <v>27</v>
       </c>
       <c r="G39">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C40">
         <v>5</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F40">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G40">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H40">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E41">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G41">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H41">
         <v>34</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
         <v>13</v>
       </c>
-      <c r="D42">
-        <v>14</v>
-      </c>
       <c r="E42">
+        <v>21</v>
+      </c>
+      <c r="F42">
         <v>22</v>
       </c>
-      <c r="F42">
-        <v>28</v>
-      </c>
       <c r="G42">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H42">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F43">
         <v>28</v>
       </c>
       <c r="G43">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H43">
         <v>38</v>
@@ -6100,58 +6100,58 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
         <v>9</v>
       </c>
-      <c r="D44">
-        <v>13</v>
-      </c>
       <c r="E44">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F44">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G44">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H44">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45">
+        <v>13</v>
+      </c>
+      <c r="E45">
         <v>14</v>
       </c>
-      <c r="D45">
-        <v>26</v>
-      </c>
-      <c r="E45">
-        <v>28</v>
-      </c>
       <c r="F45">
+        <v>18</v>
+      </c>
+      <c r="G45">
         <v>31</v>
-      </c>
-      <c r="G45">
-        <v>32</v>
       </c>
       <c r="H45">
         <v>34</v>
@@ -6162,61 +6162,61 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E46">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F46">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G46">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H46">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I46">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F47">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G47">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H47">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I47">
         <v>8</v>
@@ -6224,15 +6224,15 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>11</v>
@@ -6241,106 +6241,106 @@
         <v>14</v>
       </c>
       <c r="F48">
+        <v>17</v>
+      </c>
+      <c r="G48">
+        <v>29</v>
+      </c>
+      <c r="H48">
         <v>32</v>
       </c>
-      <c r="G48">
-        <v>36</v>
-      </c>
-      <c r="H48">
-        <v>38</v>
-      </c>
       <c r="I48">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E49">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G49">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H49">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000017</v>
+        <v>115000018</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E50">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F50">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G50">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H50">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000016</v>
+        <v>115000017</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E51">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G51">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H51">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I51">
         <v>2</v>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-14 第 115000079 期；威力彩 2026-08-17 第 115000066 期</t>
+          <t>大樂透 2026-08-18 第 115000080 期；威力彩 2026-08-17 第 115000066 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.143 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.215 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,10 +214,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.857</v>
+        <v>0.905</v>
       </c>
       <c r="D2">
-        <v>23.8</v>
+        <v>26.2</v>
       </c>
       <c r="E2">
         <v>0.0</v>
@@ -236,10 +236,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.833</v>
+        <v>0.881</v>
       </c>
       <c r="D3">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="E3">
         <v>0.0</v>
@@ -258,7 +258,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.714</v>
+        <v>0.738</v>
       </c>
       <c r="D4">
         <v>21.4</v>
@@ -280,7 +280,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.714</v>
+        <v>0.738</v>
       </c>
       <c r="D5">
         <v>19.0</v>
@@ -302,7 +302,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.714</v>
+        <v>0.69</v>
       </c>
       <c r="D6">
         <v>11.9</v>
@@ -324,7 +324,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D7">
         <v>11.9</v>
@@ -398,7 +398,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>71.85</v>
+        <v>72.28</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>58.33</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>10.0</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="3">
@@ -427,25 +427,25 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>71.4</v>
+        <v>66.85</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>66.67</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>6.67</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>66.05</v>
+        <v>66.32</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>58.33</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>3.33</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="5">
@@ -482,13 +482,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>65.85</v>
+        <v>66.08</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -497,13 +497,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>58.33</v>
+        <v>100.0</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>65.6</v>
@@ -540,13 +540,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>65.35</v>
+        <v>65.6</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>58.33</v>
+        <v>100.0</v>
       </c>
       <c r="H7">
         <v>80.0</v>
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>62.95</v>
+        <v>65.18</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>75.0</v>
+        <v>50.0</v>
       </c>
       <c r="H8">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I8">
-        <v>16.67</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="9">
@@ -598,10 +598,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C9">
-        <v>62.45</v>
+        <v>63.35</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -610,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>75.0</v>
@@ -619,7 +619,7 @@
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>13.33</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="10">
@@ -627,13 +627,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>62.35</v>
+        <v>62.38</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -642,13 +642,13 @@
         <v>4</v>
       </c>
       <c r="G10">
-        <v>58.33</v>
+        <v>75.0</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>62.0</v>
+        <v>62.28</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>83.33</v>
+        <v>58.33</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>10.0</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>61.85</v>
+        <v>61.42</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>58.33</v>
+        <v>75.0</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>10.0</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="13">
@@ -714,13 +714,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C13">
-        <v>60.95</v>
+        <v>60.83</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -729,13 +729,13 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>75.0</v>
+        <v>58.33</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>60.55</v>
+        <v>60.67</v>
       </c>
       <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
         <v>11</v>
       </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
       <c r="G14">
-        <v>91.67</v>
+        <v>58.33</v>
       </c>
       <c r="H14">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="15">
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>60.35</v>
+        <v>60.19</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -793,7 +793,7 @@
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>33.33</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>60.35</v>
+        <v>59.54</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H16">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I16">
-        <v>0.0</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>59.85</v>
+        <v>57.87</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>58.33</v>
+        <v>75.0</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>30.0</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>59.2</v>
+        <v>57.77</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>30.0</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="19">
@@ -891,7 +891,7 @@
         <v>47</v>
       </c>
       <c r="C19">
-        <v>56.35</v>
+        <v>56.64</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -900,7 +900,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>58.33</v>
@@ -909,7 +909,7 @@
         <v>20.0</v>
       </c>
       <c r="I19">
-        <v>40.0</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C20">
-        <v>56.2</v>
+        <v>55.99</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>50.0</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I20">
-        <v>10.0</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C21">
-        <v>55.7</v>
+        <v>55.83</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>12</v>
-      </c>
       <c r="G21">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H21">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I21">
-        <v>40.0</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C22">
-        <v>55.35</v>
+        <v>55.72</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
       <c r="G22">
-        <v>58.33</v>
+        <v>41.67</v>
       </c>
       <c r="H22">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C23">
-        <v>55.25</v>
+        <v>55.4</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>41.67</v>
+        <v>66.67</v>
       </c>
       <c r="H23">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>3.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C24">
-        <v>55.2</v>
+        <v>55.35</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
         <v>0</v>
       </c>
-      <c r="F24">
-        <v>21</v>
-      </c>
       <c r="G24">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H24">
+        <v>40.0</v>
+      </c>
+      <c r="I24">
         <v>0.0</v>
-      </c>
-      <c r="I24">
-        <v>70.0</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C25">
-        <v>54.85</v>
+        <v>55.35</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G25">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H25">
         <v>0.0</v>
       </c>
       <c r="I25">
-        <v>63.33</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>54.7</v>
+      </c>
+      <c r="D26">
         <v>6</v>
       </c>
-      <c r="C26">
-        <v>54.35</v>
-      </c>
-      <c r="D26">
-        <v>7</v>
-      </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I26">
-        <v>26.67</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>53.7</v>
+        <v>54.7</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H27">
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>26.67</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C28">
-        <v>53.35</v>
+        <v>54.7</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
         <v>0</v>
       </c>
-      <c r="F28">
-        <v>16</v>
-      </c>
       <c r="G28">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H28">
+        <v>40.0</v>
+      </c>
+      <c r="I28">
         <v>0.0</v>
-      </c>
-      <c r="I28">
-        <v>53.33</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C29">
-        <v>52.85</v>
+        <v>54.38</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G29">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H29">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29">
-        <v>16.67</v>
+        <v>64.52</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C30">
-        <v>52.7</v>
+        <v>53.58</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H30">
         <v>0.0</v>
       </c>
       <c r="I30">
-        <v>53.33</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C31">
-        <v>51.75</v>
+        <v>52.93</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G31">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H31">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I31">
-        <v>13.33</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="32">
@@ -1268,7 +1268,7 @@
         <v>20</v>
       </c>
       <c r="C32">
-        <v>51.7</v>
+        <v>52.12</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -1277,7 +1277,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>50.0</v>
@@ -1286,7 +1286,7 @@
         <v>20.0</v>
       </c>
       <c r="I32">
-        <v>13.33</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="C33">
-        <v>50.75</v>
+        <v>51.69</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33">
         <v>41.67</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>6.67</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
         <v>3</v>
       </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
       <c r="G34">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H34">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>3.33</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="35">
@@ -1355,7 +1355,7 @@
         <v>13</v>
       </c>
       <c r="C35">
-        <v>50.25</v>
+        <v>50.56</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G35">
         <v>41.67</v>
@@ -1373,7 +1373,7 @@
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>36.67</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>49.8</v>
+        <v>50.18</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="H36">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I36">
-        <v>100.0</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C37">
-        <v>49.7</v>
+        <v>47.38</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G37">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="H37">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I37">
-        <v>0.0</v>
+        <v>83.87</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C38">
-        <v>48.75</v>
+        <v>47.22</v>
       </c>
       <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
         <v>5</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>8</v>
-      </c>
       <c r="G38">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I38">
-        <v>26.67</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C39">
-        <v>47.75</v>
+        <v>45.77</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H39">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I39">
-        <v>20.0</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>47.3</v>
+        <v>44.85</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G40">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H40">
         <v>0.0</v>
       </c>
       <c r="I40">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="C41">
-        <v>45.8</v>
+        <v>44.15</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G41">
         <v>33.33</v>
       </c>
       <c r="H41">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I41">
-        <v>6.67</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>43.8</v>
+        <v>43.24</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H42">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I42">
-        <v>26.67</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C43">
-        <v>42.85</v>
+        <v>42.7</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>6</v>
       </c>
       <c r="G43">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H43">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I43">
-        <v>20.0</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G44">
         <v>25.0</v>
@@ -1634,7 +1634,7 @@
         <v>0.0</v>
       </c>
       <c r="I44">
-        <v>83.33</v>
+        <v>83.87</v>
       </c>
     </row>
     <row r="45">
@@ -1642,10 +1642,10 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C45">
-        <v>42.3</v>
+        <v>41.73</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G45">
         <v>33.33</v>
@@ -1663,7 +1663,7 @@
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>16.67</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="46">
@@ -1671,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C46">
-        <v>41.3</v>
+        <v>41.25</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>10.0</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="47">
@@ -1700,10 +1700,10 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C47">
-        <v>40.8</v>
+        <v>41.25</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47">
         <v>33.33</v>
@@ -1721,7 +1721,7 @@
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>6.67</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="C48">
-        <v>40.35</v>
+        <v>40.66</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G48">
         <v>25.0</v>
@@ -1750,7 +1750,7 @@
         <v>20.0</v>
       </c>
       <c r="I48">
-        <v>36.67</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>30</v>
       </c>
       <c r="C49">
-        <v>36.35</v>
+        <v>36.78</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49">
         <v>25.0</v>
@@ -1779,7 +1779,7 @@
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>10.0</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>30.95</v>
+        <v>31.08</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G50">
         <v>8.33</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>73.33</v>
+        <v>74.19</v>
       </c>
     </row>
   </sheetData>
@@ -1867,359 +1867,359 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>25</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I4">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G8">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I8">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G9">
         <v>35</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I10">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H11">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H12">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <v>15</v>
@@ -2228,345 +2228,345 @@
         <v>18</v>
       </c>
       <c r="G13">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H13">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I13">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E14">
+        <v>15</v>
+      </c>
+      <c r="F14">
+        <v>18</v>
+      </c>
+      <c r="G14">
         <v>19</v>
       </c>
-      <c r="F14">
-        <v>23</v>
-      </c>
-      <c r="G14">
-        <v>39</v>
-      </c>
       <c r="H14">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I14">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I15">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G16">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H16">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>24</v>
+      </c>
+      <c r="G17">
         <v>29</v>
       </c>
-      <c r="F17">
-        <v>33</v>
-      </c>
-      <c r="G17">
-        <v>34</v>
-      </c>
       <c r="H17">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I17">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G18">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H18">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I18">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G19">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H19">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I19">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H20">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G21">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H21">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I21">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>25</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G22">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H22">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I22">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G23">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H23">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C24">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>16</v>
+      </c>
+      <c r="F24">
         <v>20</v>
-      </c>
-      <c r="D24">
-        <v>26</v>
-      </c>
-      <c r="E24">
-        <v>29</v>
-      </c>
-      <c r="F24">
-        <v>31</v>
       </c>
       <c r="G24">
         <v>37</v>
@@ -2575,810 +2575,810 @@
         <v>49</v>
       </c>
       <c r="I24">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25">
         <v>29</v>
       </c>
       <c r="F25">
+        <v>31</v>
+      </c>
+      <c r="G25">
         <v>37</v>
       </c>
-      <c r="G25">
-        <v>47</v>
-      </c>
       <c r="H25">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G26">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H26">
         <v>48</v>
       </c>
       <c r="I26">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G27">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H27">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I27">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C28">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F28">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G28">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H28">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G29">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H29">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I29">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D30">
+        <v>12</v>
+      </c>
+      <c r="E30">
         <v>18</v>
       </c>
-      <c r="E30">
-        <v>25</v>
-      </c>
       <c r="F30">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G30">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H30">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I30">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>28</v>
       </c>
       <c r="G31">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H31">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I31">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F32">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G32">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H32">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I32">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G33">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H33">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34">
+        <v>14</v>
+      </c>
+      <c r="F34">
+        <v>25</v>
+      </c>
+      <c r="G34">
+        <v>26</v>
+      </c>
+      <c r="H34">
+        <v>32</v>
+      </c>
+      <c r="I34">
         <v>7</v>
-      </c>
-      <c r="D34">
-        <v>14</v>
-      </c>
-      <c r="E34">
-        <v>16</v>
-      </c>
-      <c r="F34">
-        <v>37</v>
-      </c>
-      <c r="G34">
-        <v>39</v>
-      </c>
-      <c r="H34">
-        <v>47</v>
-      </c>
-      <c r="I34">
-        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F35">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G35">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H35">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I35">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F36">
+        <v>19</v>
+      </c>
+      <c r="G36">
+        <v>20</v>
+      </c>
+      <c r="H36">
+        <v>40</v>
+      </c>
+      <c r="I36">
         <v>22</v>
-      </c>
-      <c r="G36">
-        <v>40</v>
-      </c>
-      <c r="H36">
-        <v>45</v>
-      </c>
-      <c r="I36">
-        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E37">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F37">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G37">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H37">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I37">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F38">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G38">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H38">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I38">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H39">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I39">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G40">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H40">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I40">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41">
+        <v>13</v>
+      </c>
+      <c r="F41">
         <v>25</v>
       </c>
-      <c r="F41">
-        <v>40</v>
-      </c>
       <c r="G41">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H41">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I41">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E42">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F42">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G42">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H42">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I42">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F43">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G43">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H43">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I43">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D44">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E44">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F44">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G44">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H44">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I44">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F45">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G45">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H45">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I45">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G46">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H46">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E47">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F47">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G47">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H47">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I47">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C48">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <v>11</v>
       </c>
       <c r="E48">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F48">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G48">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H48">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I48">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D49">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E49">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F49">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G49">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H49">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I49">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C50">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D50">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E50">
         <v>27</v>
       </c>
       <c r="F50">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G50">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H50">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I50">
         <v>37</v>
@@ -3386,30 +3386,30 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D51">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E51">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G51">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H51">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I51">
         <v>37</v>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-18 第 115000080 期；威力彩 2026-08-17 第 115000066 期</t>
+          <t>大樂透 2026-08-18 第 115000080 期；威力彩 2026-08-20 第 115000067 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 14, 19, 29, 35, 38</t>
+          <t>9, 11, 14, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.357 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,13 +3464,13 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.024</v>
+        <v>1.048</v>
       </c>
       <c r="D2">
         <v>31.0</v>
       </c>
       <c r="E2">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -3486,13 +3486,13 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.024</v>
+        <v>1.048</v>
       </c>
       <c r="D3">
         <v>31.0</v>
       </c>
       <c r="E3">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3508,13 +3508,13 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.952</v>
+        <v>1.0</v>
       </c>
       <c r="D4">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="E4">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3523,7 +3523,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B5">
@@ -3533,10 +3533,10 @@
         <v>0.952</v>
       </c>
       <c r="D5">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="E5">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3545,20 +3545,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.929</v>
+        <v>0.952</v>
       </c>
       <c r="D6">
-        <v>19.0</v>
+        <v>28.6</v>
       </c>
       <c r="E6">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3648,25 +3648,25 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>74.69</v>
+        <v>73.4</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>86.67</v>
+        <v>100.0</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>22.58</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>72.07</v>
+        <v>73.16</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>73.33</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>6.45</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>71.2</v>
+        <v>69.91</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>80.0</v>
+        <v>78.57</v>
       </c>
       <c r="H4">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>67.94</v>
+        <v>68.5</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>78.57</v>
       </c>
       <c r="H5">
-        <v>80.0</v>
+        <v>83.33</v>
       </c>
       <c r="I5">
-        <v>12.9</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>66.1</v>
+        <v>66.44</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>73.33</v>
+        <v>71.43</v>
       </c>
       <c r="H6">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>66.0</v>
+        <v>65.09</v>
       </c>
       <c r="D7">
         <v>10</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>71.43</v>
       </c>
       <c r="H7">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>65.84</v>
+        <v>64.56</v>
       </c>
       <c r="D8">
         <v>10</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>71.43</v>
+      </c>
+      <c r="H8">
         <v>66.67</v>
       </c>
-      <c r="H8">
-        <v>60.0</v>
-      </c>
       <c r="I8">
-        <v>32.26</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="9">
@@ -3851,7 +3851,7 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>64.39</v>
+        <v>63.68</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -3860,16 +3860,16 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>66.67</v>
+        <v>71.43</v>
       </c>
       <c r="H9">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I9">
-        <v>22.58</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="10">
@@ -3880,7 +3880,7 @@
         <v>21</v>
       </c>
       <c r="C10">
-        <v>63.22</v>
+        <v>62.25</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -3889,16 +3889,16 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H10">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I10">
-        <v>16.13</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="11">
@@ -3909,7 +3909,7 @@
         <v>23</v>
       </c>
       <c r="C11">
-        <v>63.22</v>
+        <v>62.25</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -3918,16 +3918,16 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H11">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I11">
-        <v>16.13</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="12">
@@ -3935,13 +3935,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>62.94</v>
+        <v>61.32</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3950,13 +3950,13 @@
         <v>4</v>
       </c>
       <c r="G12">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="H12">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I12">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
@@ -3964,10 +3964,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>62.25</v>
+        <v>60.38</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -3976,16 +3976,16 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H13">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I13">
-        <v>9.68</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14">
-        <v>62.25</v>
+        <v>58.35</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>53.33</v>
+        <v>78.57</v>
       </c>
       <c r="H14">
-        <v>60.0</v>
+        <v>33.33</v>
       </c>
       <c r="I14">
-        <v>9.68</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>61.28</v>
+        <v>58.1</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>53.33</v>
+        <v>71.43</v>
       </c>
       <c r="H15">
-        <v>60.0</v>
+        <v>33.33</v>
       </c>
       <c r="I15">
-        <v>3.23</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="16">
@@ -4054,7 +4054,7 @@
         <v>17</v>
       </c>
       <c r="C16">
-        <v>58.22</v>
+        <v>58.09</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -4063,16 +4063,16 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H16">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I16">
-        <v>16.13</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C17">
-        <v>58.03</v>
+        <v>57.2</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>73.33</v>
+        <v>100.0</v>
       </c>
       <c r="H17">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I17">
-        <v>12.9</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>57.97</v>
+        <v>57.17</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>80.0</v>
+        <v>71.43</v>
       </c>
       <c r="H18">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I18">
-        <v>45.16</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19">
-        <v>57.3</v>
+        <v>57.15</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>46.67</v>
+        <v>57.14</v>
       </c>
       <c r="H19">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I19">
-        <v>100.0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>56.97</v>
+        <v>56.93</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>66.67</v>
+        <v>64.29</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I20">
-        <v>6.45</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="21">
@@ -4196,13 +4196,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>56.87</v>
+        <v>56.21</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -4211,13 +4211,13 @@
         <v>2</v>
       </c>
       <c r="G21">
-        <v>60.0</v>
+        <v>57.14</v>
       </c>
       <c r="H21">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I21">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C22">
-        <v>56.5</v>
+        <v>54.65</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>100.0</v>
+        <v>78.57</v>
       </c>
       <c r="H22">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C23">
-        <v>56.28</v>
+        <v>54.26</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G23">
-        <v>53.33</v>
+        <v>42.86</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I23">
-        <v>3.23</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>52.7</v>
+      </c>
+      <c r="D24">
         <v>6</v>
       </c>
-      <c r="C24">
-        <v>56.17</v>
-      </c>
-      <c r="D24">
-        <v>7</v>
-      </c>
       <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
         <v>2</v>
       </c>
-      <c r="F24">
-        <v>8</v>
-      </c>
       <c r="G24">
-        <v>46.67</v>
+        <v>42.86</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I24">
-        <v>25.81</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>53.88</v>
+        <v>52.33</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>40.0</v>
+        <v>92.86</v>
       </c>
       <c r="H25">
-        <v>60.0</v>
+        <v>16.67</v>
       </c>
       <c r="I25">
-        <v>3.23</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>53.52</v>
+        <v>51.76</v>
       </c>
       <c r="D26">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>73.33</v>
+        <v>42.86</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="I26">
-        <v>16.13</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>50.47</v>
+        <v>51.69</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
-        <v>60.0</v>
+        <v>16.67</v>
       </c>
       <c r="I27">
-        <v>6.45</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C28">
-        <v>48.24</v>
+        <v>49.12</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>40.0</v>
+        <v>35.71</v>
       </c>
       <c r="H28">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="I28">
-        <v>32.26</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>45.95</v>
+        <v>48.58</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="H29">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I29">
-        <v>9.68</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>45.95</v>
+        <v>47.59</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G30">
+        <v>42.86</v>
+      </c>
+      <c r="H30">
         <v>33.33</v>
       </c>
-      <c r="H30">
-        <v>40.0</v>
-      </c>
       <c r="I30">
-        <v>9.68</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -4486,10 +4486,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C31">
-        <v>45.47</v>
+        <v>45.42</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,16 +4498,16 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31">
+        <v>35.71</v>
+      </c>
+      <c r="H31">
         <v>33.33</v>
       </c>
-      <c r="H31">
-        <v>40.0</v>
-      </c>
       <c r="I31">
-        <v>6.45</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>44.5</v>
+        <v>40.91</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32">
+        <v>28.57</v>
+      </c>
+      <c r="H32">
         <v>33.33</v>
       </c>
-      <c r="H32">
-        <v>40.0</v>
-      </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>42.38</v>
+        <v>39.85</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>26.67</v>
+        <v>35.71</v>
       </c>
       <c r="H33">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I33">
-        <v>45.16</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C34">
-        <v>40.57</v>
+        <v>39.85</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>20.0</v>
+        <v>35.71</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I34">
-        <v>25.81</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>39.98</v>
+        <v>39.68</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G35">
+        <v>21.43</v>
+      </c>
+      <c r="H35">
         <v>33.33</v>
       </c>
-      <c r="H35">
-        <v>20.0</v>
-      </c>
       <c r="I35">
-        <v>3.23</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>39.98</v>
+        <v>38.2</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G36">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="H36">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I36">
-        <v>3.23</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>39.5</v>
+        <v>36.28</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="H37">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I37">
-        <v>0.0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="38">
@@ -4689,10 +4689,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>37.02</v>
+        <v>33.17</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,16 +4701,16 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>20.0</v>
+        <v>21.43</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I38">
-        <v>35.48</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="39">
@@ -4718,28 +4718,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C39">
-        <v>33.15</v>
+        <v>32.88</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G39">
-        <v>20.0</v>
+        <v>14.29</v>
       </c>
       <c r="H39">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I39">
-        <v>9.68</v>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
@@ -4798,185 +4798,185 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
         <v>11</v>
       </c>
-      <c r="E2">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>19</v>
-      </c>
       <c r="G2">
+        <v>29</v>
+      </c>
+      <c r="H2">
         <v>35</v>
       </c>
-      <c r="H2">
-        <v>38</v>
-      </c>
       <c r="I2">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>26</v>
+      </c>
+      <c r="H6">
+        <v>33</v>
+      </c>
+      <c r="I6">
         <v>4</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>26</v>
-      </c>
-      <c r="G6">
-        <v>34</v>
-      </c>
-      <c r="H6">
-        <v>36</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -4984,30 +4984,30 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>17</v>
+      </c>
+      <c r="F8">
         <v>19</v>
       </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>28</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
       <c r="G8">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H8">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -5015,30 +5015,30 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -5046,24 +5046,24 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>13</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G10">
         <v>29</v>
@@ -5072,97 +5072,97 @@
         <v>31</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C11">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D11">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>13</v>
+      </c>
+      <c r="F11">
         <v>23</v>
       </c>
-      <c r="E11">
-        <v>25</v>
-      </c>
-      <c r="F11">
+      <c r="G11">
         <v>29</v>
       </c>
-      <c r="G11">
-        <v>34</v>
-      </c>
       <c r="H11">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12">
+        <v>25</v>
+      </c>
+      <c r="F12">
         <v>29</v>
       </c>
-      <c r="F12">
-        <v>32</v>
-      </c>
       <c r="G12">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G13">
         <v>35</v>
       </c>
       <c r="H13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -5170,402 +5170,402 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G15">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H15">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G16">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H16">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17">
         <v>6</v>
       </c>
-      <c r="D17">
-        <v>10</v>
-      </c>
       <c r="E17">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G18">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H18">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>18</v>
+      </c>
+      <c r="H20">
+        <v>23</v>
+      </c>
+      <c r="I20">
         <v>4</v>
-      </c>
-      <c r="D20">
-        <v>17</v>
-      </c>
-      <c r="E20">
-        <v>19</v>
-      </c>
-      <c r="F20">
-        <v>25</v>
-      </c>
-      <c r="G20">
-        <v>28</v>
-      </c>
-      <c r="H20">
-        <v>29</v>
-      </c>
-      <c r="I20">
-        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H21">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I21">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G22">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H22">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G23">
         <v>28</v>
       </c>
       <c r="H23">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G24">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H24">
         <v>35</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>15</v>
+      </c>
+      <c r="G25">
         <v>24</v>
       </c>
-      <c r="F25">
-        <v>31</v>
-      </c>
-      <c r="G25">
-        <v>34</v>
-      </c>
       <c r="H25">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G26">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H26">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I26">
         <v>3</v>
@@ -5573,554 +5573,554 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G27">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H27">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G28">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H28">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C29">
         <v>6</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F29">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G29">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H29">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G30">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H30">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D31">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F31">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G31">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H31">
         <v>38</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F32">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G32">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H32">
         <v>38</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G33">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H33">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>13</v>
+      </c>
+      <c r="F34">
+        <v>19</v>
+      </c>
+      <c r="G34">
+        <v>27</v>
+      </c>
+      <c r="H34">
+        <v>30</v>
+      </c>
+      <c r="I34">
         <v>8</v>
-      </c>
-      <c r="E34">
-        <v>27</v>
-      </c>
-      <c r="F34">
-        <v>33</v>
-      </c>
-      <c r="G34">
-        <v>35</v>
-      </c>
-      <c r="H34">
-        <v>38</v>
-      </c>
-      <c r="I34">
-        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G35">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H35">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F36">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G36">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H36">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F37">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G37">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H37">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G38">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H38">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F39">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G39">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H39">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E40">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F40">
         <v>27</v>
       </c>
       <c r="G40">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H40">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
       <c r="D41">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G41">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H41">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E42">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F42">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G42">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H42">
         <v>34</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
         <v>13</v>
       </c>
-      <c r="D43">
-        <v>14</v>
-      </c>
       <c r="E43">
+        <v>21</v>
+      </c>
+      <c r="F43">
         <v>22</v>
       </c>
-      <c r="F43">
-        <v>28</v>
-      </c>
       <c r="G43">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H43">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E44">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F44">
         <v>28</v>
       </c>
       <c r="G44">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H44">
         <v>38</v>
@@ -6131,58 +6131,58 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
         <v>9</v>
       </c>
-      <c r="D45">
-        <v>13</v>
-      </c>
       <c r="E45">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F45">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G45">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H45">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C46">
+        <v>9</v>
+      </c>
+      <c r="D46">
+        <v>13</v>
+      </c>
+      <c r="E46">
         <v>14</v>
       </c>
-      <c r="D46">
-        <v>26</v>
-      </c>
-      <c r="E46">
-        <v>28</v>
-      </c>
       <c r="F46">
+        <v>18</v>
+      </c>
+      <c r="G46">
         <v>31</v>
-      </c>
-      <c r="G46">
-        <v>32</v>
       </c>
       <c r="H46">
         <v>34</v>
@@ -6193,61 +6193,61 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E47">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G47">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H47">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I47">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F48">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G48">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H48">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I48">
         <v>8</v>
@@ -6255,15 +6255,15 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>11</v>
@@ -6272,78 +6272,78 @@
         <v>14</v>
       </c>
       <c r="F49">
+        <v>17</v>
+      </c>
+      <c r="G49">
+        <v>29</v>
+      </c>
+      <c r="H49">
         <v>32</v>
       </c>
-      <c r="G49">
-        <v>36</v>
-      </c>
-      <c r="H49">
-        <v>38</v>
-      </c>
       <c r="I49">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C50">
         <v>7</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F50">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G50">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H50">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000017</v>
+        <v>115000018</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E51">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F51">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G51">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H51">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-18 第 115000080 期；威力彩 2026-08-20 第 115000067 期</t>
+          <t>大樂透 2026-08-21 第 115000081 期；威力彩 2026-08-20 第 115000067 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 11, 12, 16, 25, 29</t>
+          <t>4, 11, 12, 25, 26, 29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -258,7 +258,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.738</v>
+        <v>0.762</v>
       </c>
       <c r="D4">
         <v>21.4</v>
@@ -280,7 +280,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.738</v>
+        <v>0.762</v>
       </c>
       <c r="D5">
         <v>19.0</v>
@@ -324,10 +324,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.595</v>
       </c>
       <c r="D7">
-        <v>11.9</v>
+        <v>9.5</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -398,7 +398,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>72.28</v>
+        <v>72.69</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>58.33</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>12.9</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>66.85</v>
+        <v>70.4</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>66.67</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>9.68</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,10 +453,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>66.32</v>
+        <v>67.22</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -465,7 +465,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>58.33</v>
@@ -474,7 +474,7 @@
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>6.45</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>66.08</v>
+        <v>66.54</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -494,7 +494,7 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>100.0</v>
@@ -503,7 +503,7 @@
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>3.23</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
@@ -514,25 +514,25 @@
         <v>25</v>
       </c>
       <c r="C6">
-        <v>65.6</v>
+        <v>66.02</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>100.0</v>
+        <v>91.67</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>65.6</v>
+        <v>65.64</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="H7">
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C8">
-        <v>65.18</v>
+        <v>65.5</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>50.0</v>
+        <v>83.33</v>
       </c>
       <c r="H8">
         <v>80.0</v>
       </c>
       <c r="I8">
-        <v>3.23</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>63.35</v>
+        <v>61.29</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>75.0</v>
+        <v>58.33</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>19.35</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C10">
-        <v>62.38</v>
+        <v>61.07</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>75.0</v>
+        <v>100.0</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>12.9</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>62.28</v>
+        <v>60.97</v>
       </c>
       <c r="D11">
         <v>7</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>58.33</v>
       </c>
       <c r="H11">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I11">
-        <v>12.9</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12">
-        <v>61.42</v>
+        <v>60.4</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>75.0</v>
+        <v>66.67</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>6.45</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C13">
-        <v>60.83</v>
+        <v>60.4</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>3.23</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>60.67</v>
+        <v>58.26</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>58.33</v>
+        <v>75.0</v>
       </c>
       <c r="H14">
         <v>40.0</v>
       </c>
       <c r="I14">
-        <v>35.48</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>60.19</v>
+        <v>57.79</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>58.33</v>
+        <v>75.0</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>32.26</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C16">
-        <v>59.54</v>
+        <v>57.69</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>32.26</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="17">
@@ -830,10 +830,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C17">
-        <v>57.87</v>
+        <v>56.86</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17">
         <v>75.0</v>
@@ -851,7 +851,7 @@
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>16.13</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C18">
-        <v>57.77</v>
+        <v>56.16</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>58.33</v>
+        <v>41.67</v>
       </c>
       <c r="H18">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I18">
-        <v>16.13</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C19">
-        <v>56.64</v>
+        <v>55.87</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>13</v>
-      </c>
       <c r="G19">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H19">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I19">
-        <v>41.94</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C20">
-        <v>55.99</v>
+        <v>55.64</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <v>50.0</v>
       </c>
       <c r="H20">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>41.94</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>55.83</v>
+        <v>55.51</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>58.33</v>
       </c>
       <c r="H21">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I21">
-        <v>3.23</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C22">
-        <v>55.72</v>
+        <v>55.48</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G22">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H22">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="I22">
-        <v>6.45</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="23">
@@ -1004,7 +1004,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>55.4</v>
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>55.35</v>
+        <v>55.17</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H24">
         <v>40.0</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>55.35</v>
+        <v>55.04</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H25">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>70.97</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C26">
-        <v>54.7</v>
+        <v>54.86</v>
       </c>
       <c r="D26">
         <v>6</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>50.0</v>
       </c>
       <c r="H26">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C27">
-        <v>54.7</v>
+        <v>54.75</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>58.33</v>
+        <v>41.67</v>
       </c>
       <c r="H27">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="I27">
-        <v>29.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>54.7</v>
+        <v>54.54</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G28">
         <v>50.0</v>
       </c>
       <c r="H28">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28">
-        <v>0.0</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C29">
-        <v>54.38</v>
+        <v>53.79</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G29">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H29">
         <v>0.0</v>
       </c>
       <c r="I29">
-        <v>64.52</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>53.58</v>
+        <v>52.51</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H30">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I30">
-        <v>54.84</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C31">
-        <v>52.93</v>
+        <v>52.09</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H31">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>54.84</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>52.12</v>
+        <v>51.63</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I32">
-        <v>16.13</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C33">
-        <v>51.69</v>
+        <v>51.31</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>41.67</v>
       </c>
       <c r="H33">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I33">
-        <v>12.9</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C34">
-        <v>51.2</v>
+        <v>50.84</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G34">
         <v>41.67</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I34">
-        <v>9.68</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>50.56</v>
+        <v>50.64</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H35">
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>38.71</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
+        <v>27</v>
+      </c>
+      <c r="C36">
+        <v>50.22</v>
+      </c>
+      <c r="D36">
         <v>5</v>
       </c>
-      <c r="C36">
-        <v>50.18</v>
-      </c>
-      <c r="D36">
-        <v>6</v>
-      </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H36">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I36">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C37">
-        <v>47.38</v>
+        <v>48.19</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G37">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H37">
         <v>0.0</v>
       </c>
       <c r="I37">
-        <v>83.87</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="38">
@@ -1442,7 +1442,7 @@
         <v>44</v>
       </c>
       <c r="C38">
-        <v>47.22</v>
+        <v>47.61</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -1451,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>33.33</v>
@@ -1460,7 +1460,7 @@
         <v>40.0</v>
       </c>
       <c r="I38">
-        <v>16.13</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C39">
-        <v>45.77</v>
+        <v>47.46</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G39">
         <v>33.33</v>
       </c>
       <c r="H39">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I39">
-        <v>6.45</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="40">
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G40">
         <v>25.0</v>
@@ -1529,7 +1529,7 @@
         <v>17</v>
       </c>
       <c r="C41">
-        <v>44.15</v>
+        <v>44.49</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G41">
         <v>33.33</v>
@@ -1547,7 +1547,7 @@
         <v>20.0</v>
       </c>
       <c r="I41">
-        <v>29.03</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="42">
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="C42">
-        <v>43.24</v>
+        <v>43.6</v>
       </c>
       <c r="D42">
         <v>3</v>
@@ -1567,7 +1567,7 @@
         <v>2</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G42">
         <v>25.0</v>
@@ -1576,7 +1576,7 @@
         <v>40.0</v>
       </c>
       <c r="I42">
-        <v>22.58</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="43">
@@ -1587,7 +1587,7 @@
         <v>32</v>
       </c>
       <c r="C43">
-        <v>42.7</v>
+        <v>43.08</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G43">
         <v>33.33</v>
@@ -1605,7 +1605,7 @@
         <v>20.0</v>
       </c>
       <c r="I43">
-        <v>19.35</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>42.43</v>
+        <v>42.51</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G44">
         <v>25.0</v>
@@ -1634,7 +1634,7 @@
         <v>0.0</v>
       </c>
       <c r="I44">
-        <v>83.87</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>9</v>
       </c>
       <c r="C45">
-        <v>41.73</v>
+        <v>42.14</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45">
         <v>33.33</v>
@@ -1663,7 +1663,7 @@
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>12.9</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>41.25</v>
+        <v>41.67</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46">
         <v>33.33</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>9.68</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>41</v>
       </c>
       <c r="C47">
-        <v>41.25</v>
+        <v>41.67</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47">
         <v>33.33</v>
@@ -1721,7 +1721,7 @@
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>9.68</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="C48">
-        <v>40.66</v>
+        <v>40.94</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G48">
         <v>25.0</v>
@@ -1750,7 +1750,7 @@
         <v>20.0</v>
       </c>
       <c r="I48">
-        <v>38.71</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>30</v>
       </c>
       <c r="C49">
-        <v>36.78</v>
+        <v>37.19</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G49">
         <v>25.0</v>
@@ -1779,7 +1779,7 @@
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>12.9</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.08</v>
+        <v>31.2</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G50">
         <v>8.33</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>74.19</v>
+        <v>75.0</v>
       </c>
     </row>
   </sheetData>
@@ -1867,390 +1867,390 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>14</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>25</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>12</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I8">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G9">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G10">
         <v>35</v>
       </c>
       <c r="H10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G11">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I11">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H12">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G13">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H13">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>15</v>
@@ -2259,345 +2259,345 @@
         <v>18</v>
       </c>
       <c r="G14">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I14">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E15">
+        <v>15</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15">
         <v>19</v>
       </c>
-      <c r="F15">
-        <v>23</v>
-      </c>
-      <c r="G15">
-        <v>39</v>
-      </c>
       <c r="H15">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G16">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H16">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I16">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G17">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H17">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18">
+        <v>23</v>
+      </c>
+      <c r="F18">
+        <v>24</v>
+      </c>
+      <c r="G18">
         <v>29</v>
       </c>
-      <c r="F18">
-        <v>33</v>
-      </c>
-      <c r="G18">
-        <v>34</v>
-      </c>
       <c r="H18">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I18">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H19">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I19">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G20">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H20">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I20">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H21">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C22">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G22">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H22">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I22">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>25</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G23">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H23">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I23">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G24">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H24">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="E25">
+        <v>16</v>
+      </c>
+      <c r="F25">
         <v>20</v>
-      </c>
-      <c r="D25">
-        <v>26</v>
-      </c>
-      <c r="E25">
-        <v>29</v>
-      </c>
-      <c r="F25">
-        <v>31</v>
       </c>
       <c r="G25">
         <v>37</v>
@@ -2606,810 +2606,810 @@
         <v>49</v>
       </c>
       <c r="I25">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26">
         <v>29</v>
       </c>
       <c r="F26">
+        <v>31</v>
+      </c>
+      <c r="G26">
         <v>37</v>
       </c>
-      <c r="G26">
-        <v>47</v>
-      </c>
       <c r="H26">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G27">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H27">
         <v>48</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D28">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F28">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G28">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H28">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I28">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C29">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E29">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F29">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G29">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H29">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G30">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H30">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I30">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31">
+        <v>12</v>
+      </c>
+      <c r="E31">
         <v>18</v>
       </c>
-      <c r="E31">
-        <v>25</v>
-      </c>
       <c r="F31">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G31">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H31">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I31">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E32">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F32">
         <v>28</v>
       </c>
       <c r="G32">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H32">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I32">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E33">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F33">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G33">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H33">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I33">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G34">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H34">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>14</v>
+      </c>
+      <c r="F35">
+        <v>25</v>
+      </c>
+      <c r="G35">
+        <v>26</v>
+      </c>
+      <c r="H35">
+        <v>32</v>
+      </c>
+      <c r="I35">
         <v>7</v>
-      </c>
-      <c r="D35">
-        <v>14</v>
-      </c>
-      <c r="E35">
-        <v>16</v>
-      </c>
-      <c r="F35">
-        <v>37</v>
-      </c>
-      <c r="G35">
-        <v>39</v>
-      </c>
-      <c r="H35">
-        <v>47</v>
-      </c>
-      <c r="I35">
-        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G36">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H36">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I36">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F37">
+        <v>19</v>
+      </c>
+      <c r="G37">
+        <v>20</v>
+      </c>
+      <c r="H37">
+        <v>40</v>
+      </c>
+      <c r="I37">
         <v>22</v>
-      </c>
-      <c r="G37">
-        <v>40</v>
-      </c>
-      <c r="H37">
-        <v>45</v>
-      </c>
-      <c r="I37">
-        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G38">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H38">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I38">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F39">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G39">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H39">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I39">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H40">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I40">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G41">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H41">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C42">
         <v>5</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E42">
+        <v>13</v>
+      </c>
+      <c r="F42">
         <v>25</v>
       </c>
-      <c r="F42">
-        <v>40</v>
-      </c>
       <c r="G42">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H42">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E43">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F43">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G43">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H43">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I43">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F44">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G44">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H44">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I44">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C45">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E45">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F45">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G45">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H45">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I45">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F46">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G46">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H46">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I46">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F47">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G47">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H47">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C48">
         <v>5</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E48">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F48">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G48">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I48">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D49">
         <v>11</v>
       </c>
       <c r="E49">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F49">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G49">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H49">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I49">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D50">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F50">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G50">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H50">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I50">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C51">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E51">
         <v>27</v>
       </c>
       <c r="F51">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G51">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H51">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I51">
         <v>37</v>
